--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -435,7 +435,7 @@
           <t>PARAMETERS</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>STATUS / CHECKS</t>
         </is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="F2">
-        <f>IF(B2&lt;=0,ERROR: Invalid StartLot,OK)</f>
+        <f>IF(B2&lt;=0,"ERROR: Invalid StartLot","OK")</f>
         <v/>
       </c>
     </row>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="F3">
-        <f>IF(B5&lt;=0,ERROR: Invalid LotStep,OK)</f>
+        <f>IF(B5&lt;=0,"ERROR: Invalid LotStep","OK")</f>
         <v/>
       </c>
     </row>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="F4">
-        <f>IF(B4&lt;1,ERROR: Invalid MaxLevels,OK)</f>
+        <f>IF(B4&lt;1,"ERROR: Invalid MaxLevels","OK")</f>
         <v/>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="F5">
-        <f>IF(OR(B6=DOWN,B6=UP),OK,ERROR: Invalid Direction)</f>
+        <f>IF(OR(B6="DOWN",B6="UP"),"OK","ERROR: Invalid Direction")</f>
         <v/>
       </c>
     </row>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="F6">
-        <f>IF(B3&lt;=0,ERROR: Invalid StepPoints,OK)</f>
+        <f>IF(B3&lt;=0,"ERROR: Invalid StepPoints","OK")</f>
         <v/>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F7">
-        <f>IF(B11&lt;=0,ERROR: Invalid PointValue,OK)</f>
+        <f>IF(B11&lt;=0,"ERROR: Invalid PointValue","OK")</f>
         <v/>
       </c>
     </row>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="F8">
-        <f>IF(B12&lt;0,ERROR: Invalid Spread,OK)</f>
+        <f>IF(B12&lt;0,"ERROR: Invalid Spread","OK")</f>
         <v/>
       </c>
     </row>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F9">
-        <f>IF(B13&lt;0,ERROR: Invalid Commission,OK)</f>
+        <f>IF(B13&lt;0,"ERROR: Invalid Commission","OK")</f>
         <v/>
       </c>
     </row>
@@ -732,11 +732,6 @@
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>ManualClose %</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>TargetSkewLot</t>
         </is>
       </c>
     </row>
@@ -754,10 +749,6 @@
         <v>0</v>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="G18">
-        <f>B2*D18/100</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -773,10 +764,6 @@
         <v>15</v>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="G19">
-        <f>B2*D19/100</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -792,10 +779,6 @@
         <v>10</v>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="G20">
-        <f>B2*D20/100</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -811,10 +794,6 @@
         <v>10</v>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="G21">
-        <f>B2*D21/100</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -830,10 +809,6 @@
         <v>10</v>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="G22">
-        <f>B2*D22/100</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1028,7 +1003,7 @@
         <v/>
       </c>
       <c r="N26">
-        <f>MIN(J26,IF(E26= ,M{r},E{r}))</f>
+        <f>MIN(J26,IF(E26="",M26,E26))</f>
         <v/>
       </c>
       <c r="O26">
@@ -1076,7 +1051,7 @@
         <v/>
       </c>
       <c r="Z26">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B26&lt;C26,B26&lt;0,C26&lt;0,D26&lt;0,E26&lt;0,E26&gt;J26,T26&gt;U26,W26&gt;X26,AND(B26&gt;0,G26=0),AND(C26&gt;0,I26=0)),"ERROR",IF(AND(D26&gt;0,Y26&lt;($B$2*D26/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B26&lt;C26,B26&lt;0,C26&lt;0,D26&lt;0,E26&lt;0,E26&gt;J26,T26&gt;U26,W26&gt;X26,Y26&lt;0,AND(B26&gt;0,G26=0),AND(C26&gt;0,I26=0)),"ERROR",IF(AND(D26&gt;0,Y26&lt;($B$2*D26/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1109,7 @@
         <v/>
       </c>
       <c r="N27">
-        <f>MIN(J27,IF(E27= ,M{r},E{r}))</f>
+        <f>MIN(J27,IF(E27="",M27,E27))</f>
         <v/>
       </c>
       <c r="O27">
@@ -1182,7 +1157,7 @@
         <v/>
       </c>
       <c r="Z27">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B27&lt;C27,B27&lt;0,C27&lt;0,D27&lt;0,E27&lt;0,E27&gt;J27,T27&gt;U27,W27&gt;X27,AND(B27&gt;0,G27=0),AND(C27&gt;0,I27=0)),"ERROR",IF(AND(D27&gt;0,Y27&lt;($B$2*D27/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B27&lt;C27,B27&lt;0,C27&lt;0,D27&lt;0,E27&lt;0,E27&gt;J27,T27&gt;U27,W27&gt;X27,Y27&lt;0,AND(B27&gt;0,G27=0),AND(C27&gt;0,I27=0)),"ERROR",IF(AND(D27&gt;0,Y27&lt;($B$2*D27/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1215,7 @@
         <v/>
       </c>
       <c r="N28">
-        <f>MIN(J28,IF(E28= ,M{r},E{r}))</f>
+        <f>MIN(J28,IF(E28="",M28,E28))</f>
         <v/>
       </c>
       <c r="O28">
@@ -1288,7 +1263,7 @@
         <v/>
       </c>
       <c r="Z28">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B28&lt;C28,B28&lt;0,C28&lt;0,D28&lt;0,E28&lt;0,E28&gt;J28,T28&gt;U28,W28&gt;X28,AND(B28&gt;0,G28=0),AND(C28&gt;0,I28=0)),"ERROR",IF(AND(D28&gt;0,Y28&lt;($B$2*D28/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B28&lt;C28,B28&lt;0,C28&lt;0,D28&lt;0,E28&lt;0,E28&gt;J28,T28&gt;U28,W28&gt;X28,Y28&lt;0,AND(B28&gt;0,G28=0),AND(C28&gt;0,I28=0)),"ERROR",IF(AND(D28&gt;0,Y28&lt;($B$2*D28/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1346,7 +1321,7 @@
         <v/>
       </c>
       <c r="N29">
-        <f>MIN(J29,IF(E29= ,M{r},E{r}))</f>
+        <f>MIN(J29,IF(E29="",M29,E29))</f>
         <v/>
       </c>
       <c r="O29">
@@ -1394,7 +1369,7 @@
         <v/>
       </c>
       <c r="Z29">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B29&lt;C29,B29&lt;0,C29&lt;0,D29&lt;0,E29&lt;0,E29&gt;J29,T29&gt;U29,W29&gt;X29,AND(B29&gt;0,G29=0),AND(C29&gt;0,I29=0)),"ERROR",IF(AND(D29&gt;0,Y29&lt;($B$2*D29/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B29&lt;C29,B29&lt;0,C29&lt;0,D29&lt;0,E29&lt;0,E29&gt;J29,T29&gt;U29,W29&gt;X29,Y29&lt;0,AND(B29&gt;0,G29=0),AND(C29&gt;0,I29=0)),"ERROR",IF(AND(D29&gt;0,Y29&lt;($B$2*D29/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1452,7 +1427,7 @@
         <v/>
       </c>
       <c r="N30">
-        <f>MIN(J30,IF(E30= ,M{r},E{r}))</f>
+        <f>MIN(J30,IF(E30="",M30,E30))</f>
         <v/>
       </c>
       <c r="O30">
@@ -1500,7 +1475,7 @@
         <v/>
       </c>
       <c r="Z30">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B30&lt;C30,B30&lt;0,C30&lt;0,D30&lt;0,E30&lt;0,E30&gt;J30,T30&gt;U30,W30&gt;X30,AND(B30&gt;0,G30=0),AND(C30&gt;0,I30=0)),"ERROR",IF(AND(D30&gt;0,Y30&lt;($B$2*D30/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B30&lt;C30,B30&lt;0,C30&lt;0,D30&lt;0,E30&lt;0,E30&gt;J30,T30&gt;U30,W30&gt;X30,Y30&lt;0,AND(B30&gt;0,G30=0),AND(C30&gt;0,I30=0)),"ERROR",IF(AND(D30&gt;0,Y30&lt;($B$2*D30/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1697,7 +1672,7 @@
         <v/>
       </c>
       <c r="N35">
-        <f>MIN(J35,IF(E35= ,M{r},E{r}))</f>
+        <f>MIN(J35,IF(E35="",M35,E35))</f>
         <v/>
       </c>
       <c r="O35">
@@ -1745,7 +1720,7 @@
         <v/>
       </c>
       <c r="Z35">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B35&lt;C35,B35&lt;0,C35&lt;0,D35&lt;0,E35&lt;0,E35&gt;J35,T35&gt;U35,W35&gt;X35,AND(B35&gt;0,G35=0),AND(C35&gt;0,I35=0)),"ERROR",IF(AND(D35&gt;0,Y35&lt;($B$2*D35/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B35&lt;C35,B35&lt;0,C35&lt;0,D35&lt;0,E35&lt;0,E35&gt;J35,T35&gt;U35,W35&gt;X35,Y35&lt;0,AND(B35&gt;0,G35=0),AND(C35&gt;0,I35=0)),"ERROR",IF(AND(D35&gt;0,Y35&lt;($B$2*D35/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1803,7 +1778,7 @@
         <v/>
       </c>
       <c r="N36">
-        <f>MIN(J36,IF(E36= ,M{r},E{r}))</f>
+        <f>MIN(J36,IF(E36="",M36,E36))</f>
         <v/>
       </c>
       <c r="O36">
@@ -1851,7 +1826,7 @@
         <v/>
       </c>
       <c r="Z36">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B36&lt;C36,B36&lt;0,C36&lt;0,D36&lt;0,E36&lt;0,E36&gt;J36,T36&gt;U36,W36&gt;X36,AND(B36&gt;0,G36=0),AND(C36&gt;0,I36=0)),"ERROR",IF(AND(D36&gt;0,Y36&lt;($B$2*D36/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B36&lt;C36,B36&lt;0,C36&lt;0,D36&lt;0,E36&lt;0,E36&gt;J36,T36&gt;U36,W36&gt;X36,Y36&lt;0,AND(B36&gt;0,G36=0),AND(C36&gt;0,I36=0)),"ERROR",IF(AND(D36&gt;0,Y36&lt;($B$2*D36/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1909,7 +1884,7 @@
         <v/>
       </c>
       <c r="N37">
-        <f>MIN(J37,IF(E37= ,M{r},E{r}))</f>
+        <f>MIN(J37,IF(E37="",M37,E37))</f>
         <v/>
       </c>
       <c r="O37">
@@ -1957,7 +1932,7 @@
         <v/>
       </c>
       <c r="Z37">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B37&lt;C37,B37&lt;0,C37&lt;0,D37&lt;0,E37&lt;0,E37&gt;J37,T37&gt;U37,W37&gt;X37,AND(B37&gt;0,G37=0),AND(C37&gt;0,I37=0)),"ERROR",IF(AND(D37&gt;0,Y37&lt;($B$2*D37/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B37&lt;C37,B37&lt;0,C37&lt;0,D37&lt;0,E37&lt;0,E37&gt;J37,T37&gt;U37,W37&gt;X37,Y37&lt;0,AND(B37&gt;0,G37=0),AND(C37&gt;0,I37=0)),"ERROR",IF(AND(D37&gt;0,Y37&lt;($B$2*D37/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2015,7 +1990,7 @@
         <v/>
       </c>
       <c r="N38">
-        <f>MIN(J38,IF(E38= ,M{r},E{r}))</f>
+        <f>MIN(J38,IF(E38="",M38,E38))</f>
         <v/>
       </c>
       <c r="O38">
@@ -2063,7 +2038,7 @@
         <v/>
       </c>
       <c r="Z38">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B38&lt;C38,B38&lt;0,C38&lt;0,D38&lt;0,E38&lt;0,E38&gt;J38,T38&gt;U38,W38&gt;X38,AND(B38&gt;0,G38=0),AND(C38&gt;0,I38=0)),"ERROR",IF(AND(D38&gt;0,Y38&lt;($B$2*D38/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B38&lt;C38,B38&lt;0,C38&lt;0,D38&lt;0,E38&lt;0,E38&gt;J38,T38&gt;U38,W38&gt;X38,Y38&lt;0,AND(B38&gt;0,G38=0),AND(C38&gt;0,I38=0)),"ERROR",IF(AND(D38&gt;0,Y38&lt;($B$2*D38/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2121,7 +2096,7 @@
         <v/>
       </c>
       <c r="N39">
-        <f>MIN(J39,IF(E39= ,M{r},E{r}))</f>
+        <f>MIN(J39,IF(E39="",M39,E39))</f>
         <v/>
       </c>
       <c r="O39">
@@ -2169,7 +2144,7 @@
         <v/>
       </c>
       <c r="Z39">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B39&lt;C39,B39&lt;0,C39&lt;0,D39&lt;0,E39&lt;0,E39&gt;J39,T39&gt;U39,W39&gt;X39,AND(B39&gt;0,G39=0),AND(C39&gt;0,I39=0)),"ERROR",IF(AND(D39&gt;0,Y39&lt;($B$2*D39/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B39&lt;C39,B39&lt;0,C39&lt;0,D39&lt;0,E39&lt;0,E39&gt;J39,T39&gt;U39,W39&gt;X39,Y39&lt;0,AND(B39&gt;0,G39=0),AND(C39&gt;0,I39=0)),"ERROR",IF(AND(D39&gt;0,Y39&lt;($B$2*D39/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2301,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,12 +2287,12 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Expected</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Actual</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -2332,12 +2307,12 @@
           <t>Down L1 Close%</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
+        <f>Calculator!N26</f>
+        <v/>
+      </c>
+      <c r="C2" t="n">
         <v>60</v>
-      </c>
-      <c r="C2">
-        <f>Calculator!N26</f>
-        <v/>
       </c>
       <c r="D2">
         <f>IF(B2=C2,"PASS","FAIL")</f>
@@ -2350,12 +2325,12 @@
           <t>Down L2 Close%</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
+        <f>Calculator!N27</f>
+        <v/>
+      </c>
+      <c r="C3" t="n">
         <v>30</v>
-      </c>
-      <c r="C3">
-        <f>Calculator!N27</f>
-        <v/>
       </c>
       <c r="D3">
         <f>IF(B3=C3,"PASS","FAIL")</f>
@@ -2365,15 +2340,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Down L3 Close%</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <f>Calculator!N28</f>
-        <v/>
+          <t>Down Final Main</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>Calculator!T30</f>
+        <v/>
+      </c>
+      <c r="C4" t="n">
+        <v>165</v>
       </c>
       <c r="D4">
         <f>IF(B4=C4,"PASS","FAIL")</f>
@@ -2383,15 +2358,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Down Final Main%</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>165</v>
-      </c>
-      <c r="C5">
-        <f>Calculator!T30</f>
-        <v/>
+          <t>Down Final Opp</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>Calculator!U30</f>
+        <v/>
+      </c>
+      <c r="C5" t="n">
+        <v>175</v>
       </c>
       <c r="D5">
         <f>IF(B5=C5,"PASS","FAIL")</f>
@@ -2401,15 +2376,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Down Final Opp%</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>175</v>
-      </c>
-      <c r="C6">
-        <f>Calculator!U30</f>
-        <v/>
+          <t>Down Final Skew</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>Calculator!V30</f>
+        <v/>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
       </c>
       <c r="D6">
         <f>IF(B6=C6,"PASS","FAIL")</f>
@@ -2419,15 +2394,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Down Final Skew%</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <f>Calculator!V30</f>
-        <v/>
+          <t>Up L1 Close%</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>Calculator!N35</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>60</v>
       </c>
       <c r="D7">
         <f>IF(B7=C7,"PASS","FAIL")</f>
@@ -2437,15 +2412,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Up L1 Close%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <f>Calculator!N35</f>
-        <v/>
+          <t>Up L2 Close%</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>Calculator!N36</f>
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v>30</v>
       </c>
       <c r="D8">
         <f>IF(B8=C8,"PASS","FAIL")</f>
@@ -2455,15 +2430,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Up L2 Close%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C9">
-        <f>Calculator!N36</f>
-        <v/>
+          <t>Up Final Main</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>Calculator!T39</f>
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v>165</v>
       </c>
       <c r="D9">
         <f>IF(B9=C9,"PASS","FAIL")</f>
@@ -2473,15 +2448,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Up L3 Close%</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <f>Calculator!N37</f>
-        <v/>
+          <t>Up Final Opp</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>Calculator!U39</f>
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v>175</v>
       </c>
       <c r="D10">
         <f>IF(B10=C10,"PASS","FAIL")</f>
@@ -2491,194 +2466,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Up Final Main%</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>165</v>
-      </c>
-      <c r="C11">
-        <f>Calculator!T39</f>
-        <v/>
+          <t>Up Final Skew</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>Calculator!V39</f>
+        <v/>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
       </c>
       <c r="D11">
         <f>IF(B11=C11,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Up Final Opp%</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>175</v>
-      </c>
-      <c r="C12">
-        <f>Calculator!U39</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>IF(B12=C12,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Up Final Skew%</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <f>Calculator!V39</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>IF(B13=C13,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Level1 TargetSkew=0 no warning</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C14">
-        <f>Calculator!Z26</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>IF(B14=C14,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BigRounded zero test</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C15">
-        <f>IF(AND(Calculator!B22&gt;0,Calculator!G30=0),"ERROR","OK")</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>IF(B15=C15,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SmallRounded zero test</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C16">
-        <f>IF(AND(Calculator!C22&gt;0,Calculator!I30=0),"ERROR","OK")</f>
-        <v/>
-      </c>
-      <c r="D16">
-        <f>IF(B16=C16,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ManualClose &gt; Remaining</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C17">
-        <f>IF(Calculator!E18&gt;Calculator!J26,"ERROR","ERROR")</f>
-        <v/>
-      </c>
-      <c r="D17">
-        <f>IF(B17=C17,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Big &lt; Small</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C18">
-        <f>IF(Calculator!B18&lt;Calculator!C18,"ERROR","ERROR")</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>IF(B18=C18,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>StartLot &lt;= 0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C19">
-        <f>IF(Calculator!B2&lt;=0,"ERROR","ERROR")</f>
-        <v/>
-      </c>
-      <c r="D19">
-        <f>IF(B19=C19,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LotStep &lt;= 0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C20">
-        <f>IF(Calculator!B5&lt;=0,"ERROR","ERROR")</f>
-        <v/>
-      </c>
-      <c r="D20">
-        <f>IF(B20=C20,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -1039,7 +1039,7 @@
         <v/>
       </c>
       <c r="W26">
-        <f>MAX(0,$B$2-P26)+SUM($G$26:G26)</f>
+        <f>$B$2*Q26/100+SUM($G$26:G26)</f>
         <v/>
       </c>
       <c r="X26">
@@ -1051,7 +1051,7 @@
         <v/>
       </c>
       <c r="Z26">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B26&lt;C26,B26&lt;0,C26&lt;0,D26&lt;0,E26&lt;0,E26&gt;J26,T26&gt;U26,W26&gt;X26,Y26&lt;0,AND(B26&gt;0,G26=0),AND(C26&gt;0,I26=0)),"ERROR",IF(AND(D26&gt;0,Y26&lt;($B$2*D26/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B26&lt;C26,B26&lt;0,C26&lt;0,D26&lt;0,E26&lt;0,E26&gt;J26,T26&gt;U26,W26&gt;X26,AND(B26&gt;0,G26=0),AND(C26&gt;0,I26=0)),"ERROR",IF(AND(D26&gt;0,Y26&lt;($B$2*D26/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         <v/>
       </c>
       <c r="W27">
-        <f>MAX(0,$B$2-P27)+SUM($G$26:G27)</f>
+        <f>$B$2*Q27/100+SUM($G$26:G27)</f>
         <v/>
       </c>
       <c r="X27">
@@ -1157,7 +1157,7 @@
         <v/>
       </c>
       <c r="Z27">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B27&lt;C27,B27&lt;0,C27&lt;0,D27&lt;0,E27&lt;0,E27&gt;J27,T27&gt;U27,W27&gt;X27,Y27&lt;0,AND(B27&gt;0,G27=0),AND(C27&gt;0,I27=0)),"ERROR",IF(AND(D27&gt;0,Y27&lt;($B$2*D27/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B27&lt;C27,B27&lt;0,C27&lt;0,D27&lt;0,E27&lt;0,E27&gt;J27,T27&gt;U27,W27&gt;X27,AND(B27&gt;0,G27=0),AND(C27&gt;0,I27=0)),"ERROR",IF(AND(D27&gt;0,Y27&lt;($B$2*D27/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="W28">
-        <f>MAX(0,$B$2-P28)+SUM($G$26:G28)</f>
+        <f>$B$2*Q28/100+SUM($G$26:G28)</f>
         <v/>
       </c>
       <c r="X28">
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="Z28">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B28&lt;C28,B28&lt;0,C28&lt;0,D28&lt;0,E28&lt;0,E28&gt;J28,T28&gt;U28,W28&gt;X28,Y28&lt;0,AND(B28&gt;0,G28=0),AND(C28&gt;0,I28=0)),"ERROR",IF(AND(D28&gt;0,Y28&lt;($B$2*D28/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B28&lt;C28,B28&lt;0,C28&lt;0,D28&lt;0,E28&lt;0,E28&gt;J28,T28&gt;U28,W28&gt;X28,AND(B28&gt;0,G28=0),AND(C28&gt;0,I28=0)),"ERROR",IF(AND(D28&gt;0,Y28&lt;($B$2*D28/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v/>
       </c>
       <c r="W29">
-        <f>MAX(0,$B$2-P29)+SUM($G$26:G29)</f>
+        <f>$B$2*Q29/100+SUM($G$26:G29)</f>
         <v/>
       </c>
       <c r="X29">
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="Z29">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B29&lt;C29,B29&lt;0,C29&lt;0,D29&lt;0,E29&lt;0,E29&gt;J29,T29&gt;U29,W29&gt;X29,Y29&lt;0,AND(B29&gt;0,G29=0),AND(C29&gt;0,I29=0)),"ERROR",IF(AND(D29&gt;0,Y29&lt;($B$2*D29/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B29&lt;C29,B29&lt;0,C29&lt;0,D29&lt;0,E29&lt;0,E29&gt;J29,T29&gt;U29,W29&gt;X29,AND(B29&gt;0,G29=0),AND(C29&gt;0,I29=0)),"ERROR",IF(AND(D29&gt;0,Y29&lt;($B$2*D29/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
         <v/>
       </c>
       <c r="W30">
-        <f>MAX(0,$B$2-P30)+SUM($G$26:G30)</f>
+        <f>$B$2*Q30/100+SUM($G$26:G30)</f>
         <v/>
       </c>
       <c r="X30">
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="Z30">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B30&lt;C30,B30&lt;0,C30&lt;0,D30&lt;0,E30&lt;0,E30&gt;J30,T30&gt;U30,W30&gt;X30,Y30&lt;0,AND(B30&gt;0,G30=0),AND(C30&gt;0,I30=0)),"ERROR",IF(AND(D30&gt;0,Y30&lt;($B$2*D30/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B30&lt;C30,B30&lt;0,C30&lt;0,D30&lt;0,E30&lt;0,E30&gt;J30,T30&gt;U30,W30&gt;X30,AND(B30&gt;0,G30=0),AND(C30&gt;0,I30=0)),"ERROR",IF(AND(D30&gt;0,Y30&lt;($B$2*D30/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         <v/>
       </c>
       <c r="W35">
-        <f>MAX(0,$B$2-P35)+SUM($G$35:G35)</f>
+        <f>$B$2*Q35/100+SUM($G$35:G35)</f>
         <v/>
       </c>
       <c r="X35">
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="Z35">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B35&lt;C35,B35&lt;0,C35&lt;0,D35&lt;0,E35&lt;0,E35&gt;J35,T35&gt;U35,W35&gt;X35,Y35&lt;0,AND(B35&gt;0,G35=0),AND(C35&gt;0,I35=0)),"ERROR",IF(AND(D35&gt;0,Y35&lt;($B$2*D35/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B35&lt;C35,B35&lt;0,C35&lt;0,D35&lt;0,E35&lt;0,E35&gt;J35,T35&gt;U35,W35&gt;X35,AND(B35&gt;0,G35=0),AND(C35&gt;0,I35=0)),"ERROR",IF(AND(D35&gt;0,Y35&lt;($B$2*D35/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
         <v/>
       </c>
       <c r="W36">
-        <f>MAX(0,$B$2-P36)+SUM($G$35:G36)</f>
+        <f>$B$2*Q36/100+SUM($G$35:G36)</f>
         <v/>
       </c>
       <c r="X36">
@@ -1826,7 +1826,7 @@
         <v/>
       </c>
       <c r="Z36">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B36&lt;C36,B36&lt;0,C36&lt;0,D36&lt;0,E36&lt;0,E36&gt;J36,T36&gt;U36,W36&gt;X36,Y36&lt;0,AND(B36&gt;0,G36=0),AND(C36&gt;0,I36=0)),"ERROR",IF(AND(D36&gt;0,Y36&lt;($B$2*D36/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B36&lt;C36,B36&lt;0,C36&lt;0,D36&lt;0,E36&lt;0,E36&gt;J36,T36&gt;U36,W36&gt;X36,AND(B36&gt;0,G36=0),AND(C36&gt;0,I36=0)),"ERROR",IF(AND(D36&gt;0,Y36&lt;($B$2*D36/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v/>
       </c>
       <c r="W37">
-        <f>MAX(0,$B$2-P37)+SUM($G$35:G37)</f>
+        <f>$B$2*Q37/100+SUM($G$35:G37)</f>
         <v/>
       </c>
       <c r="X37">
@@ -1932,7 +1932,7 @@
         <v/>
       </c>
       <c r="Z37">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B37&lt;C37,B37&lt;0,C37&lt;0,D37&lt;0,E37&lt;0,E37&gt;J37,T37&gt;U37,W37&gt;X37,Y37&lt;0,AND(B37&gt;0,G37=0),AND(C37&gt;0,I37=0)),"ERROR",IF(AND(D37&gt;0,Y37&lt;($B$2*D37/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B37&lt;C37,B37&lt;0,C37&lt;0,D37&lt;0,E37&lt;0,E37&gt;J37,T37&gt;U37,W37&gt;X37,AND(B37&gt;0,G37=0),AND(C37&gt;0,I37=0)),"ERROR",IF(AND(D37&gt;0,Y37&lt;($B$2*D37/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
         <v/>
       </c>
       <c r="W38">
-        <f>MAX(0,$B$2-P38)+SUM($G$35:G38)</f>
+        <f>$B$2*Q38/100+SUM($G$35:G38)</f>
         <v/>
       </c>
       <c r="X38">
@@ -2038,7 +2038,7 @@
         <v/>
       </c>
       <c r="Z38">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B38&lt;C38,B38&lt;0,C38&lt;0,D38&lt;0,E38&lt;0,E38&gt;J38,T38&gt;U38,W38&gt;X38,Y38&lt;0,AND(B38&gt;0,G38=0),AND(C38&gt;0,I38=0)),"ERROR",IF(AND(D38&gt;0,Y38&lt;($B$2*D38/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B38&lt;C38,B38&lt;0,C38&lt;0,D38&lt;0,E38&lt;0,E38&gt;J38,T38&gt;U38,W38&gt;X38,AND(B38&gt;0,G38=0),AND(C38&gt;0,I38=0)),"ERROR",IF(AND(D38&gt;0,Y38&lt;($B$2*D38/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v/>
       </c>
       <c r="W39">
-        <f>MAX(0,$B$2-P39)+SUM($G$35:G39)</f>
+        <f>$B$2*Q39/100+SUM($G$35:G39)</f>
         <v/>
       </c>
       <c r="X39">
@@ -2144,7 +2144,7 @@
         <v/>
       </c>
       <c r="Z39">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B39&lt;C39,B39&lt;0,C39&lt;0,D39&lt;0,E39&lt;0,E39&gt;J39,T39&gt;U39,W39&gt;X39,Y39&lt;0,AND(B39&gt;0,G39=0),AND(C39&gt;0,I39=0)),"ERROR",IF(AND(D39&gt;0,Y39&lt;($B$2*D39/100)),"WARNING","OK")))</f>
+        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B39&lt;C39,B39&lt;0,C39&lt;0,D39&lt;0,E39&lt;0,E39&gt;J39,T39&gt;U39,W39&gt;X39,AND(B39&gt;0,G39=0),AND(C39&gt;0,I39=0)),"ERROR",IF(AND(D39&gt;0,Y39&lt;($B$2*D39/100)),"WARNING","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2315,7 +2315,7 @@
         <v>60</v>
       </c>
       <c r="D2">
-        <f>IF(B2=C2,"PASS","FAIL")</f>
+        <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <f>IF(B3=C3,"PASS","FAIL")</f>
+        <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
         <v>165</v>
       </c>
       <c r="D4">
-        <f>IF(B4=C4,"PASS","FAIL")</f>
+        <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>175</v>
       </c>
       <c r="D5">
-        <f>IF(B5=C5,"PASS","FAIL")</f>
+        <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <f>IF(B6=C6,"PASS","FAIL")</f>
+        <f>IF(ABS(B6-C6)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>60</v>
       </c>
       <c r="D7">
-        <f>IF(B7=C7,"PASS","FAIL")</f>
+        <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <f>IF(B8=C8,"PASS","FAIL")</f>
+        <f>IF(ABS(B8-C8)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
         <v>165</v>
       </c>
       <c r="D9">
-        <f>IF(B9=C9,"PASS","FAIL")</f>
+        <f>IF(ABS(B9-C9)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
         <v>175</v>
       </c>
       <c r="D10">
-        <f>IF(B10=C10,"PASS","FAIL")</f>
+        <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2477,7 +2477,491 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <f>IF(B11=C11,"PASS","FAIL")</f>
+        <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Down L1 Rounded Main</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>Calculator!W26</f>
+        <v/>
+      </c>
+      <c r="C12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D12">
+        <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Down L1 Rounded Opp</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>Calculator!X26</f>
+        <v/>
+      </c>
+      <c r="C13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D13">
+        <f>IF(ABS(B13-C13)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Down L1 Rounded Skew</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>Calculator!Y26</f>
+        <v/>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>IF(ABS(B14-C14)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Down L1 Status</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>Calculator!Z26</f>
+        <v/>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D15">
+        <f>IF(B15=C15,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Down L2 Rounded Main</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>Calculator!W27</f>
+        <v/>
+      </c>
+      <c r="C16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D16">
+        <f>IF(ABS(B16-C16)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Down L2 Rounded Opp</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>Calculator!X27</f>
+        <v/>
+      </c>
+      <c r="C17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D17">
+        <f>IF(ABS(B17-C17)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Down L2 Rounded Skew</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>Calculator!Y27</f>
+        <v/>
+      </c>
+      <c r="C18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D18">
+        <f>IF(ABS(B18-C18)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Down L2 Status</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>Calculator!Z27</f>
+        <v/>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D19">
+        <f>IF(B19=C19,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Down Final Rounded Main</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>Calculator!W30</f>
+        <v/>
+      </c>
+      <c r="C20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D20">
+        <f>IF(ABS(B20-C20)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Down Final Rounded Opp</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>Calculator!X30</f>
+        <v/>
+      </c>
+      <c r="C21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D21">
+        <f>IF(ABS(B21-C21)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Down Final Rounded Skew</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>Calculator!Y30</f>
+        <v/>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22">
+        <f>IF(ABS(B22-C22)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Down Final Status</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>Calculator!Z30</f>
+        <v/>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D23">
+        <f>IF(B23=C23,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Up L1 Rounded Main</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>Calculator!W35</f>
+        <v/>
+      </c>
+      <c r="C24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D24">
+        <f>IF(ABS(B24-C24)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Up L1 Rounded Opp</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>Calculator!X35</f>
+        <v/>
+      </c>
+      <c r="C25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D25">
+        <f>IF(ABS(B25-C25)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Up L1 Rounded Skew</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>Calculator!Y35</f>
+        <v/>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>IF(ABS(B26-C26)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Up L1 Status</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>Calculator!Z35</f>
+        <v/>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D27">
+        <f>IF(B27=C27,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Up L2 Rounded Main</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>Calculator!W36</f>
+        <v/>
+      </c>
+      <c r="C28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D28">
+        <f>IF(ABS(B28-C28)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Up L2 Rounded Opp</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>Calculator!X36</f>
+        <v/>
+      </c>
+      <c r="C29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D29">
+        <f>IF(ABS(B29-C29)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Up L2 Rounded Skew</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>Calculator!Y36</f>
+        <v/>
+      </c>
+      <c r="C30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D30">
+        <f>IF(ABS(B30-C30)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Up L2 Status</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>Calculator!Z36</f>
+        <v/>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D31">
+        <f>IF(B31=C31,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Up Final Rounded Main</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>Calculator!W39</f>
+        <v/>
+      </c>
+      <c r="C32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D32">
+        <f>IF(ABS(B32-C32)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Up Final Rounded Opp</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>Calculator!X39</f>
+        <v/>
+      </c>
+      <c r="C33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D33">
+        <f>IF(ABS(B33-C33)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Up Final Rounded Skew</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>Calculator!Y39</f>
+        <v/>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34">
+        <f>IF(ABS(B34-C34)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Up Final Status</t>
+        </is>
+      </c>
+      <c r="B35">
+        <f>Calculator!Z39</f>
+        <v/>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D35">
+        <f>IF(B35=C35,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Summary Final Rounded Status</t>
+        </is>
+      </c>
+      <c r="B36">
+        <f>Calculator!B51</f>
+        <v/>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D36">
+        <f>IF(B36=C36,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Summary Final System Status</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>Calculator!B52</f>
+        <v/>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D37">
+        <f>IF(B37=C37,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="E26">
-        <f>E18</f>
+        <f>IF(E18="","",E18)</f>
         <v/>
       </c>
       <c r="F26">
@@ -1073,7 +1073,7 @@
         <v/>
       </c>
       <c r="E27">
-        <f>E19</f>
+        <f>IF(E19="","",E19)</f>
         <v/>
       </c>
       <c r="F27">
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="E28">
-        <f>E20</f>
+        <f>IF(E20="","",E20)</f>
         <v/>
       </c>
       <c r="F28">
@@ -1285,7 +1285,7 @@
         <v/>
       </c>
       <c r="E29">
-        <f>E21</f>
+        <f>IF(E21="","",E21)</f>
         <v/>
       </c>
       <c r="F29">
@@ -1391,7 +1391,7 @@
         <v/>
       </c>
       <c r="E30">
-        <f>E22</f>
+        <f>IF(E22="","",E22)</f>
         <v/>
       </c>
       <c r="F30">
@@ -1636,7 +1636,7 @@
         <v/>
       </c>
       <c r="E35">
-        <f>E18</f>
+        <f>IF(E18="","",E18)</f>
         <v/>
       </c>
       <c r="F35">
@@ -1742,7 +1742,7 @@
         <v/>
       </c>
       <c r="E36">
-        <f>E19</f>
+        <f>IF(E19="","",E19)</f>
         <v/>
       </c>
       <c r="F36">
@@ -1848,7 +1848,7 @@
         <v/>
       </c>
       <c r="E37">
-        <f>E20</f>
+        <f>IF(E20="","",E20)</f>
         <v/>
       </c>
       <c r="F37">
@@ -1954,7 +1954,7 @@
         <v/>
       </c>
       <c r="E38">
-        <f>E21</f>
+        <f>IF(E21="","",E21)</f>
         <v/>
       </c>
       <c r="F38">
@@ -2060,7 +2060,7 @@
         <v/>
       </c>
       <c r="E39">
-        <f>E22</f>
+        <f>IF(E22="","",E22)</f>
         <v/>
       </c>
       <c r="F39">
@@ -2276,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,6 +2962,66 @@
       </c>
       <c r="D37">
         <f>IF(B37=C37,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Empty ManualClose uses AutoClose</t>
+        </is>
+      </c>
+      <c r="B38">
+        <f>IF(AND(ABS(Calculator!N26-Calculator!M26)&lt;0.000001,ABS(Calculator!N27-Calculator!M27)&lt;0.000001,ABS(Calculator!N35-Calculator!M35)&lt;0.000001),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D38">
+        <f>IF(B38=C38,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ManualClose override works</t>
+        </is>
+      </c>
+      <c r="B39">
+        <f>IF(AND(MIN(Calculator!J26,IF(50="",Calculator!M26,50))=50,MIN(Calculator!J35,IF(50="",Calculator!M35,50))=50),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D39">
+        <f>IF(B39=C39,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Empty ManualClose is blank not zero</t>
+        </is>
+      </c>
+      <c r="B40">
+        <f>IF(AND(Calculator!E26="",Calculator!E27="",Calculator!E28="",Calculator!E35="",Calculator!E36="",Calculator!E37=""),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D40">
+        <f>IF(B40=C40,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -1051,7 +1051,7 @@
         <v/>
       </c>
       <c r="Z26">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B26&lt;C26,B26&lt;0,C26&lt;0,D26&lt;0,E26&lt;0,E26&gt;J26,T26&gt;U26,W26&gt;X26,AND(B26&gt;0,G26=0),AND(C26&gt;0,I26=0)),"ERROR",IF(AND(D26&gt;0,Y26&lt;($B$2*D26/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B26&lt;C26,"ERROR",IF(AND(E26&lt;&gt;"",E26&gt;J26),"ERROR",IF(T26&gt;U26,"ERROR",IF(W26&gt;X26,"ERROR",IF(AND(B26&gt;0,G26=0),"ERROR",IF(AND(C26&gt;0,I26=0),"ERROR",IF(AND(D26&gt;0,Y26&lt;($B$2*D26/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v/>
       </c>
       <c r="Z27">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B27&lt;C27,B27&lt;0,C27&lt;0,D27&lt;0,E27&lt;0,E27&gt;J27,T27&gt;U27,W27&gt;X27,AND(B27&gt;0,G27=0),AND(C27&gt;0,I27=0)),"ERROR",IF(AND(D27&gt;0,Y27&lt;($B$2*D27/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B27&lt;C27,"ERROR",IF(AND(E27&lt;&gt;"",E27&gt;J27),"ERROR",IF(T27&gt;U27,"ERROR",IF(W27&gt;X27,"ERROR",IF(AND(B27&gt;0,G27=0),"ERROR",IF(AND(C27&gt;0,I27=0),"ERROR",IF(AND(D27&gt;0,Y27&lt;($B$2*D27/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="Z28">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B28&lt;C28,B28&lt;0,C28&lt;0,D28&lt;0,E28&lt;0,E28&gt;J28,T28&gt;U28,W28&gt;X28,AND(B28&gt;0,G28=0),AND(C28&gt;0,I28=0)),"ERROR",IF(AND(D28&gt;0,Y28&lt;($B$2*D28/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B28&lt;C28,"ERROR",IF(AND(E28&lt;&gt;"",E28&gt;J28),"ERROR",IF(T28&gt;U28,"ERROR",IF(W28&gt;X28,"ERROR",IF(AND(B28&gt;0,G28=0),"ERROR",IF(AND(C28&gt;0,I28=0),"ERROR",IF(AND(D28&gt;0,Y28&lt;($B$2*D28/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="Z29">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B29&lt;C29,B29&lt;0,C29&lt;0,D29&lt;0,E29&lt;0,E29&gt;J29,T29&gt;U29,W29&gt;X29,AND(B29&gt;0,G29=0),AND(C29&gt;0,I29=0)),"ERROR",IF(AND(D29&gt;0,Y29&lt;($B$2*D29/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B29&lt;C29,"ERROR",IF(AND(E29&lt;&gt;"",E29&gt;J29),"ERROR",IF(T29&gt;U29,"ERROR",IF(W29&gt;X29,"ERROR",IF(AND(B29&gt;0,G29=0),"ERROR",IF(AND(C29&gt;0,I29=0),"ERROR",IF(AND(D29&gt;0,Y29&lt;($B$2*D29/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="Z30">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B30&lt;C30,B30&lt;0,C30&lt;0,D30&lt;0,E30&lt;0,E30&gt;J30,T30&gt;U30,W30&gt;X30,AND(B30&gt;0,G30=0),AND(C30&gt;0,I30=0)),"ERROR",IF(AND(D30&gt;0,Y30&lt;($B$2*D30/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B30&lt;C30,"ERROR",IF(AND(E30&lt;&gt;"",E30&gt;J30),"ERROR",IF(T30&gt;U30,"ERROR",IF(W30&gt;X30,"ERROR",IF(AND(B30&gt;0,G30=0),"ERROR",IF(AND(C30&gt;0,I30=0),"ERROR",IF(AND(D30&gt;0,Y30&lt;($B$2*D30/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="Z35">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B35&lt;C35,B35&lt;0,C35&lt;0,D35&lt;0,E35&lt;0,E35&gt;J35,T35&gt;U35,W35&gt;X35,AND(B35&gt;0,G35=0),AND(C35&gt;0,I35=0)),"ERROR",IF(AND(D35&gt;0,Y35&lt;($B$2*D35/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B35&lt;C35,"ERROR",IF(AND(E35&lt;&gt;"",E35&gt;J35),"ERROR",IF(T35&gt;U35,"ERROR",IF(W35&gt;X35,"ERROR",IF(AND(B35&gt;0,G35=0),"ERROR",IF(AND(C35&gt;0,I35=0),"ERROR",IF(AND(D35&gt;0,Y35&lt;($B$2*D35/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
         <v/>
       </c>
       <c r="Z36">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B36&lt;C36,B36&lt;0,C36&lt;0,D36&lt;0,E36&lt;0,E36&gt;J36,T36&gt;U36,W36&gt;X36,AND(B36&gt;0,G36=0),AND(C36&gt;0,I36=0)),"ERROR",IF(AND(D36&gt;0,Y36&lt;($B$2*D36/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B36&lt;C36,"ERROR",IF(AND(E36&lt;&gt;"",E36&gt;J36),"ERROR",IF(T36&gt;U36,"ERROR",IF(W36&gt;X36,"ERROR",IF(AND(B36&gt;0,G36=0),"ERROR",IF(AND(C36&gt;0,I36=0),"ERROR",IF(AND(D36&gt;0,Y36&lt;($B$2*D36/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
         <v/>
       </c>
       <c r="Z37">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B37&lt;C37,B37&lt;0,C37&lt;0,D37&lt;0,E37&lt;0,E37&gt;J37,T37&gt;U37,W37&gt;X37,AND(B37&gt;0,G37=0),AND(C37&gt;0,I37=0)),"ERROR",IF(AND(D37&gt;0,Y37&lt;($B$2*D37/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B37&lt;C37,"ERROR",IF(AND(E37&lt;&gt;"",E37&gt;J37),"ERROR",IF(T37&gt;U37,"ERROR",IF(W37&gt;X37,"ERROR",IF(AND(B37&gt;0,G37=0),"ERROR",IF(AND(C37&gt;0,I37=0),"ERROR",IF(AND(D37&gt;0,Y37&lt;($B$2*D37/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v/>
       </c>
       <c r="Z38">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B38&lt;C38,B38&lt;0,C38&lt;0,D38&lt;0,E38&lt;0,E38&gt;J38,T38&gt;U38,W38&gt;X38,AND(B38&gt;0,G38=0),AND(C38&gt;0,I38=0)),"ERROR",IF(AND(D38&gt;0,Y38&lt;($B$2*D38/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B38&lt;C38,"ERROR",IF(AND(E38&lt;&gt;"",E38&gt;J38),"ERROR",IF(T38&gt;U38,"ERROR",IF(W38&gt;X38,"ERROR",IF(AND(B38&gt;0,G38=0),"ERROR",IF(AND(C38&gt;0,I38=0),"ERROR",IF(AND(D38&gt;0,Y38&lt;($B$2*D38/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
         <v/>
       </c>
       <c r="Z39">
-        <f>IF(COUNTIF($F$2:$F$9,"ERROR*")&gt;0,"ERROR",IF(OR(B39&lt;C39,B39&lt;0,C39&lt;0,D39&lt;0,E39&lt;0,E39&gt;J39,T39&gt;U39,W39&gt;X39,AND(B39&gt;0,G39=0),AND(C39&gt;0,I39=0)),"ERROR",IF(AND(D39&gt;0,Y39&lt;($B$2*D39/100)),"WARNING","OK")))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B39&lt;C39,"ERROR",IF(AND(E39&lt;&gt;"",E39&gt;J39),"ERROR",IF(T39&gt;U39,"ERROR",IF(W39&gt;X39,"ERROR",IF(AND(B39&gt;0,G39=0),"ERROR",IF(AND(C39&gt;0,I39=0),"ERROR",IF(AND(D39&gt;0,Y39&lt;($B$2*D39/100)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2928,11 +2928,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Summary Final Rounded Status</t>
+          <t>Down Level1 Status</t>
         </is>
       </c>
       <c r="B36">
-        <f>Calculator!B51</f>
+        <f>Calculator!Z26</f>
         <v/>
       </c>
       <c r="C36" t="inlineStr">
@@ -2948,11 +2948,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Summary Final System Status</t>
+          <t>Down Level2 Status</t>
         </is>
       </c>
       <c r="B37">
-        <f>Calculator!B52</f>
+        <f>Calculator!Z27</f>
         <v/>
       </c>
       <c r="C37" t="inlineStr">
@@ -2968,16 +2968,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Empty ManualClose uses AutoClose</t>
+          <t>Down Level5 Status</t>
         </is>
       </c>
       <c r="B38">
-        <f>IF(AND(ABS(Calculator!N26-Calculator!M26)&lt;0.000001,ABS(Calculator!N27-Calculator!M27)&lt;0.000001,ABS(Calculator!N35-Calculator!M35)&lt;0.000001),"PASS","FAIL")</f>
+        <f>Calculator!Z30</f>
         <v/>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D38">
@@ -2988,16 +2988,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ManualClose override works</t>
+          <t>Up Level1 Status</t>
         </is>
       </c>
       <c r="B39">
-        <f>IF(AND(MIN(Calculator!J26,IF(50="",Calculator!M26,50))=50,MIN(Calculator!J35,IF(50="",Calculator!M35,50))=50),"PASS","FAIL")</f>
+        <f>Calculator!Z35</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D39">
@@ -3008,20 +3008,140 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Empty ManualClose is blank not zero</t>
+          <t>Up Level2 Status</t>
         </is>
       </c>
       <c r="B40">
-        <f>IF(AND(Calculator!E26="",Calculator!E27="",Calculator!E28="",Calculator!E35="",Calculator!E36="",Calculator!E37=""),"PASS","FAIL")</f>
+        <f>Calculator!Z36</f>
         <v/>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D40">
         <f>IF(B40=C40,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Up Level5 Status</t>
+        </is>
+      </c>
+      <c r="B41">
+        <f>Calculator!Z39</f>
+        <v/>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D41">
+        <f>IF(B41=C41,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Summary Final Rounded Status</t>
+        </is>
+      </c>
+      <c r="B42">
+        <f>Calculator!B51</f>
+        <v/>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D42">
+        <f>IF(B42=C42,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Summary Final System Status</t>
+        </is>
+      </c>
+      <c r="B43">
+        <f>Calculator!B52</f>
+        <v/>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D43">
+        <f>IF(B43=C43,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Empty ManualClose uses AutoClose</t>
+        </is>
+      </c>
+      <c r="B44">
+        <f>IF(AND(ABS(Calculator!N26-Calculator!M26)&lt;0.000001,ABS(Calculator!N27-Calculator!M27)&lt;0.000001,ABS(Calculator!N35-Calculator!M35)&lt;0.000001),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D44">
+        <f>IF(B44=C44,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ManualClose override works</t>
+        </is>
+      </c>
+      <c r="B45">
+        <f>IF(AND(MIN(Calculator!J26,IF(50="",Calculator!M26,50))=50,MIN(Calculator!J35,IF(50="",Calculator!M35,50))=50),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D45">
+        <f>IF(B45=C45,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Empty ManualClose is blank not zero</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>IF(AND(Calculator!E26="",Calculator!E27="",Calculator!E28="",Calculator!E35="",Calculator!E36="",Calculator!E37=""),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D46">
+        <f>IF(B46=C46,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -1051,7 +1051,7 @@
         <v/>
       </c>
       <c r="Z26">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B26&lt;C26,"ERROR",IF(AND(E26&lt;&gt;"",E26&gt;J26),"ERROR",IF(T26&gt;U26,"ERROR",IF(W26&gt;X26,"ERROR",IF(AND(B26&gt;0,G26=0),"ERROR",IF(AND(C26&gt;0,I26=0),"ERROR",IF(AND(D26&gt;0,Y26&lt;($B$2*D26/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B26&lt;C26,"ERROR",IF(AND(E26&lt;&gt;"",E26&gt;J26),"ERROR",IF(T26&gt;U26,"ERROR",IF(W26&gt;X26,"ERROR",IF(AND(B26&gt;0,G26=0),"ERROR",IF(AND(C26&gt;0,I26=0),"ERROR",IF(AND(D26&gt;0,ROUND(Y26,6)&lt;ROUND($B$2*D26/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v/>
       </c>
       <c r="Z27">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B27&lt;C27,"ERROR",IF(AND(E27&lt;&gt;"",E27&gt;J27),"ERROR",IF(T27&gt;U27,"ERROR",IF(W27&gt;X27,"ERROR",IF(AND(B27&gt;0,G27=0),"ERROR",IF(AND(C27&gt;0,I27=0),"ERROR",IF(AND(D27&gt;0,Y27&lt;($B$2*D27/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B27&lt;C27,"ERROR",IF(AND(E27&lt;&gt;"",E27&gt;J27),"ERROR",IF(T27&gt;U27,"ERROR",IF(W27&gt;X27,"ERROR",IF(AND(B27&gt;0,G27=0),"ERROR",IF(AND(C27&gt;0,I27=0),"ERROR",IF(AND(D27&gt;0,ROUND(Y27,6)&lt;ROUND($B$2*D27/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="Z28">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B28&lt;C28,"ERROR",IF(AND(E28&lt;&gt;"",E28&gt;J28),"ERROR",IF(T28&gt;U28,"ERROR",IF(W28&gt;X28,"ERROR",IF(AND(B28&gt;0,G28=0),"ERROR",IF(AND(C28&gt;0,I28=0),"ERROR",IF(AND(D28&gt;0,Y28&lt;($B$2*D28/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B28&lt;C28,"ERROR",IF(AND(E28&lt;&gt;"",E28&gt;J28),"ERROR",IF(T28&gt;U28,"ERROR",IF(W28&gt;X28,"ERROR",IF(AND(B28&gt;0,G28=0),"ERROR",IF(AND(C28&gt;0,I28=0),"ERROR",IF(AND(D28&gt;0,ROUND(Y28,6)&lt;ROUND($B$2*D28/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="Z29">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B29&lt;C29,"ERROR",IF(AND(E29&lt;&gt;"",E29&gt;J29),"ERROR",IF(T29&gt;U29,"ERROR",IF(W29&gt;X29,"ERROR",IF(AND(B29&gt;0,G29=0),"ERROR",IF(AND(C29&gt;0,I29=0),"ERROR",IF(AND(D29&gt;0,Y29&lt;($B$2*D29/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B29&lt;C29,"ERROR",IF(AND(E29&lt;&gt;"",E29&gt;J29),"ERROR",IF(T29&gt;U29,"ERROR",IF(W29&gt;X29,"ERROR",IF(AND(B29&gt;0,G29=0),"ERROR",IF(AND(C29&gt;0,I29=0),"ERROR",IF(AND(D29&gt;0,ROUND(Y29,6)&lt;ROUND($B$2*D29/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="Z30">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B30&lt;C30,"ERROR",IF(AND(E30&lt;&gt;"",E30&gt;J30),"ERROR",IF(T30&gt;U30,"ERROR",IF(W30&gt;X30,"ERROR",IF(AND(B30&gt;0,G30=0),"ERROR",IF(AND(C30&gt;0,I30=0),"ERROR",IF(AND(D30&gt;0,Y30&lt;($B$2*D30/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B30&lt;C30,"ERROR",IF(AND(E30&lt;&gt;"",E30&gt;J30),"ERROR",IF(T30&gt;U30,"ERROR",IF(W30&gt;X30,"ERROR",IF(AND(B30&gt;0,G30=0),"ERROR",IF(AND(C30&gt;0,I30=0),"ERROR",IF(AND(D30&gt;0,ROUND(Y30,6)&lt;ROUND($B$2*D30/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="Z35">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B35&lt;C35,"ERROR",IF(AND(E35&lt;&gt;"",E35&gt;J35),"ERROR",IF(T35&gt;U35,"ERROR",IF(W35&gt;X35,"ERROR",IF(AND(B35&gt;0,G35=0),"ERROR",IF(AND(C35&gt;0,I35=0),"ERROR",IF(AND(D35&gt;0,Y35&lt;($B$2*D35/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B35&lt;C35,"ERROR",IF(AND(E35&lt;&gt;"",E35&gt;J35),"ERROR",IF(T35&gt;U35,"ERROR",IF(W35&gt;X35,"ERROR",IF(AND(B35&gt;0,G35=0),"ERROR",IF(AND(C35&gt;0,I35=0),"ERROR",IF(AND(D35&gt;0,ROUND(Y35,6)&lt;ROUND($B$2*D35/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
         <v/>
       </c>
       <c r="Z36">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B36&lt;C36,"ERROR",IF(AND(E36&lt;&gt;"",E36&gt;J36),"ERROR",IF(T36&gt;U36,"ERROR",IF(W36&gt;X36,"ERROR",IF(AND(B36&gt;0,G36=0),"ERROR",IF(AND(C36&gt;0,I36=0),"ERROR",IF(AND(D36&gt;0,Y36&lt;($B$2*D36/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B36&lt;C36,"ERROR",IF(AND(E36&lt;&gt;"",E36&gt;J36),"ERROR",IF(T36&gt;U36,"ERROR",IF(W36&gt;X36,"ERROR",IF(AND(B36&gt;0,G36=0),"ERROR",IF(AND(C36&gt;0,I36=0),"ERROR",IF(AND(D36&gt;0,ROUND(Y36,6)&lt;ROUND($B$2*D36/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
         <v/>
       </c>
       <c r="Z37">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B37&lt;C37,"ERROR",IF(AND(E37&lt;&gt;"",E37&gt;J37),"ERROR",IF(T37&gt;U37,"ERROR",IF(W37&gt;X37,"ERROR",IF(AND(B37&gt;0,G37=0),"ERROR",IF(AND(C37&gt;0,I37=0),"ERROR",IF(AND(D37&gt;0,Y37&lt;($B$2*D37/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B37&lt;C37,"ERROR",IF(AND(E37&lt;&gt;"",E37&gt;J37),"ERROR",IF(T37&gt;U37,"ERROR",IF(W37&gt;X37,"ERROR",IF(AND(B37&gt;0,G37=0),"ERROR",IF(AND(C37&gt;0,I37=0),"ERROR",IF(AND(D37&gt;0,ROUND(Y37,6)&lt;ROUND($B$2*D37/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v/>
       </c>
       <c r="Z38">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B38&lt;C38,"ERROR",IF(AND(E38&lt;&gt;"",E38&gt;J38),"ERROR",IF(T38&gt;U38,"ERROR",IF(W38&gt;X38,"ERROR",IF(AND(B38&gt;0,G38=0),"ERROR",IF(AND(C38&gt;0,I38=0),"ERROR",IF(AND(D38&gt;0,Y38&lt;($B$2*D38/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B38&lt;C38,"ERROR",IF(AND(E38&lt;&gt;"",E38&gt;J38),"ERROR",IF(T38&gt;U38,"ERROR",IF(W38&gt;X38,"ERROR",IF(AND(B38&gt;0,G38=0),"ERROR",IF(AND(C38&gt;0,I38=0),"ERROR",IF(AND(D38&gt;0,ROUND(Y38,6)&lt;ROUND($B$2*D38/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
         <v/>
       </c>
       <c r="Z39">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B39&lt;C39,"ERROR",IF(AND(E39&lt;&gt;"",E39&gt;J39),"ERROR",IF(T39&gt;U39,"ERROR",IF(W39&gt;X39,"ERROR",IF(AND(B39&gt;0,G39=0),"ERROR",IF(AND(C39&gt;0,I39=0),"ERROR",IF(AND(D39&gt;0,Y39&lt;($B$2*D39/100)),"WARNING","OK"))))))))</f>
+        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B39&lt;C39,"ERROR",IF(AND(E39&lt;&gt;"",E39&gt;J39),"ERROR",IF(T39&gt;U39,"ERROR",IF(W39&gt;X39,"ERROR",IF(AND(B39&gt;0,G39=0),"ERROR",IF(AND(C39&gt;0,I39=0),"ERROR",IF(AND(D39&gt;0,ROUND(Y39,6)&lt;ROUND($B$2*D39/100,6)),"WARNING","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2968,11 +2968,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Down Level5 Status</t>
+          <t>Down L4 Status</t>
         </is>
       </c>
       <c r="B38">
-        <f>Calculator!Z30</f>
+        <f>Calculator!Z29</f>
         <v/>
       </c>
       <c r="C38" t="inlineStr">
@@ -2988,11 +2988,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Up Level1 Status</t>
+          <t>Down Level5 Status</t>
         </is>
       </c>
       <c r="B39">
-        <f>Calculator!Z35</f>
+        <f>Calculator!Z30</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
@@ -3008,11 +3008,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Up Level2 Status</t>
+          <t>Up Level1 Status</t>
         </is>
       </c>
       <c r="B40">
-        <f>Calculator!Z36</f>
+        <f>Calculator!Z35</f>
         <v/>
       </c>
       <c r="C40" t="inlineStr">
@@ -3028,11 +3028,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Up Level5 Status</t>
+          <t>Up Level2 Status</t>
         </is>
       </c>
       <c r="B41">
-        <f>Calculator!Z39</f>
+        <f>Calculator!Z36</f>
         <v/>
       </c>
       <c r="C41" t="inlineStr">
@@ -3048,11 +3048,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Summary Final Rounded Status</t>
+          <t>Up L4 Status</t>
         </is>
       </c>
       <c r="B42">
-        <f>Calculator!B51</f>
+        <f>Calculator!Z38</f>
         <v/>
       </c>
       <c r="C42" t="inlineStr">
@@ -3068,11 +3068,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Summary Final System Status</t>
+          <t>Up Level5 Status</t>
         </is>
       </c>
       <c r="B43">
-        <f>Calculator!B52</f>
+        <f>Calculator!Z39</f>
         <v/>
       </c>
       <c r="C43" t="inlineStr">
@@ -3088,16 +3088,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Empty ManualClose uses AutoClose</t>
+          <t>Summary Final Rounded Status</t>
         </is>
       </c>
       <c r="B44">
-        <f>IF(AND(ABS(Calculator!N26-Calculator!M26)&lt;0.000001,ABS(Calculator!N27-Calculator!M27)&lt;0.000001,ABS(Calculator!N35-Calculator!M35)&lt;0.000001),"PASS","FAIL")</f>
+        <f>Calculator!B51</f>
         <v/>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D44">
@@ -3108,16 +3108,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ManualClose override works</t>
+          <t>Summary Final System Status</t>
         </is>
       </c>
       <c r="B45">
-        <f>IF(AND(MIN(Calculator!J26,IF(50="",Calculator!M26,50))=50,MIN(Calculator!J35,IF(50="",Calculator!M35,50))=50),"PASS","FAIL")</f>
+        <f>Calculator!B52</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D45">
@@ -3128,20 +3128,80 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Empty ManualClose is blank not zero</t>
+          <t>Summary Final Status</t>
         </is>
       </c>
       <c r="B46">
-        <f>IF(AND(Calculator!E26="",Calculator!E27="",Calculator!E28="",Calculator!E35="",Calculator!E36="",Calculator!E37=""),"PASS","FAIL")</f>
+        <f>Calculator!B52</f>
         <v/>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D46">
         <f>IF(B46=C46,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Empty ManualClose uses AutoClose</t>
+        </is>
+      </c>
+      <c r="B47">
+        <f>IF(AND(ABS(Calculator!N26-Calculator!M26)&lt;0.000001,ABS(Calculator!N27-Calculator!M27)&lt;0.000001,ABS(Calculator!N35-Calculator!M35)&lt;0.000001),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D47">
+        <f>IF(B47=C47,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ManualClose override works</t>
+        </is>
+      </c>
+      <c r="B48">
+        <f>IF(AND(MIN(Calculator!J26,IF(50="",Calculator!M26,50))=50,MIN(Calculator!J35,IF(50="",Calculator!M35,50))=50),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D48">
+        <f>IF(B48=C48,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Empty ManualClose is blank not zero</t>
+        </is>
+      </c>
+      <c r="B49">
+        <f>IF(AND(Calculator!E26="",Calculator!E27="",Calculator!E28="",Calculator!E35="",Calculator!E36="",Calculator!E37=""),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D49">
+        <f>IF(B49=C49,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tests" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Manual" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="README" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="HumanSummary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tests" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Manual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z52"/>
+  <dimension ref="A1:Z61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2262,6 +2263,550 @@
       </c>
       <c r="B52">
         <f>IF(B6="DOWN",IF(COUNTIF(Z26:Z30,"ERROR")&gt;0,"ERROR",IF(COUNTIF(Z26:Z30,"WARNING")&gt;0,"WARNING","OK")),IF(COUNTIF(Z35:Z39,"ERROR")&gt;0,"ERROR",IF(COUNTIF(Z35:Z39,"WARNING")&gt;0,"WARNING","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>HUMAN-READABLE LEVEL SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Action Big</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Big %</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Big Lot</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Action Small</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Small %</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Small Lot</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Close Action</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Close %</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Close Lot</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Start Remaining %</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Start Remaining Lot</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Total Main %</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Total Opposite %</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Skew %</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Main Lot</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Opp Lot</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Skew Lot</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>Human Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <f>A18</f>
+        <v/>
+      </c>
+      <c r="B57">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>IF($B$6="DOWN",B18,B18)</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>IF($B$6="DOWN",G18,G27)</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>IF($B$6="DOWN",C18,C18)</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>IF($B$6="DOWN",I18,I27)</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J57">
+        <f>IF($B$6="DOWN",N18,N27)</f>
+        <v/>
+      </c>
+      <c r="K57">
+        <f>IF($B$6="DOWN",P18,P27)</f>
+        <v/>
+      </c>
+      <c r="L57">
+        <f>IF($B$6="DOWN",Q18,Q27)</f>
+        <v/>
+      </c>
+      <c r="M57">
+        <f>$B$2*L57/100</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>IF($B$6="DOWN",T18,T27)</f>
+        <v/>
+      </c>
+      <c r="O57">
+        <f>IF($B$6="DOWN",U18,U27)</f>
+        <v/>
+      </c>
+      <c r="P57">
+        <f>IF($B$6="DOWN",V18,V27)</f>
+        <v/>
+      </c>
+      <c r="Q57">
+        <f>IF($B$6="DOWN",W18,W27)</f>
+        <v/>
+      </c>
+      <c r="R57">
+        <f>IF($B$6="DOWN",X18,X27)</f>
+        <v/>
+      </c>
+      <c r="S57">
+        <f>IF($B$6="DOWN",Y18,Y27)</f>
+        <v/>
+      </c>
+      <c r="T57">
+        <f>IF($B$6="DOWN",Z18,Z27)</f>
+        <v/>
+      </c>
+      <c r="U57">
+        <f>CONCAT("Level ",A57,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C57," ",TEXT(E57,"0.00")," lot, ",F57," ",TEXT(H57,"0.00")," lot, ",I57," ",TEXT(K57,"0.00")," lot. Start remaining ",TEXT(M57,"0.00")," lot. Status=",T57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <f>A19</f>
+        <v/>
+      </c>
+      <c r="B58">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>IF($B$6="DOWN",B19,B19)</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>IF($B$6="DOWN",G19,G28)</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>IF($B$6="DOWN",C19,C19)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>IF($B$6="DOWN",I19,I28)</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J58">
+        <f>IF($B$6="DOWN",N19,N28)</f>
+        <v/>
+      </c>
+      <c r="K58">
+        <f>IF($B$6="DOWN",P19,P28)</f>
+        <v/>
+      </c>
+      <c r="L58">
+        <f>IF($B$6="DOWN",Q19,Q28)</f>
+        <v/>
+      </c>
+      <c r="M58">
+        <f>$B$2*L58/100</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>IF($B$6="DOWN",T19,T28)</f>
+        <v/>
+      </c>
+      <c r="O58">
+        <f>IF($B$6="DOWN",U19,U28)</f>
+        <v/>
+      </c>
+      <c r="P58">
+        <f>IF($B$6="DOWN",V19,V28)</f>
+        <v/>
+      </c>
+      <c r="Q58">
+        <f>IF($B$6="DOWN",W19,W28)</f>
+        <v/>
+      </c>
+      <c r="R58">
+        <f>IF($B$6="DOWN",X19,X28)</f>
+        <v/>
+      </c>
+      <c r="S58">
+        <f>IF($B$6="DOWN",Y19,Y28)</f>
+        <v/>
+      </c>
+      <c r="T58">
+        <f>IF($B$6="DOWN",Z19,Z28)</f>
+        <v/>
+      </c>
+      <c r="U58">
+        <f>CONCAT("Level ",A58,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C58," ",TEXT(E58,"0.00")," lot, ",F58," ",TEXT(H58,"0.00")," lot, ",I58," ",TEXT(K58,"0.00")," lot. Start remaining ",TEXT(M58,"0.00")," lot. Status=",T58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <f>A20</f>
+        <v/>
+      </c>
+      <c r="B59">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>IF($B$6="DOWN",B20,B20)</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>IF($B$6="DOWN",G20,G29)</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>IF($B$6="DOWN",C20,C20)</f>
+        <v/>
+      </c>
+      <c r="H59">
+        <f>IF($B$6="DOWN",I20,I29)</f>
+        <v/>
+      </c>
+      <c r="I59">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J59">
+        <f>IF($B$6="DOWN",N20,N29)</f>
+        <v/>
+      </c>
+      <c r="K59">
+        <f>IF($B$6="DOWN",P20,P29)</f>
+        <v/>
+      </c>
+      <c r="L59">
+        <f>IF($B$6="DOWN",Q20,Q29)</f>
+        <v/>
+      </c>
+      <c r="M59">
+        <f>$B$2*L59/100</f>
+        <v/>
+      </c>
+      <c r="N59">
+        <f>IF($B$6="DOWN",T20,T29)</f>
+        <v/>
+      </c>
+      <c r="O59">
+        <f>IF($B$6="DOWN",U20,U29)</f>
+        <v/>
+      </c>
+      <c r="P59">
+        <f>IF($B$6="DOWN",V20,V29)</f>
+        <v/>
+      </c>
+      <c r="Q59">
+        <f>IF($B$6="DOWN",W20,W29)</f>
+        <v/>
+      </c>
+      <c r="R59">
+        <f>IF($B$6="DOWN",X20,X29)</f>
+        <v/>
+      </c>
+      <c r="S59">
+        <f>IF($B$6="DOWN",Y20,Y29)</f>
+        <v/>
+      </c>
+      <c r="T59">
+        <f>IF($B$6="DOWN",Z20,Z29)</f>
+        <v/>
+      </c>
+      <c r="U59">
+        <f>CONCAT("Level ",A59,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C59," ",TEXT(E59,"0.00")," lot, ",F59," ",TEXT(H59,"0.00")," lot, ",I59," ",TEXT(K59,"0.00")," lot. Start remaining ",TEXT(M59,"0.00")," lot. Status=",T59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <f>A21</f>
+        <v/>
+      </c>
+      <c r="B60">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>IF($B$6="DOWN",B21,B21)</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>IF($B$6="DOWN",G21,G30)</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>IF($B$6="DOWN",C21,C21)</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>IF($B$6="DOWN",I21,I30)</f>
+        <v/>
+      </c>
+      <c r="I60">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J60">
+        <f>IF($B$6="DOWN",N21,N30)</f>
+        <v/>
+      </c>
+      <c r="K60">
+        <f>IF($B$6="DOWN",P21,P30)</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>IF($B$6="DOWN",Q21,Q30)</f>
+        <v/>
+      </c>
+      <c r="M60">
+        <f>$B$2*L60/100</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>IF($B$6="DOWN",T21,T30)</f>
+        <v/>
+      </c>
+      <c r="O60">
+        <f>IF($B$6="DOWN",U21,U30)</f>
+        <v/>
+      </c>
+      <c r="P60">
+        <f>IF($B$6="DOWN",V21,V30)</f>
+        <v/>
+      </c>
+      <c r="Q60">
+        <f>IF($B$6="DOWN",W21,W30)</f>
+        <v/>
+      </c>
+      <c r="R60">
+        <f>IF($B$6="DOWN",X21,X30)</f>
+        <v/>
+      </c>
+      <c r="S60">
+        <f>IF($B$6="DOWN",Y21,Y30)</f>
+        <v/>
+      </c>
+      <c r="T60">
+        <f>IF($B$6="DOWN",Z21,Z30)</f>
+        <v/>
+      </c>
+      <c r="U60">
+        <f>CONCAT("Level ",A60,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C60," ",TEXT(E60,"0.00")," lot, ",F60," ",TEXT(H60,"0.00")," lot, ",I60," ",TEXT(K60,"0.00")," lot. Start remaining ",TEXT(M60,"0.00")," lot. Status=",T60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <f>A22</f>
+        <v/>
+      </c>
+      <c r="B61">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>IF($B$6="DOWN",B22,B22)</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>IF($B$6="DOWN",G22,G31)</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>IF($B$6="DOWN",C22,C22)</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>IF($B$6="DOWN",I22,I31)</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>IF($B$6="DOWN",N22,N31)</f>
+        <v/>
+      </c>
+      <c r="K61">
+        <f>IF($B$6="DOWN",P22,P31)</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>IF($B$6="DOWN",Q22,Q31)</f>
+        <v/>
+      </c>
+      <c r="M61">
+        <f>$B$2*L61/100</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>IF($B$6="DOWN",T22,T31)</f>
+        <v/>
+      </c>
+      <c r="O61">
+        <f>IF($B$6="DOWN",U22,U31)</f>
+        <v/>
+      </c>
+      <c r="P61">
+        <f>IF($B$6="DOWN",V22,V31)</f>
+        <v/>
+      </c>
+      <c r="Q61">
+        <f>IF($B$6="DOWN",W22,W31)</f>
+        <v/>
+      </c>
+      <c r="R61">
+        <f>IF($B$6="DOWN",X22,X31)</f>
+        <v/>
+      </c>
+      <c r="S61">
+        <f>IF($B$6="DOWN",Y22,Y31)</f>
+        <v/>
+      </c>
+      <c r="T61">
+        <f>IF($B$6="DOWN",Z22,Z31)</f>
+        <v/>
+      </c>
+      <c r="U61">
+        <f>CONCAT("Level ",A61,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C61," ",TEXT(E61,"0.00")," lot, ",F61," ",TEXT(H61,"0.00")," lot, ",I61," ",TEXT(K61,"0.00")," lot. Start remaining ",TEXT(M61,"0.00")," lot. Status=",T61)</f>
         <v/>
       </c>
     </row>
@@ -2276,932 +2821,678 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Result</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ИТОГОВЫЙ ЧЕЛОВЕЧЕСКИЙ РАСЧЁТ ВСЕХ УРОВНЕЙ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Down L1 Close%</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>Calculator!N26</f>
-        <v/>
-      </c>
-      <c r="C2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D2">
-        <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Action Big</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Big %</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Big Lot</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Action Small</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Small %</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Small Lot</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Close Action</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Close %</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Close Lot</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Start Remaining %</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Start Remaining Lot</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Total Main %</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Total Opposite %</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Skew %</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Main Lot</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Opp Lot</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Skew Lot</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Human Comment</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Down L2 Close%</t>
-        </is>
+      <c r="A3">
+        <f>Calculator!A57</f>
+        <v/>
       </c>
       <c r="B3">
-        <f>Calculator!N27</f>
-        <v/>
-      </c>
-      <c r="C3" t="n">
-        <v>30</v>
+        <f>Calculator!B57</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>Calculator!C57</f>
+        <v/>
       </c>
       <c r="D3">
-        <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
+        <f>Calculator!D57</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>Calculator!E57</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>Calculator!F57</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>Calculator!G57</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>Calculator!H57</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>Calculator!I57</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>Calculator!J57</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>Calculator!K57</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>Calculator!L57</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>Calculator!M57</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>Calculator!N57</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>Calculator!O57</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>Calculator!P57</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>Calculator!Q57</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>Calculator!R57</f>
+        <v/>
+      </c>
+      <c r="S3">
+        <f>Calculator!S57</f>
+        <v/>
+      </c>
+      <c r="T3">
+        <f>Calculator!T57</f>
+        <v/>
+      </c>
+      <c r="U3">
+        <f>Calculator!U57</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Down Final Main</t>
-        </is>
+      <c r="A4">
+        <f>Calculator!A58</f>
+        <v/>
       </c>
       <c r="B4">
-        <f>Calculator!T30</f>
-        <v/>
-      </c>
-      <c r="C4" t="n">
-        <v>165</v>
+        <f>Calculator!B58</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>Calculator!C58</f>
+        <v/>
       </c>
       <c r="D4">
-        <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
+        <f>Calculator!D58</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>Calculator!E58</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>Calculator!F58</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>Calculator!G58</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>Calculator!H58</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>Calculator!I58</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>Calculator!J58</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>Calculator!K58</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>Calculator!L58</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>Calculator!M58</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>Calculator!N58</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>Calculator!O58</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>Calculator!P58</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>Calculator!Q58</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>Calculator!R58</f>
+        <v/>
+      </c>
+      <c r="S4">
+        <f>Calculator!S58</f>
+        <v/>
+      </c>
+      <c r="T4">
+        <f>Calculator!T58</f>
+        <v/>
+      </c>
+      <c r="U4">
+        <f>Calculator!U58</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Down Final Opp</t>
-        </is>
+      <c r="A5">
+        <f>Calculator!A59</f>
+        <v/>
       </c>
       <c r="B5">
-        <f>Calculator!U30</f>
-        <v/>
-      </c>
-      <c r="C5" t="n">
-        <v>175</v>
+        <f>Calculator!B59</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>Calculator!C59</f>
+        <v/>
       </c>
       <c r="D5">
-        <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
+        <f>Calculator!D59</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>Calculator!E59</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>Calculator!F59</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>Calculator!G59</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>Calculator!H59</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>Calculator!I59</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>Calculator!J59</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>Calculator!K59</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>Calculator!L59</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>Calculator!M59</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>Calculator!N59</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>Calculator!O59</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>Calculator!P59</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>Calculator!Q59</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>Calculator!R59</f>
+        <v/>
+      </c>
+      <c r="S5">
+        <f>Calculator!S59</f>
+        <v/>
+      </c>
+      <c r="T5">
+        <f>Calculator!T59</f>
+        <v/>
+      </c>
+      <c r="U5">
+        <f>Calculator!U59</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Down Final Skew</t>
-        </is>
+      <c r="A6">
+        <f>Calculator!A60</f>
+        <v/>
       </c>
       <c r="B6">
-        <f>Calculator!V30</f>
-        <v/>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
+        <f>Calculator!B60</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>Calculator!C60</f>
+        <v/>
       </c>
       <c r="D6">
-        <f>IF(ABS(B6-C6)&lt;0.000001,"PASS","FAIL")</f>
+        <f>Calculator!D60</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>Calculator!E60</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>Calculator!F60</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>Calculator!G60</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>Calculator!H60</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>Calculator!I60</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>Calculator!J60</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>Calculator!K60</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>Calculator!L60</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>Calculator!M60</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>Calculator!N60</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>Calculator!O60</f>
+        <v/>
+      </c>
+      <c r="P6">
+        <f>Calculator!P60</f>
+        <v/>
+      </c>
+      <c r="Q6">
+        <f>Calculator!Q60</f>
+        <v/>
+      </c>
+      <c r="R6">
+        <f>Calculator!R60</f>
+        <v/>
+      </c>
+      <c r="S6">
+        <f>Calculator!S60</f>
+        <v/>
+      </c>
+      <c r="T6">
+        <f>Calculator!T60</f>
+        <v/>
+      </c>
+      <c r="U6">
+        <f>Calculator!U60</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Up L1 Close%</t>
-        </is>
+      <c r="A7">
+        <f>Calculator!A61</f>
+        <v/>
       </c>
       <c r="B7">
-        <f>Calculator!N35</f>
-        <v/>
-      </c>
-      <c r="C7" t="n">
-        <v>60</v>
+        <f>Calculator!B61</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>Calculator!C61</f>
+        <v/>
       </c>
       <c r="D7">
-        <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Up L2 Close%</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>Calculator!N36</f>
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <f>IF(ABS(B8-C8)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Up Final Main</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>Calculator!T39</f>
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v>165</v>
-      </c>
-      <c r="D9">
-        <f>IF(ABS(B9-C9)&lt;0.000001,"PASS","FAIL")</f>
+        <f>Calculator!D61</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>Calculator!E61</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>Calculator!F61</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>Calculator!G61</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>Calculator!H61</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>Calculator!I61</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>Calculator!J61</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>Calculator!K61</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>Calculator!L61</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>Calculator!M61</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>Calculator!N61</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>Calculator!O61</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>Calculator!P61</f>
+        <v/>
+      </c>
+      <c r="Q7">
+        <f>Calculator!Q61</f>
+        <v/>
+      </c>
+      <c r="R7">
+        <f>Calculator!R61</f>
+        <v/>
+      </c>
+      <c r="S7">
+        <f>Calculator!S61</f>
+        <v/>
+      </c>
+      <c r="T7">
+        <f>Calculator!T61</f>
+        <v/>
+      </c>
+      <c r="U7">
+        <f>Calculator!U61</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Up Final Opp</t>
-        </is>
-      </c>
-      <c r="B10">
-        <f>Calculator!U39</f>
-        <v/>
-      </c>
-      <c r="C10" t="n">
-        <v>175</v>
-      </c>
-      <c r="D10">
-        <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>HUMAN TOTALS</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Up Final Skew</t>
+          <t>Sum Big Lots</t>
         </is>
       </c>
       <c r="B11">
-        <f>Calculator!V39</f>
-        <v/>
-      </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
+        <f>SUM(E3:E7)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Down L1 Rounded Main</t>
+          <t>Sum Small Lots</t>
         </is>
       </c>
       <c r="B12">
-        <f>Calculator!W26</f>
-        <v/>
-      </c>
-      <c r="C12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D12">
-        <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
+        <f>SUM(H3:H7)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Down L1 Rounded Opp</t>
+          <t>Sum Close Lots</t>
         </is>
       </c>
       <c r="B13">
-        <f>Calculator!X26</f>
-        <v/>
-      </c>
-      <c r="C13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D13">
-        <f>IF(ABS(B13-C13)&lt;0.000001,"PASS","FAIL")</f>
+        <f>SUM(K3:K7)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Down L1 Rounded Skew</t>
+          <t>Final Start Remaining Lot</t>
         </is>
       </c>
       <c r="B14">
-        <f>Calculator!Y26</f>
-        <v/>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <f>IF(ABS(B14-C14)&lt;0.000001,"PASS","FAIL")</f>
+        <f>M7</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Down L1 Status</t>
+          <t>Final Total Main %</t>
         </is>
       </c>
       <c r="B15">
-        <f>Calculator!Z26</f>
-        <v/>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D15">
-        <f>IF(B15=C15,"PASS","FAIL")</f>
+        <f>N7</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Down L2 Rounded Main</t>
+          <t>Final Total Opposite %</t>
         </is>
       </c>
       <c r="B16">
-        <f>Calculator!W27</f>
-        <v/>
-      </c>
-      <c r="C16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D16">
-        <f>IF(ABS(B16-C16)&lt;0.000001,"PASS","FAIL")</f>
+        <f>O7</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Down L2 Rounded Opp</t>
+          <t>Final Skew %</t>
         </is>
       </c>
       <c r="B17">
-        <f>Calculator!X27</f>
-        <v/>
-      </c>
-      <c r="C17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="D17">
-        <f>IF(ABS(B17-C17)&lt;0.000001,"PASS","FAIL")</f>
+        <f>P7</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Down L2 Rounded Skew</t>
+          <t>Final Rounded Main Lot</t>
         </is>
       </c>
       <c r="B18">
-        <f>Calculator!Y27</f>
-        <v/>
-      </c>
-      <c r="C18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D18">
-        <f>IF(ABS(B18-C18)&lt;0.000001,"PASS","FAIL")</f>
+        <f>Q7</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Down L2 Status</t>
+          <t>Final Rounded Opp Lot</t>
         </is>
       </c>
       <c r="B19">
-        <f>Calculator!Z27</f>
-        <v/>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D19">
-        <f>IF(B19=C19,"PASS","FAIL")</f>
+        <f>R7</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Down Final Rounded Main</t>
+          <t>Final Rounded Skew Lot</t>
         </is>
       </c>
       <c r="B20">
-        <f>Calculator!W30</f>
-        <v/>
-      </c>
-      <c r="C20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="D20">
-        <f>IF(ABS(B20-C20)&lt;0.000001,"PASS","FAIL")</f>
+        <f>S7</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Down Final Rounded Opp</t>
+          <t>Final Status</t>
         </is>
       </c>
       <c r="B21">
-        <f>Calculator!X30</f>
-        <v/>
-      </c>
-      <c r="C21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D21">
-        <f>IF(ABS(B21-C21)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Down Final Rounded Skew</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>Calculator!Y30</f>
-        <v/>
-      </c>
-      <c r="C22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D22">
-        <f>IF(ABS(B22-C22)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Down Final Status</t>
-        </is>
-      </c>
-      <c r="B23">
-        <f>Calculator!Z30</f>
-        <v/>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D23">
-        <f>IF(B23=C23,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Up L1 Rounded Main</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>Calculator!W35</f>
-        <v/>
-      </c>
-      <c r="C24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D24">
-        <f>IF(ABS(B24-C24)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Up L1 Rounded Opp</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>Calculator!X35</f>
-        <v/>
-      </c>
-      <c r="C25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D25">
-        <f>IF(ABS(B25-C25)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Up L1 Rounded Skew</t>
-        </is>
-      </c>
-      <c r="B26">
-        <f>Calculator!Y35</f>
-        <v/>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <f>IF(ABS(B26-C26)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Up L1 Status</t>
-        </is>
-      </c>
-      <c r="B27">
-        <f>Calculator!Z35</f>
-        <v/>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D27">
-        <f>IF(B27=C27,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Up L2 Rounded Main</t>
-        </is>
-      </c>
-      <c r="B28">
-        <f>Calculator!W36</f>
-        <v/>
-      </c>
-      <c r="C28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D28">
-        <f>IF(ABS(B28-C28)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Up L2 Rounded Opp</t>
-        </is>
-      </c>
-      <c r="B29">
-        <f>Calculator!X36</f>
-        <v/>
-      </c>
-      <c r="C29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="D29">
-        <f>IF(ABS(B29-C29)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Up L2 Rounded Skew</t>
-        </is>
-      </c>
-      <c r="B30">
-        <f>Calculator!Y36</f>
-        <v/>
-      </c>
-      <c r="C30" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D30">
-        <f>IF(ABS(B30-C30)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Up L2 Status</t>
-        </is>
-      </c>
-      <c r="B31">
-        <f>Calculator!Z36</f>
-        <v/>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D31">
-        <f>IF(B31=C31,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Up Final Rounded Main</t>
-        </is>
-      </c>
-      <c r="B32">
-        <f>Calculator!W39</f>
-        <v/>
-      </c>
-      <c r="C32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="D32">
-        <f>IF(ABS(B32-C32)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Up Final Rounded Opp</t>
-        </is>
-      </c>
-      <c r="B33">
-        <f>Calculator!X39</f>
-        <v/>
-      </c>
-      <c r="C33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D33">
-        <f>IF(ABS(B33-C33)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Up Final Rounded Skew</t>
-        </is>
-      </c>
-      <c r="B34">
-        <f>Calculator!Y39</f>
-        <v/>
-      </c>
-      <c r="C34" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D34">
-        <f>IF(ABS(B34-C34)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Up Final Status</t>
-        </is>
-      </c>
-      <c r="B35">
-        <f>Calculator!Z39</f>
-        <v/>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D35">
-        <f>IF(B35=C35,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Down Level1 Status</t>
-        </is>
-      </c>
-      <c r="B36">
-        <f>Calculator!Z26</f>
-        <v/>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D36">
-        <f>IF(B36=C36,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Down Level2 Status</t>
-        </is>
-      </c>
-      <c r="B37">
-        <f>Calculator!Z27</f>
-        <v/>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D37">
-        <f>IF(B37=C37,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Down L4 Status</t>
-        </is>
-      </c>
-      <c r="B38">
-        <f>Calculator!Z29</f>
-        <v/>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D38">
-        <f>IF(B38=C38,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Down Level5 Status</t>
-        </is>
-      </c>
-      <c r="B39">
-        <f>Calculator!Z30</f>
-        <v/>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D39">
-        <f>IF(B39=C39,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Up Level1 Status</t>
-        </is>
-      </c>
-      <c r="B40">
-        <f>Calculator!Z35</f>
-        <v/>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D40">
-        <f>IF(B40=C40,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Up Level2 Status</t>
-        </is>
-      </c>
-      <c r="B41">
-        <f>Calculator!Z36</f>
-        <v/>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D41">
-        <f>IF(B41=C41,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Up L4 Status</t>
-        </is>
-      </c>
-      <c r="B42">
-        <f>Calculator!Z38</f>
-        <v/>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D42">
-        <f>IF(B42=C42,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Up Level5 Status</t>
-        </is>
-      </c>
-      <c r="B43">
-        <f>Calculator!Z39</f>
-        <v/>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D43">
-        <f>IF(B43=C43,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Summary Final Rounded Status</t>
-        </is>
-      </c>
-      <c r="B44">
-        <f>Calculator!B51</f>
-        <v/>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D44">
-        <f>IF(B44=C44,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Summary Final System Status</t>
-        </is>
-      </c>
-      <c r="B45">
-        <f>Calculator!B52</f>
-        <v/>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D45">
-        <f>IF(B45=C45,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Summary Final Status</t>
-        </is>
-      </c>
-      <c r="B46">
-        <f>Calculator!B52</f>
-        <v/>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D46">
-        <f>IF(B46=C46,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Empty ManualClose uses AutoClose</t>
-        </is>
-      </c>
-      <c r="B47">
-        <f>IF(AND(ABS(Calculator!N26-Calculator!M26)&lt;0.000001,ABS(Calculator!N27-Calculator!M27)&lt;0.000001,ABS(Calculator!N35-Calculator!M35)&lt;0.000001),"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D47">
-        <f>IF(B47=C47,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ManualClose override works</t>
-        </is>
-      </c>
-      <c r="B48">
-        <f>IF(AND(MIN(Calculator!J26,IF(50="",Calculator!M26,50))=50,MIN(Calculator!J35,IF(50="",Calculator!M35,50))=50),"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D48">
-        <f>IF(B48=C48,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Empty ManualClose is blank not zero</t>
-        </is>
-      </c>
-      <c r="B49">
-        <f>IF(AND(Calculator!E26="",Calculator!E27="",Calculator!E28="",Calculator!E35="",Calculator!E36="",Calculator!E37=""),"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D49">
-        <f>IF(B49=C49,"PASS","FAIL")</f>
+        <f>T7</f>
         <v/>
       </c>
     </row>
@@ -3216,77 +3507,401 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Инструкция</t>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Result</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. Ввести StartLot.</t>
-        </is>
+          <t>Down L1 Close%</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>Calculator!N26</f>
+        <v/>
+      </c>
+      <c r="C2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2">
+        <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2. Проверить StepPoints.</t>
-        </is>
+          <t>Down L2 Close%</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>Calculator!N27</f>
+        <v/>
+      </c>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3. Выбрать Direction DOWN или UP.</t>
-        </is>
+          <t>Down Final Main</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>Calculator!T30</f>
+        <v/>
+      </c>
+      <c r="C4" t="n">
+        <v>165</v>
+      </c>
+      <c r="D4">
+        <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4. При необходимости изменить Level Grid.</t>
-        </is>
+          <t>Down Final Opp</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>Calculator!U30</f>
+        <v/>
+      </c>
+      <c r="C5" t="n">
+        <v>175</v>
+      </c>
+      <c r="D5">
+        <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5. Смотреть Main Table.</t>
-        </is>
+          <t>Down Final Skew</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>Calculator!V30</f>
+        <v/>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <f>IF(ABS(B6-C6)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6. Проверить Summary.</t>
-        </is>
+          <t>Up L1 Close%</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>Calculator!N35</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D7">
+        <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7. Если Status = OK — сетка безопасна по математике.</t>
-        </is>
+          <t>Up L2 Close%</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>Calculator!N36</f>
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <f>IF(ABS(B8-C8)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8. Если ERROR — использовать нельзя.</t>
-        </is>
+          <t>Up Final Main</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>Calculator!T39</f>
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v>165</v>
+      </c>
+      <c r="D9">
+        <f>IF(ABS(B9-C9)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9. Если WARNING — проверить skew и rounded-лоты.</t>
-        </is>
+          <t>Up Final Opp</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>Calculator!U39</f>
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v>175</v>
+      </c>
+      <c r="D10">
+        <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Up Final Skew</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>Calculator!V39</f>
+        <v/>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Human Sum Big Lots</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>HumanSummary!B11</f>
+        <v/>
+      </c>
+      <c r="C12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D12">
+        <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Human Sum Small Lots</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>HumanSummary!B12</f>
+        <v/>
+      </c>
+      <c r="C13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D13">
+        <f>IF(ABS(B13-C13)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Human Sum Close Lots</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>HumanSummary!B13</f>
+        <v/>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D14">
+        <f>IF(ABS(B14-C14)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Human Final Start Remaining Lot</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>HumanSummary!B14</f>
+        <v/>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D15">
+        <f>IF(ABS(B15-C15)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Human Final Status</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>HumanSummary!B21</f>
+        <v/>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D16">
+        <f>IF(B16=C16,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Human Level 1 Big Action</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>HumanSummary!C3</f>
+        <v/>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Open Big BUY</t>
+        </is>
+      </c>
+      <c r="D17">
+        <f>IF(B17=C17,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Human Level 1 Small Action</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>HumanSummary!F3</f>
+        <v/>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Open Small SELL</t>
+        </is>
+      </c>
+      <c r="D18">
+        <f>IF(B18=C18,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Human Level 1 Close Action</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>HumanSummary!I3</f>
+        <v/>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Close Start BUY</t>
+        </is>
+      </c>
+      <c r="D19">
+        <f>IF(B19=C19,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Human UP Big Action</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>IF(Calculator!B6="UP",HumanSummary!C3,"SKIP")</f>
+        <v/>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Open Big SELL</t>
+        </is>
+      </c>
+      <c r="D20">
+        <f>IF(B20=C20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Summary Final System Status</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>Calculator!B52</f>
+        <v/>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D21">
+        <f>IF(B21=C21,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3300,6 +3915,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Инструкция</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. Ввести StartLot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2. Проверить StepPoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. Выбрать Direction DOWN или UP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. При необходимости изменить Level Grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. Смотреть Main Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. Проверить Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7. Смотреть Human Summary: Big=основная rescue-позиция, Small=встречная защитная, Close=частичное закрытие стартовой позиции.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8. Start Remaining = остаток стартовой позиции, Total Main/Opp = баланс сторон, Skew = защитный перевес.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9. Если Status = OK — сетка безопасна по математике.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3355,14 +4054,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Main &lt;= Opposite обязательно для сохранения защиты.</t>
+          <t>Skew — защитный перевес Opposite над Main.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Status: OK — безопасно, WARNING — проверить skew/rounded, ERROR — нельзя использовать.</t>
+          <t>Как читать Human Summary: Big/Small/Close показывают действия по уровню; Start Remaining — остаток стартовой позиции; Status отражает безопасность уровня.</t>
         </is>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -2381,9 +2381,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <f>A18</f>
-        <v/>
+      <c r="A57" t="n">
+        <v>1</v>
       </c>
       <c r="B57">
         <f>$B$6</f>
@@ -2394,11 +2393,11 @@
         <v/>
       </c>
       <c r="D57">
-        <f>IF($B$6="DOWN",B18,B18)</f>
+        <f>IF($B$6="DOWN",B26,B35)</f>
         <v/>
       </c>
       <c r="E57">
-        <f>IF($B$6="DOWN",G18,G27)</f>
+        <f>IF($B$6="DOWN",G26,G35)</f>
         <v/>
       </c>
       <c r="F57">
@@ -2406,11 +2405,11 @@
         <v/>
       </c>
       <c r="G57">
-        <f>IF($B$6="DOWN",C18,C18)</f>
+        <f>IF($B$6="DOWN",C26,C35)</f>
         <v/>
       </c>
       <c r="H57">
-        <f>IF($B$6="DOWN",I18,I27)</f>
+        <f>IF($B$6="DOWN",I26,I35)</f>
         <v/>
       </c>
       <c r="I57">
@@ -2418,15 +2417,15 @@
         <v/>
       </c>
       <c r="J57">
-        <f>IF($B$6="DOWN",N18,N27)</f>
+        <f>IF($B$6="DOWN",N26,N35)</f>
         <v/>
       </c>
       <c r="K57">
-        <f>IF($B$6="DOWN",P18,P27)</f>
+        <f>IF($B$6="DOWN",P26,P35)</f>
         <v/>
       </c>
       <c r="L57">
-        <f>IF($B$6="DOWN",Q18,Q27)</f>
+        <f>IF($B$6="DOWN",Q26,Q35)</f>
         <v/>
       </c>
       <c r="M57">
@@ -2434,42 +2433,41 @@
         <v/>
       </c>
       <c r="N57">
-        <f>IF($B$6="DOWN",T18,T27)</f>
+        <f>IF($B$6="DOWN",T26,T35)</f>
         <v/>
       </c>
       <c r="O57">
-        <f>IF($B$6="DOWN",U18,U27)</f>
+        <f>IF($B$6="DOWN",U26,U35)</f>
         <v/>
       </c>
       <c r="P57">
-        <f>IF($B$6="DOWN",V18,V27)</f>
+        <f>IF($B$6="DOWN",V26,V35)</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF($B$6="DOWN",W18,W27)</f>
+        <f>IF($B$6="DOWN",W26,W35)</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF($B$6="DOWN",X18,X27)</f>
+        <f>IF($B$6="DOWN",X26,X35)</f>
         <v/>
       </c>
       <c r="S57">
-        <f>IF($B$6="DOWN",Y18,Y27)</f>
+        <f>IF($B$6="DOWN",Y26,Y35)</f>
         <v/>
       </c>
       <c r="T57">
-        <f>IF($B$6="DOWN",Z18,Z27)</f>
+        <f>IF($B$6="DOWN",Z26,Z35)</f>
         <v/>
       </c>
       <c r="U57">
-        <f>CONCAT("Level ",A57,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C57," ",TEXT(E57,"0.00")," lot, ",F57," ",TEXT(H57,"0.00")," lot, ",I57," ",TEXT(K57,"0.00")," lot. Start remaining ",TEXT(M57,"0.00")," lot. Status=",T57)</f>
+        <f>"Level "&amp;A57&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C57&amp;" "&amp;TEXT(E57,"0.00")&amp;" lot, "&amp;F57&amp;" "&amp;TEXT(H57,"0.00")&amp;" lot, "&amp;I57&amp;" "&amp;TEXT(K57,"0.00")&amp;" lot. Start remains "&amp;TEXT(M57,"0.00")&amp;" lot. Status: "&amp;T57</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <f>A19</f>
-        <v/>
+      <c r="A58" t="n">
+        <v>2</v>
       </c>
       <c r="B58">
         <f>$B$6</f>
@@ -2480,11 +2478,11 @@
         <v/>
       </c>
       <c r="D58">
-        <f>IF($B$6="DOWN",B19,B19)</f>
+        <f>IF($B$6="DOWN",B27,B36)</f>
         <v/>
       </c>
       <c r="E58">
-        <f>IF($B$6="DOWN",G19,G28)</f>
+        <f>IF($B$6="DOWN",G27,G36)</f>
         <v/>
       </c>
       <c r="F58">
@@ -2492,11 +2490,11 @@
         <v/>
       </c>
       <c r="G58">
-        <f>IF($B$6="DOWN",C19,C19)</f>
+        <f>IF($B$6="DOWN",C27,C36)</f>
         <v/>
       </c>
       <c r="H58">
-        <f>IF($B$6="DOWN",I19,I28)</f>
+        <f>IF($B$6="DOWN",I27,I36)</f>
         <v/>
       </c>
       <c r="I58">
@@ -2504,15 +2502,15 @@
         <v/>
       </c>
       <c r="J58">
-        <f>IF($B$6="DOWN",N19,N28)</f>
+        <f>IF($B$6="DOWN",N27,N36)</f>
         <v/>
       </c>
       <c r="K58">
-        <f>IF($B$6="DOWN",P19,P28)</f>
+        <f>IF($B$6="DOWN",P27,P36)</f>
         <v/>
       </c>
       <c r="L58">
-        <f>IF($B$6="DOWN",Q19,Q28)</f>
+        <f>IF($B$6="DOWN",Q27,Q36)</f>
         <v/>
       </c>
       <c r="M58">
@@ -2520,42 +2518,41 @@
         <v/>
       </c>
       <c r="N58">
-        <f>IF($B$6="DOWN",T19,T28)</f>
+        <f>IF($B$6="DOWN",T27,T36)</f>
         <v/>
       </c>
       <c r="O58">
-        <f>IF($B$6="DOWN",U19,U28)</f>
+        <f>IF($B$6="DOWN",U27,U36)</f>
         <v/>
       </c>
       <c r="P58">
-        <f>IF($B$6="DOWN",V19,V28)</f>
+        <f>IF($B$6="DOWN",V27,V36)</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF($B$6="DOWN",W19,W28)</f>
+        <f>IF($B$6="DOWN",W27,W36)</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF($B$6="DOWN",X19,X28)</f>
+        <f>IF($B$6="DOWN",X27,X36)</f>
         <v/>
       </c>
       <c r="S58">
-        <f>IF($B$6="DOWN",Y19,Y28)</f>
+        <f>IF($B$6="DOWN",Y27,Y36)</f>
         <v/>
       </c>
       <c r="T58">
-        <f>IF($B$6="DOWN",Z19,Z28)</f>
+        <f>IF($B$6="DOWN",Z27,Z36)</f>
         <v/>
       </c>
       <c r="U58">
-        <f>CONCAT("Level ",A58,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C58," ",TEXT(E58,"0.00")," lot, ",F58," ",TEXT(H58,"0.00")," lot, ",I58," ",TEXT(K58,"0.00")," lot. Start remaining ",TEXT(M58,"0.00")," lot. Status=",T58)</f>
+        <f>"Level "&amp;A58&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C58&amp;" "&amp;TEXT(E58,"0.00")&amp;" lot, "&amp;F58&amp;" "&amp;TEXT(H58,"0.00")&amp;" lot, "&amp;I58&amp;" "&amp;TEXT(K58,"0.00")&amp;" lot. Start remains "&amp;TEXT(M58,"0.00")&amp;" lot. Status: "&amp;T58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59">
-        <f>A20</f>
-        <v/>
+      <c r="A59" t="n">
+        <v>3</v>
       </c>
       <c r="B59">
         <f>$B$6</f>
@@ -2566,11 +2563,11 @@
         <v/>
       </c>
       <c r="D59">
-        <f>IF($B$6="DOWN",B20,B20)</f>
+        <f>IF($B$6="DOWN",B28,B37)</f>
         <v/>
       </c>
       <c r="E59">
-        <f>IF($B$6="DOWN",G20,G29)</f>
+        <f>IF($B$6="DOWN",G28,G37)</f>
         <v/>
       </c>
       <c r="F59">
@@ -2578,11 +2575,11 @@
         <v/>
       </c>
       <c r="G59">
-        <f>IF($B$6="DOWN",C20,C20)</f>
+        <f>IF($B$6="DOWN",C28,C37)</f>
         <v/>
       </c>
       <c r="H59">
-        <f>IF($B$6="DOWN",I20,I29)</f>
+        <f>IF($B$6="DOWN",I28,I37)</f>
         <v/>
       </c>
       <c r="I59">
@@ -2590,15 +2587,15 @@
         <v/>
       </c>
       <c r="J59">
-        <f>IF($B$6="DOWN",N20,N29)</f>
+        <f>IF($B$6="DOWN",N28,N37)</f>
         <v/>
       </c>
       <c r="K59">
-        <f>IF($B$6="DOWN",P20,P29)</f>
+        <f>IF($B$6="DOWN",P28,P37)</f>
         <v/>
       </c>
       <c r="L59">
-        <f>IF($B$6="DOWN",Q20,Q29)</f>
+        <f>IF($B$6="DOWN",Q28,Q37)</f>
         <v/>
       </c>
       <c r="M59">
@@ -2606,42 +2603,41 @@
         <v/>
       </c>
       <c r="N59">
-        <f>IF($B$6="DOWN",T20,T29)</f>
+        <f>IF($B$6="DOWN",T28,T37)</f>
         <v/>
       </c>
       <c r="O59">
-        <f>IF($B$6="DOWN",U20,U29)</f>
+        <f>IF($B$6="DOWN",U28,U37)</f>
         <v/>
       </c>
       <c r="P59">
-        <f>IF($B$6="DOWN",V20,V29)</f>
+        <f>IF($B$6="DOWN",V28,V37)</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF($B$6="DOWN",W20,W29)</f>
+        <f>IF($B$6="DOWN",W28,W37)</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF($B$6="DOWN",X20,X29)</f>
+        <f>IF($B$6="DOWN",X28,X37)</f>
         <v/>
       </c>
       <c r="S59">
-        <f>IF($B$6="DOWN",Y20,Y29)</f>
+        <f>IF($B$6="DOWN",Y28,Y37)</f>
         <v/>
       </c>
       <c r="T59">
-        <f>IF($B$6="DOWN",Z20,Z29)</f>
+        <f>IF($B$6="DOWN",Z28,Z37)</f>
         <v/>
       </c>
       <c r="U59">
-        <f>CONCAT("Level ",A59,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C59," ",TEXT(E59,"0.00")," lot, ",F59," ",TEXT(H59,"0.00")," lot, ",I59," ",TEXT(K59,"0.00")," lot. Start remaining ",TEXT(M59,"0.00")," lot. Status=",T59)</f>
+        <f>"Level "&amp;A59&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C59&amp;" "&amp;TEXT(E59,"0.00")&amp;" lot, "&amp;F59&amp;" "&amp;TEXT(H59,"0.00")&amp;" lot, "&amp;I59&amp;" "&amp;TEXT(K59,"0.00")&amp;" lot. Start remains "&amp;TEXT(M59,"0.00")&amp;" lot. Status: "&amp;T59</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60">
-        <f>A21</f>
-        <v/>
+      <c r="A60" t="n">
+        <v>4</v>
       </c>
       <c r="B60">
         <f>$B$6</f>
@@ -2652,11 +2648,11 @@
         <v/>
       </c>
       <c r="D60">
-        <f>IF($B$6="DOWN",B21,B21)</f>
+        <f>IF($B$6="DOWN",B29,B38)</f>
         <v/>
       </c>
       <c r="E60">
-        <f>IF($B$6="DOWN",G21,G30)</f>
+        <f>IF($B$6="DOWN",G29,G38)</f>
         <v/>
       </c>
       <c r="F60">
@@ -2664,11 +2660,11 @@
         <v/>
       </c>
       <c r="G60">
-        <f>IF($B$6="DOWN",C21,C21)</f>
+        <f>IF($B$6="DOWN",C29,C38)</f>
         <v/>
       </c>
       <c r="H60">
-        <f>IF($B$6="DOWN",I21,I30)</f>
+        <f>IF($B$6="DOWN",I29,I38)</f>
         <v/>
       </c>
       <c r="I60">
@@ -2676,15 +2672,15 @@
         <v/>
       </c>
       <c r="J60">
-        <f>IF($B$6="DOWN",N21,N30)</f>
+        <f>IF($B$6="DOWN",N29,N38)</f>
         <v/>
       </c>
       <c r="K60">
-        <f>IF($B$6="DOWN",P21,P30)</f>
+        <f>IF($B$6="DOWN",P29,P38)</f>
         <v/>
       </c>
       <c r="L60">
-        <f>IF($B$6="DOWN",Q21,Q30)</f>
+        <f>IF($B$6="DOWN",Q29,Q38)</f>
         <v/>
       </c>
       <c r="M60">
@@ -2692,42 +2688,41 @@
         <v/>
       </c>
       <c r="N60">
-        <f>IF($B$6="DOWN",T21,T30)</f>
+        <f>IF($B$6="DOWN",T29,T38)</f>
         <v/>
       </c>
       <c r="O60">
-        <f>IF($B$6="DOWN",U21,U30)</f>
+        <f>IF($B$6="DOWN",U29,U38)</f>
         <v/>
       </c>
       <c r="P60">
-        <f>IF($B$6="DOWN",V21,V30)</f>
+        <f>IF($B$6="DOWN",V29,V38)</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF($B$6="DOWN",W21,W30)</f>
+        <f>IF($B$6="DOWN",W29,W38)</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF($B$6="DOWN",X21,X30)</f>
+        <f>IF($B$6="DOWN",X29,X38)</f>
         <v/>
       </c>
       <c r="S60">
-        <f>IF($B$6="DOWN",Y21,Y30)</f>
+        <f>IF($B$6="DOWN",Y29,Y38)</f>
         <v/>
       </c>
       <c r="T60">
-        <f>IF($B$6="DOWN",Z21,Z30)</f>
+        <f>IF($B$6="DOWN",Z29,Z38)</f>
         <v/>
       </c>
       <c r="U60">
-        <f>CONCAT("Level ",A60,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C60," ",TEXT(E60,"0.00")," lot, ",F60," ",TEXT(H60,"0.00")," lot, ",I60," ",TEXT(K60,"0.00")," lot. Start remaining ",TEXT(M60,"0.00")," lot. Status=",T60)</f>
+        <f>"Level "&amp;A60&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C60&amp;" "&amp;TEXT(E60,"0.00")&amp;" lot, "&amp;F60&amp;" "&amp;TEXT(H60,"0.00")&amp;" lot, "&amp;I60&amp;" "&amp;TEXT(K60,"0.00")&amp;" lot. Start remains "&amp;TEXT(M60,"0.00")&amp;" lot. Status: "&amp;T60</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61">
-        <f>A22</f>
-        <v/>
+      <c r="A61" t="n">
+        <v>5</v>
       </c>
       <c r="B61">
         <f>$B$6</f>
@@ -2738,11 +2733,11 @@
         <v/>
       </c>
       <c r="D61">
-        <f>IF($B$6="DOWN",B22,B22)</f>
+        <f>IF($B$6="DOWN",B30,B39)</f>
         <v/>
       </c>
       <c r="E61">
-        <f>IF($B$6="DOWN",G22,G31)</f>
+        <f>IF($B$6="DOWN",G30,G39)</f>
         <v/>
       </c>
       <c r="F61">
@@ -2750,11 +2745,11 @@
         <v/>
       </c>
       <c r="G61">
-        <f>IF($B$6="DOWN",C22,C22)</f>
+        <f>IF($B$6="DOWN",C30,C39)</f>
         <v/>
       </c>
       <c r="H61">
-        <f>IF($B$6="DOWN",I22,I31)</f>
+        <f>IF($B$6="DOWN",I30,I39)</f>
         <v/>
       </c>
       <c r="I61">
@@ -2762,15 +2757,15 @@
         <v/>
       </c>
       <c r="J61">
-        <f>IF($B$6="DOWN",N22,N31)</f>
+        <f>IF($B$6="DOWN",N30,N39)</f>
         <v/>
       </c>
       <c r="K61">
-        <f>IF($B$6="DOWN",P22,P31)</f>
+        <f>IF($B$6="DOWN",P30,P39)</f>
         <v/>
       </c>
       <c r="L61">
-        <f>IF($B$6="DOWN",Q22,Q31)</f>
+        <f>IF($B$6="DOWN",Q30,Q39)</f>
         <v/>
       </c>
       <c r="M61">
@@ -2778,35 +2773,35 @@
         <v/>
       </c>
       <c r="N61">
-        <f>IF($B$6="DOWN",T22,T31)</f>
+        <f>IF($B$6="DOWN",T30,T39)</f>
         <v/>
       </c>
       <c r="O61">
-        <f>IF($B$6="DOWN",U22,U31)</f>
+        <f>IF($B$6="DOWN",U30,U39)</f>
         <v/>
       </c>
       <c r="P61">
-        <f>IF($B$6="DOWN",V22,V31)</f>
+        <f>IF($B$6="DOWN",V30,V39)</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF($B$6="DOWN",W22,W31)</f>
+        <f>IF($B$6="DOWN",W30,W39)</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF($B$6="DOWN",X22,X31)</f>
+        <f>IF($B$6="DOWN",X30,X39)</f>
         <v/>
       </c>
       <c r="S61">
-        <f>IF($B$6="DOWN",Y22,Y31)</f>
+        <f>IF($B$6="DOWN",Y30,Y39)</f>
         <v/>
       </c>
       <c r="T61">
-        <f>IF($B$6="DOWN",Z22,Z31)</f>
+        <f>IF($B$6="DOWN",Z30,Z39)</f>
         <v/>
       </c>
       <c r="U61">
-        <f>CONCAT("Level ",A61,": ",IF($B$6="DOWN","цена идёт вниз","цена идёт вверх"),". ",C61," ",TEXT(E61,"0.00")," lot, ",F61," ",TEXT(H61,"0.00")," lot, ",I61," ",TEXT(K61,"0.00")," lot. Start remaining ",TEXT(M61,"0.00")," lot. Status=",T61)</f>
+        <f>"Level "&amp;A61&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C61&amp;" "&amp;TEXT(E61,"0.00")&amp;" lot, "&amp;F61&amp;" "&amp;TEXT(H61,"0.00")&amp;" lot, "&amp;I61&amp;" "&amp;TEXT(K61,"0.00")&amp;" lot. Start remains "&amp;TEXT(M61,"0.00")&amp;" lot. Status: "&amp;T61</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -1015,28 +1015,12 @@
         <f>MIN($B$2*J26/100,IF($B$7,CEILING(O26,$B$5),O26))</f>
         <v/>
       </c>
-      <c r="Q26">
-        <f>J26-N26</f>
-        <v/>
-      </c>
       <c r="R26">
         <f>SUM($B$26:B26)</f>
         <v/>
       </c>
       <c r="S26">
         <f>SUM($C$26:C26)</f>
-        <v/>
-      </c>
-      <c r="T26">
-        <f>Q26+R26</f>
-        <v/>
-      </c>
-      <c r="U26">
-        <f>100+S26</f>
-        <v/>
-      </c>
-      <c r="V26">
-        <f>U26-T26</f>
         <v/>
       </c>
       <c r="W26">
@@ -1121,28 +1105,12 @@
         <f>MIN($B$2*J27/100,IF($B$7,CEILING(O27,$B$5),O27))</f>
         <v/>
       </c>
-      <c r="Q27">
-        <f>J27-N27</f>
-        <v/>
-      </c>
       <c r="R27">
         <f>SUM($B$26:B27)</f>
         <v/>
       </c>
       <c r="S27">
         <f>SUM($C$26:C27)</f>
-        <v/>
-      </c>
-      <c r="T27">
-        <f>Q27+R27</f>
-        <v/>
-      </c>
-      <c r="U27">
-        <f>100+S27</f>
-        <v/>
-      </c>
-      <c r="V27">
-        <f>U27-T27</f>
         <v/>
       </c>
       <c r="W27">
@@ -1227,28 +1195,12 @@
         <f>MIN($B$2*J28/100,IF($B$7,CEILING(O28,$B$5),O28))</f>
         <v/>
       </c>
-      <c r="Q28">
-        <f>J28-N28</f>
-        <v/>
-      </c>
       <c r="R28">
         <f>SUM($B$26:B28)</f>
         <v/>
       </c>
       <c r="S28">
         <f>SUM($C$26:C28)</f>
-        <v/>
-      </c>
-      <c r="T28">
-        <f>Q28+R28</f>
-        <v/>
-      </c>
-      <c r="U28">
-        <f>100+S28</f>
-        <v/>
-      </c>
-      <c r="V28">
-        <f>U28-T28</f>
         <v/>
       </c>
       <c r="W28">
@@ -1333,28 +1285,12 @@
         <f>MIN($B$2*J29/100,IF($B$7,CEILING(O29,$B$5),O29))</f>
         <v/>
       </c>
-      <c r="Q29">
-        <f>J29-N29</f>
-        <v/>
-      </c>
       <c r="R29">
         <f>SUM($B$26:B29)</f>
         <v/>
       </c>
       <c r="S29">
         <f>SUM($C$26:C29)</f>
-        <v/>
-      </c>
-      <c r="T29">
-        <f>Q29+R29</f>
-        <v/>
-      </c>
-      <c r="U29">
-        <f>100+S29</f>
-        <v/>
-      </c>
-      <c r="V29">
-        <f>U29-T29</f>
         <v/>
       </c>
       <c r="W29">
@@ -1439,28 +1375,12 @@
         <f>MIN($B$2*J30/100,IF($B$7,CEILING(O30,$B$5),O30))</f>
         <v/>
       </c>
-      <c r="Q30">
-        <f>J30-N30</f>
-        <v/>
-      </c>
       <c r="R30">
         <f>SUM($B$26:B30)</f>
         <v/>
       </c>
       <c r="S30">
         <f>SUM($C$26:C30)</f>
-        <v/>
-      </c>
-      <c r="T30">
-        <f>Q30+R30</f>
-        <v/>
-      </c>
-      <c r="U30">
-        <f>100+S30</f>
-        <v/>
-      </c>
-      <c r="V30">
-        <f>U30-T30</f>
         <v/>
       </c>
       <c r="W30">
@@ -1684,28 +1604,12 @@
         <f>MIN($B$2*J35/100,IF($B$7,CEILING(O35,$B$5),O35))</f>
         <v/>
       </c>
-      <c r="Q35">
-        <f>J35-N35</f>
-        <v/>
-      </c>
       <c r="R35">
         <f>SUM($B$35:B35)</f>
         <v/>
       </c>
       <c r="S35">
         <f>SUM($C$35:C35)</f>
-        <v/>
-      </c>
-      <c r="T35">
-        <f>Q35+R35</f>
-        <v/>
-      </c>
-      <c r="U35">
-        <f>100+S35</f>
-        <v/>
-      </c>
-      <c r="V35">
-        <f>U35-T35</f>
         <v/>
       </c>
       <c r="W35">
@@ -1790,28 +1694,12 @@
         <f>MIN($B$2*J36/100,IF($B$7,CEILING(O36,$B$5),O36))</f>
         <v/>
       </c>
-      <c r="Q36">
-        <f>J36-N36</f>
-        <v/>
-      </c>
       <c r="R36">
         <f>SUM($B$35:B36)</f>
         <v/>
       </c>
       <c r="S36">
         <f>SUM($C$35:C36)</f>
-        <v/>
-      </c>
-      <c r="T36">
-        <f>Q36+R36</f>
-        <v/>
-      </c>
-      <c r="U36">
-        <f>100+S36</f>
-        <v/>
-      </c>
-      <c r="V36">
-        <f>U36-T36</f>
         <v/>
       </c>
       <c r="W36">
@@ -1896,28 +1784,12 @@
         <f>MIN($B$2*J37/100,IF($B$7,CEILING(O37,$B$5),O37))</f>
         <v/>
       </c>
-      <c r="Q37">
-        <f>J37-N37</f>
-        <v/>
-      </c>
       <c r="R37">
         <f>SUM($B$35:B37)</f>
         <v/>
       </c>
       <c r="S37">
         <f>SUM($C$35:C37)</f>
-        <v/>
-      </c>
-      <c r="T37">
-        <f>Q37+R37</f>
-        <v/>
-      </c>
-      <c r="U37">
-        <f>100+S37</f>
-        <v/>
-      </c>
-      <c r="V37">
-        <f>U37-T37</f>
         <v/>
       </c>
       <c r="W37">
@@ -2002,28 +1874,12 @@
         <f>MIN($B$2*J38/100,IF($B$7,CEILING(O38,$B$5),O38))</f>
         <v/>
       </c>
-      <c r="Q38">
-        <f>J38-N38</f>
-        <v/>
-      </c>
       <c r="R38">
         <f>SUM($B$35:B38)</f>
         <v/>
       </c>
       <c r="S38">
         <f>SUM($C$35:C38)</f>
-        <v/>
-      </c>
-      <c r="T38">
-        <f>Q38+R38</f>
-        <v/>
-      </c>
-      <c r="U38">
-        <f>100+S38</f>
-        <v/>
-      </c>
-      <c r="V38">
-        <f>U38-T38</f>
         <v/>
       </c>
       <c r="W38">
@@ -2108,28 +1964,12 @@
         <f>MIN($B$2*J39/100,IF($B$7,CEILING(O39,$B$5),O39))</f>
         <v/>
       </c>
-      <c r="Q39">
-        <f>J39-N39</f>
-        <v/>
-      </c>
       <c r="R39">
         <f>SUM($B$35:B39)</f>
         <v/>
       </c>
       <c r="S39">
         <f>SUM($C$35:C39)</f>
-        <v/>
-      </c>
-      <c r="T39">
-        <f>Q39+R39</f>
-        <v/>
-      </c>
-      <c r="U39">
-        <f>100+S39</f>
-        <v/>
-      </c>
-      <c r="V39">
-        <f>U39-T39</f>
         <v/>
       </c>
       <c r="W39">
@@ -2461,7 +2301,7 @@
         <v/>
       </c>
       <c r="U57">
-        <f>"Level "&amp;A57&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C57&amp;" "&amp;TEXT(E57,"0.00")&amp;" lot, "&amp;F57&amp;" "&amp;TEXT(H57,"0.00")&amp;" lot, "&amp;I57&amp;" "&amp;TEXT(K57,"0.00")&amp;" lot. Start remains "&amp;TEXT(M57,"0.00")&amp;" lot. Status: "&amp;T57</f>
+        <f>"Level "&amp;A57&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C57&amp;" "&amp;ROUND(E57,2)&amp;" lot, "&amp;F57&amp;" "&amp;ROUND(H57,2)&amp;" lot, "&amp;I57&amp;" "&amp;ROUND(K57,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M57,2)&amp;" lot. "&amp;"Total Main = "&amp;N57&amp;"%, "&amp;"Total Opposite = "&amp;O57&amp;"%, "&amp;"Skew = "&amp;P57&amp;"%, "&amp;"Status = "&amp;T57&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2546,7 +2386,7 @@
         <v/>
       </c>
       <c r="U58">
-        <f>"Level "&amp;A58&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C58&amp;" "&amp;TEXT(E58,"0.00")&amp;" lot, "&amp;F58&amp;" "&amp;TEXT(H58,"0.00")&amp;" lot, "&amp;I58&amp;" "&amp;TEXT(K58,"0.00")&amp;" lot. Start remains "&amp;TEXT(M58,"0.00")&amp;" lot. Status: "&amp;T58</f>
+        <f>"Level "&amp;A58&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C58&amp;" "&amp;ROUND(E58,2)&amp;" lot, "&amp;F58&amp;" "&amp;ROUND(H58,2)&amp;" lot, "&amp;I58&amp;" "&amp;ROUND(K58,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M58,2)&amp;" lot. "&amp;"Total Main = "&amp;N58&amp;"%, "&amp;"Total Opposite = "&amp;O58&amp;"%, "&amp;"Skew = "&amp;P58&amp;"%, "&amp;"Status = "&amp;T58&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2631,7 +2471,7 @@
         <v/>
       </c>
       <c r="U59">
-        <f>"Level "&amp;A59&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C59&amp;" "&amp;TEXT(E59,"0.00")&amp;" lot, "&amp;F59&amp;" "&amp;TEXT(H59,"0.00")&amp;" lot, "&amp;I59&amp;" "&amp;TEXT(K59,"0.00")&amp;" lot. Start remains "&amp;TEXT(M59,"0.00")&amp;" lot. Status: "&amp;T59</f>
+        <f>"Level "&amp;A59&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C59&amp;" "&amp;ROUND(E59,2)&amp;" lot, "&amp;F59&amp;" "&amp;ROUND(H59,2)&amp;" lot, "&amp;I59&amp;" "&amp;ROUND(K59,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M59,2)&amp;" lot. "&amp;"Total Main = "&amp;N59&amp;"%, "&amp;"Total Opposite = "&amp;O59&amp;"%, "&amp;"Skew = "&amp;P59&amp;"%, "&amp;"Status = "&amp;T59&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2716,7 +2556,7 @@
         <v/>
       </c>
       <c r="U60">
-        <f>"Level "&amp;A60&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C60&amp;" "&amp;TEXT(E60,"0.00")&amp;" lot, "&amp;F60&amp;" "&amp;TEXT(H60,"0.00")&amp;" lot, "&amp;I60&amp;" "&amp;TEXT(K60,"0.00")&amp;" lot. Start remains "&amp;TEXT(M60,"0.00")&amp;" lot. Status: "&amp;T60</f>
+        <f>"Level "&amp;A60&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C60&amp;" "&amp;ROUND(E60,2)&amp;" lot, "&amp;F60&amp;" "&amp;ROUND(H60,2)&amp;" lot, "&amp;I60&amp;" "&amp;ROUND(K60,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M60,2)&amp;" lot. "&amp;"Total Main = "&amp;N60&amp;"%, "&amp;"Total Opposite = "&amp;O60&amp;"%, "&amp;"Skew = "&amp;P60&amp;"%, "&amp;"Status = "&amp;T60&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2801,7 +2641,7 @@
         <v/>
       </c>
       <c r="U61">
-        <f>"Level "&amp;A61&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C61&amp;" "&amp;TEXT(E61,"0.00")&amp;" lot, "&amp;F61&amp;" "&amp;TEXT(H61,"0.00")&amp;" lot, "&amp;I61&amp;" "&amp;TEXT(K61,"0.00")&amp;" lot. Start remains "&amp;TEXT(M61,"0.00")&amp;" lot. Status: "&amp;T61</f>
+        <f>"Level "&amp;A61&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C61&amp;" "&amp;ROUND(E61,2)&amp;" lot, "&amp;F61&amp;" "&amp;ROUND(H61,2)&amp;" lot, "&amp;I61&amp;" "&amp;ROUND(K61,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M61,2)&amp;" lot. "&amp;"Total Main = "&amp;N61&amp;"%, "&amp;"Total Opposite = "&amp;O61&amp;"%, "&amp;"Skew = "&amp;P61&amp;"%, "&amp;"Status = "&amp;T61&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -3502,7 +3342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3896,6 +3736,166 @@
       </c>
       <c r="D21">
         <f>IF(B21=C21,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Human Comment L1 is text</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>IF(LEN(HumanSummary!U3)&gt;0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D22">
+        <f>IF(B22=C22,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Human Comment L1 no #VALUE</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>IF(ISNUMBER(SEARCH("#VALUE",HumanSummary!U3)),"FAIL","PASS")</f>
+        <v/>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D23">
+        <f>IF(B23=C23,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Human Comment L1 no #ИМЯ</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>IF(ISNUMBER(SEARCH("#ИМЯ",HumanSummary!U3)),"FAIL","PASS")</f>
+        <v/>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D24">
+        <f>IF(B24=C24,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Human Comment L1 has Open Big BUY</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>IF(ISNUMBER(SEARCH("Open Big BUY",HumanSummary!U3)),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D25">
+        <f>IF(B25=C25,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Human Comment L1 has Close Start BUY</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>IF(ISNUMBER(SEARCH("Close Start BUY",HumanSummary!U3)),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D26">
+        <f>IF(B26=C26,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Human Comment L1 has Status</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>IF(ISNUMBER(SEARCH("Status =",HumanSummary!U3)),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D27">
+        <f>IF(B27=C27,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Human Comment L5 is text</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>IF(LEN(HumanSummary!U7)&gt;0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D28">
+        <f>IF(B28=C28,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Human Comment L5 no error</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>IF(OR(ISNUMBER(SEARCH("#VALUE",HumanSummary!U7)),ISNUMBER(SEARCH("#ИМЯ",HumanSummary!U7)),ISNUMBER(SEARCH("#NAME",HumanSummary!U7))),"FAIL","PASS")</f>
+        <v/>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D29">
+        <f>IF(B29=C29,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -436,11 +436,6 @@
           <t>PARAMETERS</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>STATUS / CHECKS</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -451,20 +446,6 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>стартовый лот</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>StartLot</t>
-        </is>
-      </c>
-      <c r="F2">
-        <f>IF(B2&lt;=0,"ERROR: Invalid StartLot","OK")</f>
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -475,20 +456,6 @@
       <c r="B3" t="n">
         <v>100</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>шаг сетки в пунктах</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LotStep</t>
-        </is>
-      </c>
-      <c r="F3">
-        <f>IF(B5&lt;=0,"ERROR: Invalid LotStep","OK")</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -499,20 +466,6 @@
       <c r="B4" t="n">
         <v>5</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>максимум уровней</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MaxLevels</t>
-        </is>
-      </c>
-      <c r="F4">
-        <f>IF(B4&lt;1,"ERROR: Invalid MaxLevels","OK")</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -523,20 +476,6 @@
       <c r="B5" t="n">
         <v>0.01</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>шаг лота брокера</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="F5">
-        <f>IF(OR(B6="DOWN",B6="UP"),"OK","ERROR: Invalid Direction")</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,20 +488,6 @@
           <t>DOWN</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>выбранный сценарий DOWN/UP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>StepPoints</t>
-        </is>
-      </c>
-      <c r="F6">
-        <f>IF(B3&lt;=0,"ERROR: Invalid StepPoints","OK")</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -573,20 +498,6 @@
       <c r="B7" t="b">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>использовать округление</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PointValue</t>
-        </is>
-      </c>
-      <c r="F7">
-        <f>IF(B11&lt;=0,"ERROR: Invalid PointValue","OK")</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -599,20 +510,6 @@
           <t>DOWN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Big округлять вниз</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="F8">
-        <f>IF(B12&lt;0,"ERROR: Invalid Spread","OK")</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -625,20 +522,6 @@
           <t>UP</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Small округлять вверх</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Commission</t>
-        </is>
-      </c>
-      <c r="F9">
-        <f>IF(B13&lt;0,"ERROR: Invalid Commission","OK")</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -651,11 +534,6 @@
           <t>SAFE</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>защитное округление Close</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -666,11 +544,6 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>стоимость пункта</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -681,11 +554,6 @@
       <c r="B12" t="n">
         <v>0</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>спред</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -695,11 +563,6 @@
       </c>
       <c r="B13" t="n">
         <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>комиссия</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -1015,12 +878,28 @@
         <f>MIN($B$2*J26/100,IF($B$7,CEILING(O26,$B$5),O26))</f>
         <v/>
       </c>
+      <c r="Q26">
+        <f>J26-N26</f>
+        <v/>
+      </c>
       <c r="R26">
         <f>SUM($B$26:B26)</f>
         <v/>
       </c>
       <c r="S26">
         <f>SUM($C$26:C26)</f>
+        <v/>
+      </c>
+      <c r="T26">
+        <f>Q26+R26</f>
+        <v/>
+      </c>
+      <c r="U26">
+        <f>100+S26</f>
+        <v/>
+      </c>
+      <c r="V26">
+        <f>U26-T26</f>
         <v/>
       </c>
       <c r="W26">
@@ -1105,12 +984,28 @@
         <f>MIN($B$2*J27/100,IF($B$7,CEILING(O27,$B$5),O27))</f>
         <v/>
       </c>
+      <c r="Q27">
+        <f>J27-N27</f>
+        <v/>
+      </c>
       <c r="R27">
         <f>SUM($B$26:B27)</f>
         <v/>
       </c>
       <c r="S27">
         <f>SUM($C$26:C27)</f>
+        <v/>
+      </c>
+      <c r="T27">
+        <f>Q27+R27</f>
+        <v/>
+      </c>
+      <c r="U27">
+        <f>100+S27</f>
+        <v/>
+      </c>
+      <c r="V27">
+        <f>U27-T27</f>
         <v/>
       </c>
       <c r="W27">
@@ -1195,12 +1090,28 @@
         <f>MIN($B$2*J28/100,IF($B$7,CEILING(O28,$B$5),O28))</f>
         <v/>
       </c>
+      <c r="Q28">
+        <f>J28-N28</f>
+        <v/>
+      </c>
       <c r="R28">
         <f>SUM($B$26:B28)</f>
         <v/>
       </c>
       <c r="S28">
         <f>SUM($C$26:C28)</f>
+        <v/>
+      </c>
+      <c r="T28">
+        <f>Q28+R28</f>
+        <v/>
+      </c>
+      <c r="U28">
+        <f>100+S28</f>
+        <v/>
+      </c>
+      <c r="V28">
+        <f>U28-T28</f>
         <v/>
       </c>
       <c r="W28">
@@ -1285,12 +1196,28 @@
         <f>MIN($B$2*J29/100,IF($B$7,CEILING(O29,$B$5),O29))</f>
         <v/>
       </c>
+      <c r="Q29">
+        <f>J29-N29</f>
+        <v/>
+      </c>
       <c r="R29">
         <f>SUM($B$26:B29)</f>
         <v/>
       </c>
       <c r="S29">
         <f>SUM($C$26:C29)</f>
+        <v/>
+      </c>
+      <c r="T29">
+        <f>Q29+R29</f>
+        <v/>
+      </c>
+      <c r="U29">
+        <f>100+S29</f>
+        <v/>
+      </c>
+      <c r="V29">
+        <f>U29-T29</f>
         <v/>
       </c>
       <c r="W29">
@@ -1375,12 +1302,28 @@
         <f>MIN($B$2*J30/100,IF($B$7,CEILING(O30,$B$5),O30))</f>
         <v/>
       </c>
+      <c r="Q30">
+        <f>J30-N30</f>
+        <v/>
+      </c>
       <c r="R30">
         <f>SUM($B$26:B30)</f>
         <v/>
       </c>
       <c r="S30">
         <f>SUM($C$26:C30)</f>
+        <v/>
+      </c>
+      <c r="T30">
+        <f>Q30+R30</f>
+        <v/>
+      </c>
+      <c r="U30">
+        <f>100+S30</f>
+        <v/>
+      </c>
+      <c r="V30">
+        <f>U30-T30</f>
         <v/>
       </c>
       <c r="W30">
@@ -1604,12 +1547,28 @@
         <f>MIN($B$2*J35/100,IF($B$7,CEILING(O35,$B$5),O35))</f>
         <v/>
       </c>
+      <c r="Q35">
+        <f>J35-N35</f>
+        <v/>
+      </c>
       <c r="R35">
         <f>SUM($B$35:B35)</f>
         <v/>
       </c>
       <c r="S35">
         <f>SUM($C$35:C35)</f>
+        <v/>
+      </c>
+      <c r="T35">
+        <f>Q35+R35</f>
+        <v/>
+      </c>
+      <c r="U35">
+        <f>100+S35</f>
+        <v/>
+      </c>
+      <c r="V35">
+        <f>U35-T35</f>
         <v/>
       </c>
       <c r="W35">
@@ -1694,12 +1653,28 @@
         <f>MIN($B$2*J36/100,IF($B$7,CEILING(O36,$B$5),O36))</f>
         <v/>
       </c>
+      <c r="Q36">
+        <f>J36-N36</f>
+        <v/>
+      </c>
       <c r="R36">
         <f>SUM($B$35:B36)</f>
         <v/>
       </c>
       <c r="S36">
         <f>SUM($C$35:C36)</f>
+        <v/>
+      </c>
+      <c r="T36">
+        <f>Q36+R36</f>
+        <v/>
+      </c>
+      <c r="U36">
+        <f>100+S36</f>
+        <v/>
+      </c>
+      <c r="V36">
+        <f>U36-T36</f>
         <v/>
       </c>
       <c r="W36">
@@ -1784,12 +1759,28 @@
         <f>MIN($B$2*J37/100,IF($B$7,CEILING(O37,$B$5),O37))</f>
         <v/>
       </c>
+      <c r="Q37">
+        <f>J37-N37</f>
+        <v/>
+      </c>
       <c r="R37">
         <f>SUM($B$35:B37)</f>
         <v/>
       </c>
       <c r="S37">
         <f>SUM($C$35:C37)</f>
+        <v/>
+      </c>
+      <c r="T37">
+        <f>Q37+R37</f>
+        <v/>
+      </c>
+      <c r="U37">
+        <f>100+S37</f>
+        <v/>
+      </c>
+      <c r="V37">
+        <f>U37-T37</f>
         <v/>
       </c>
       <c r="W37">
@@ -1874,12 +1865,28 @@
         <f>MIN($B$2*J38/100,IF($B$7,CEILING(O38,$B$5),O38))</f>
         <v/>
       </c>
+      <c r="Q38">
+        <f>J38-N38</f>
+        <v/>
+      </c>
       <c r="R38">
         <f>SUM($B$35:B38)</f>
         <v/>
       </c>
       <c r="S38">
         <f>SUM($C$35:C38)</f>
+        <v/>
+      </c>
+      <c r="T38">
+        <f>Q38+R38</f>
+        <v/>
+      </c>
+      <c r="U38">
+        <f>100+S38</f>
+        <v/>
+      </c>
+      <c r="V38">
+        <f>U38-T38</f>
         <v/>
       </c>
       <c r="W38">
@@ -1964,12 +1971,28 @@
         <f>MIN($B$2*J39/100,IF($B$7,CEILING(O39,$B$5),O39))</f>
         <v/>
       </c>
+      <c r="Q39">
+        <f>J39-N39</f>
+        <v/>
+      </c>
       <c r="R39">
         <f>SUM($B$35:B39)</f>
         <v/>
       </c>
       <c r="S39">
         <f>SUM($C$35:C39)</f>
+        <v/>
+      </c>
+      <c r="T39">
+        <f>Q39+R39</f>
+        <v/>
+      </c>
+      <c r="U39">
+        <f>100+S39</f>
+        <v/>
+      </c>
+      <c r="V39">
+        <f>U39-T39</f>
         <v/>
       </c>
       <c r="W39">
@@ -2301,7 +2324,7 @@
         <v/>
       </c>
       <c r="U57">
-        <f>"Level "&amp;A57&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C57&amp;" "&amp;ROUND(E57,2)&amp;" lot, "&amp;F57&amp;" "&amp;ROUND(H57,2)&amp;" lot, "&amp;I57&amp;" "&amp;ROUND(K57,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M57,2)&amp;" lot. "&amp;"Total Main = "&amp;N57&amp;"%, "&amp;"Total Opposite = "&amp;O57&amp;"%, "&amp;"Skew = "&amp;P57&amp;"%, "&amp;"Status = "&amp;T57&amp;"."</f>
+        <f>"Level "&amp;A57&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C57&amp;" "&amp;ROUND(E57,2)&amp;" lot, "&amp;F57&amp;" "&amp;ROUND(H57,2)&amp;" lot, "&amp;I57&amp;" "&amp;ROUND(K57,2)&amp;" lot. Start remains "&amp;ROUND(M57,2)&amp;" lot. Total Main = "&amp;N57&amp;"%, Total Opposite = "&amp;O57&amp;"%, Skew = "&amp;P57&amp;"%, Status = "&amp;T57&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2386,7 +2409,7 @@
         <v/>
       </c>
       <c r="U58">
-        <f>"Level "&amp;A58&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C58&amp;" "&amp;ROUND(E58,2)&amp;" lot, "&amp;F58&amp;" "&amp;ROUND(H58,2)&amp;" lot, "&amp;I58&amp;" "&amp;ROUND(K58,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M58,2)&amp;" lot. "&amp;"Total Main = "&amp;N58&amp;"%, "&amp;"Total Opposite = "&amp;O58&amp;"%, "&amp;"Skew = "&amp;P58&amp;"%, "&amp;"Status = "&amp;T58&amp;"."</f>
+        <f>"Level "&amp;A58&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C58&amp;" "&amp;ROUND(E58,2)&amp;" lot, "&amp;F58&amp;" "&amp;ROUND(H58,2)&amp;" lot, "&amp;I58&amp;" "&amp;ROUND(K58,2)&amp;" lot. Start remains "&amp;ROUND(M58,2)&amp;" lot. Total Main = "&amp;N58&amp;"%, Total Opposite = "&amp;O58&amp;"%, Skew = "&amp;P58&amp;"%, Status = "&amp;T58&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2471,7 +2494,7 @@
         <v/>
       </c>
       <c r="U59">
-        <f>"Level "&amp;A59&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C59&amp;" "&amp;ROUND(E59,2)&amp;" lot, "&amp;F59&amp;" "&amp;ROUND(H59,2)&amp;" lot, "&amp;I59&amp;" "&amp;ROUND(K59,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M59,2)&amp;" lot. "&amp;"Total Main = "&amp;N59&amp;"%, "&amp;"Total Opposite = "&amp;O59&amp;"%, "&amp;"Skew = "&amp;P59&amp;"%, "&amp;"Status = "&amp;T59&amp;"."</f>
+        <f>"Level "&amp;A59&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C59&amp;" "&amp;ROUND(E59,2)&amp;" lot, "&amp;F59&amp;" "&amp;ROUND(H59,2)&amp;" lot, "&amp;I59&amp;" "&amp;ROUND(K59,2)&amp;" lot. Start remains "&amp;ROUND(M59,2)&amp;" lot. Total Main = "&amp;N59&amp;"%, Total Opposite = "&amp;O59&amp;"%, Skew = "&amp;P59&amp;"%, Status = "&amp;T59&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2556,7 +2579,7 @@
         <v/>
       </c>
       <c r="U60">
-        <f>"Level "&amp;A60&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C60&amp;" "&amp;ROUND(E60,2)&amp;" lot, "&amp;F60&amp;" "&amp;ROUND(H60,2)&amp;" lot, "&amp;I60&amp;" "&amp;ROUND(K60,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M60,2)&amp;" lot. "&amp;"Total Main = "&amp;N60&amp;"%, "&amp;"Total Opposite = "&amp;O60&amp;"%, "&amp;"Skew = "&amp;P60&amp;"%, "&amp;"Status = "&amp;T60&amp;"."</f>
+        <f>"Level "&amp;A60&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C60&amp;" "&amp;ROUND(E60,2)&amp;" lot, "&amp;F60&amp;" "&amp;ROUND(H60,2)&amp;" lot, "&amp;I60&amp;" "&amp;ROUND(K60,2)&amp;" lot. Start remains "&amp;ROUND(M60,2)&amp;" lot. Total Main = "&amp;N60&amp;"%, Total Opposite = "&amp;O60&amp;"%, Skew = "&amp;P60&amp;"%, Status = "&amp;T60&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2641,7 +2664,7 @@
         <v/>
       </c>
       <c r="U61">
-        <f>"Level "&amp;A61&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C61&amp;" "&amp;ROUND(E61,2)&amp;" lot, "&amp;F61&amp;" "&amp;ROUND(H61,2)&amp;" lot, "&amp;I61&amp;" "&amp;ROUND(K61,2)&amp;" lot. "&amp;"Start remains "&amp;ROUND(M61,2)&amp;" lot. "&amp;"Total Main = "&amp;N61&amp;"%, "&amp;"Total Opposite = "&amp;O61&amp;"%, "&amp;"Skew = "&amp;P61&amp;"%, "&amp;"Status = "&amp;T61&amp;"."</f>
+        <f>"Level "&amp;A61&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C61&amp;" "&amp;ROUND(E61,2)&amp;" lot, "&amp;F61&amp;" "&amp;ROUND(H61,2)&amp;" lot, "&amp;I61&amp;" "&amp;ROUND(K61,2)&amp;" lot. Start remains "&amp;ROUND(M61,2)&amp;" lot. Total Main = "&amp;N61&amp;"%, Total Opposite = "&amp;O61&amp;"%, Skew = "&amp;P61&amp;"%, Status = "&amp;T61&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -3342,7 +3365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3370,15 +3393,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Down L1 Close%</t>
+          <t>Down Q26</t>
         </is>
       </c>
       <c r="B2">
-        <f>Calculator!N26</f>
+        <f>Calculator!Q26</f>
         <v/>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
@@ -3388,15 +3411,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Down L2 Close%</t>
+          <t>Down T26</t>
         </is>
       </c>
       <c r="B3">
-        <f>Calculator!N27</f>
+        <f>Calculator!T26</f>
         <v/>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="D3">
         <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
@@ -3406,15 +3429,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Down Final Main</t>
+          <t>Down U26</t>
         </is>
       </c>
       <c r="B4">
-        <f>Calculator!T30</f>
+        <f>Calculator!U26</f>
         <v/>
       </c>
       <c r="C4" t="n">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="D4">
         <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
@@ -3424,15 +3447,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Down Final Opp</t>
+          <t>Down V26</t>
         </is>
       </c>
       <c r="B5">
-        <f>Calculator!U30</f>
+        <f>Calculator!V26</f>
         <v/>
       </c>
       <c r="C5" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
@@ -3442,11 +3465,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Down Final Skew</t>
+          <t>Down Q30</t>
         </is>
       </c>
       <c r="B6">
-        <f>Calculator!V30</f>
+        <f>Calculator!Q30</f>
         <v/>
       </c>
       <c r="C6" t="n">
@@ -3460,15 +3483,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Up L1 Close%</t>
+          <t>Down T30</t>
         </is>
       </c>
       <c r="B7">
-        <f>Calculator!N35</f>
+        <f>Calculator!T30</f>
         <v/>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="D7">
         <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
@@ -3478,15 +3501,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Up L2 Close%</t>
+          <t>Down U30</t>
         </is>
       </c>
       <c r="B8">
-        <f>Calculator!N36</f>
+        <f>Calculator!U30</f>
         <v/>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D8">
         <f>IF(ABS(B8-C8)&lt;0.000001,"PASS","FAIL")</f>
@@ -3496,15 +3519,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Up Final Main</t>
+          <t>Down V30</t>
         </is>
       </c>
       <c r="B9">
-        <f>Calculator!T39</f>
+        <f>Calculator!V30</f>
         <v/>
       </c>
       <c r="C9" t="n">
-        <v>165</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <f>IF(ABS(B9-C9)&lt;0.000001,"PASS","FAIL")</f>
@@ -3514,15 +3537,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Up Final Opp</t>
+          <t>Up Q35</t>
         </is>
       </c>
       <c r="B10">
-        <f>Calculator!U39</f>
+        <f>Calculator!Q35</f>
         <v/>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
@@ -3532,15 +3555,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Up Final Skew</t>
+          <t>Up T35</t>
         </is>
       </c>
       <c r="B11">
-        <f>Calculator!V39</f>
+        <f>Calculator!T35</f>
         <v/>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="D11">
         <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
@@ -3550,15 +3573,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Human Sum Big Lots</t>
+          <t>Up U35</t>
         </is>
       </c>
       <c r="B12">
-        <f>HumanSummary!B11</f>
+        <f>Calculator!U35</f>
         <v/>
       </c>
       <c r="C12" t="n">
-        <v>1.55</v>
+        <v>130</v>
       </c>
       <c r="D12">
         <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
@@ -3568,15 +3591,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Human Sum Small Lots</t>
+          <t>Up V35</t>
         </is>
       </c>
       <c r="B13">
-        <f>HumanSummary!B12</f>
+        <f>Calculator!V35</f>
         <v/>
       </c>
       <c r="C13" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f>IF(ABS(B13-C13)&lt;0.000001,"PASS","FAIL")</f>
@@ -3586,15 +3609,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Human Sum Close Lots</t>
+          <t>Up Q39</t>
         </is>
       </c>
       <c r="B14">
-        <f>HumanSummary!B13</f>
+        <f>Calculator!Q39</f>
         <v/>
       </c>
       <c r="C14" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <f>IF(ABS(B14-C14)&lt;0.000001,"PASS","FAIL")</f>
@@ -3604,15 +3627,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Human Final Start Remaining Lot</t>
+          <t>Up T39</t>
         </is>
       </c>
       <c r="B15">
-        <f>HumanSummary!B14</f>
+        <f>Calculator!T39</f>
         <v/>
       </c>
       <c r="C15" t="n">
-        <v>0.1</v>
+        <v>165</v>
       </c>
       <c r="D15">
         <f>IF(ABS(B15-C15)&lt;0.000001,"PASS","FAIL")</f>
@@ -3622,191 +3645,173 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Human Final Status</t>
+          <t>Up U39</t>
         </is>
       </c>
       <c r="B16">
-        <f>HumanSummary!B21</f>
-        <v/>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+        <f>Calculator!U39</f>
+        <v/>
+      </c>
+      <c r="C16" t="n">
+        <v>175</v>
       </c>
       <c r="D16">
-        <f>IF(B16=C16,"PASS","FAIL")</f>
+        <f>IF(ABS(B16-C16)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Human Level 1 Big Action</t>
+          <t>Up V39</t>
         </is>
       </c>
       <c r="B17">
-        <f>HumanSummary!C3</f>
-        <v/>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Open Big BUY</t>
-        </is>
+        <f>Calculator!V39</f>
+        <v/>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
       </c>
       <c r="D17">
-        <f>IF(B17=C17,"PASS","FAIL")</f>
+        <f>IF(ABS(B17-C17)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Human Level 1 Small Action</t>
+          <t>Summary Main</t>
         </is>
       </c>
       <c r="B18">
-        <f>HumanSummary!F3</f>
-        <v/>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Open Small SELL</t>
-        </is>
+        <f>Calculator!B44</f>
+        <v/>
+      </c>
+      <c r="C18" t="n">
+        <v>165</v>
       </c>
       <c r="D18">
-        <f>IF(B18=C18,"PASS","FAIL")</f>
+        <f>IF(ABS(B18-C18)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Human Level 1 Close Action</t>
+          <t>Summary Opp</t>
         </is>
       </c>
       <c r="B19">
-        <f>HumanSummary!I3</f>
-        <v/>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Close Start BUY</t>
-        </is>
+        <f>Calculator!B45</f>
+        <v/>
+      </c>
+      <c r="C19" t="n">
+        <v>175</v>
       </c>
       <c r="D19">
-        <f>IF(B19=C19,"PASS","FAIL")</f>
+        <f>IF(ABS(B19-C19)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Human UP Big Action</t>
+          <t>Summary Skew</t>
         </is>
       </c>
       <c r="B20">
-        <f>IF(Calculator!B6="UP",HumanSummary!C3,"SKIP")</f>
-        <v/>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Open Big SELL</t>
-        </is>
+        <f>Calculator!B46</f>
+        <v/>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
       </c>
       <c r="D20">
-        <f>IF(B20=C20,"PASS","FAIL")</f>
+        <f>IF(ABS(B20-C20)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Summary Final System Status</t>
+          <t>Human L1 Start Remaining Lot</t>
         </is>
       </c>
       <c r="B21">
-        <f>Calculator!B52</f>
-        <v/>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+        <f>HumanSummary!M3</f>
+        <v/>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4</v>
       </c>
       <c r="D21">
-        <f>IF(B21=C21,"PASS","FAIL")</f>
+        <f>IF(ABS(B21-C21)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Human Comment L1 is text</t>
+          <t>Human L1 Total Main</t>
         </is>
       </c>
       <c r="B22">
-        <f>IF(LEN(HumanSummary!U3)&gt;0,"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>HumanSummary!N3</f>
+        <v/>
+      </c>
+      <c r="C22" t="n">
+        <v>130</v>
       </c>
       <c r="D22">
-        <f>IF(B22=C22,"PASS","FAIL")</f>
+        <f>IF(ABS(B22-C22)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Human Comment L1 no #VALUE</t>
+          <t>Human L1 Total Opp</t>
         </is>
       </c>
       <c r="B23">
-        <f>IF(ISNUMBER(SEARCH("#VALUE",HumanSummary!U3)),"FAIL","PASS")</f>
-        <v/>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>HumanSummary!O3</f>
+        <v/>
+      </c>
+      <c r="C23" t="n">
+        <v>130</v>
       </c>
       <c r="D23">
-        <f>IF(B23=C23,"PASS","FAIL")</f>
+        <f>IF(ABS(B23-C23)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Human Comment L1 no #ИМЯ</t>
+          <t>Human Sum Big</t>
         </is>
       </c>
       <c r="B24">
-        <f>IF(ISNUMBER(SEARCH("#ИМЯ",HumanSummary!U3)),"FAIL","PASS")</f>
-        <v/>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>HumanSummary!B11</f>
+        <v/>
+      </c>
+      <c r="C24" t="n">
+        <v>1.55</v>
       </c>
       <c r="D24">
-        <f>IF(B24=C24,"PASS","FAIL")</f>
+        <f>IF(ABS(B24-C24)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Human Comment L1 has Open Big BUY</t>
+          <t>Human Comment contains Total Main = 130</t>
         </is>
       </c>
       <c r="B25">
-        <f>IF(ISNUMBER(SEARCH("Open Big BUY",HumanSummary!U3)),"PASS","FAIL")</f>
+        <f>IF(ISNUMBER(SEARCH("Total Main = 130",HumanSummary!U3)),"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="C25" t="inlineStr">
@@ -3816,86 +3821,6 @@
       </c>
       <c r="D25">
         <f>IF(B25=C25,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Human Comment L1 has Close Start BUY</t>
-        </is>
-      </c>
-      <c r="B26">
-        <f>IF(ISNUMBER(SEARCH("Close Start BUY",HumanSummary!U3)),"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D26">
-        <f>IF(B26=C26,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Human Comment L1 has Status</t>
-        </is>
-      </c>
-      <c r="B27">
-        <f>IF(ISNUMBER(SEARCH("Status =",HumanSummary!U3)),"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D27">
-        <f>IF(B27=C27,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Human Comment L5 is text</t>
-        </is>
-      </c>
-      <c r="B28">
-        <f>IF(LEN(HumanSummary!U7)&gt;0,"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D28">
-        <f>IF(B28=C28,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Human Comment L5 no error</t>
-        </is>
-      </c>
-      <c r="B29">
-        <f>IF(OR(ISNUMBER(SEARCH("#VALUE",HumanSummary!U7)),ISNUMBER(SEARCH("#ИМЯ",HumanSummary!U7)),ISNUMBER(SEARCH("#NAME",HumanSummary!U7))),"FAIL","PASS")</f>
-        <v/>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D29">
-        <f>IF(B29=C29,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -3910,76 +3835,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Инструкция</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. Ввести StartLot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2. Проверить StepPoints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3. Выбрать Direction DOWN или UP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4. При необходимости изменить Level Grid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5. Смотреть Main Table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6. Проверить Summary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7. Смотреть Human Summary: Big=основная rescue-позиция, Small=встречная защитная, Close=частичное закрытие стартовой позиции.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8. Start Remaining = остаток стартовой позиции, Total Main/Opp = баланс сторон, Skew = защитный перевес.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9. Если Status = OK — сетка безопасна по математике.</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4004,62 +3866,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Это простой калькулятор skew-компрессии минусового замка.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Big — крупный ордер на основной стороне.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Small — малый ордер на противоположной стороне.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Safe Close — безопасное частичное закрытие стартового ордера.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Total Main — суммарный объём основной стороны.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total Opposite — суммарный объём противоположной стороны.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Skew — защитный перевес Opposite над Main.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Как читать Human Summary: Big/Small/Close показывают действия по уровню; Start Remaining — остаток стартовой позиции; Status отражает безопасность уровня.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Calculator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HumanSummary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tests" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Manual" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Калькулятор" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="РИСК_АНАЛИЗ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Тесты" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Руководство" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Описание" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,6 +136,561 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>График нагрузки на баланс</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'РИСК_АНАЛИЗ'!B2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$B$3:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>График роста объема</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'РИСК_АНАЛИЗ'!D2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$D$3:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>График роста маржи</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'РИСК_АНАЛИЗ'!C2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$C$3:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>График просадки</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'РИСК_АНАЛИЗ'!E2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$E$3:$E$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>График Margin Level</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'РИСК_АНАЛИЗ'!F2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'РИСК_АНАЛИЗ'!$F$3:$F$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,106 +982,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z61"/>
+  <dimension ref="A1:Z51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PARAMETERS</t>
+          <t>ПАРАМЕТРЫ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ПАРАМЕТРЫ РИСКА</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>StartLot</t>
+          <t>СтартЛот</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>StepPoints</t>
+          <t>ШагПункты</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Плечо</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MaxLevels</t>
+          <t>МаксУровни</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>РазмерКонтракта</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LotStep</t>
+          <t>ШагЛота</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.01</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ЦенаИнструмента</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Направление</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>СтоимостьПунктаНа1Лот</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UseRounding</t>
+          <t>Округлять</t>
         </is>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>МаксДвижениеПротив(пункты)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BigRoundMode</t>
+          <t>РежимBig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DOWN</t>
-        </is>
+          <t>ВНИЗ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>УровеньStopOut%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SmallRoundMode</t>
+          <t>РежимSmall</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UP</t>
-        </is>
+          <t>ВВЕРХ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>УровеньMarginCall%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CloseRoundMode</t>
+          <t>РежимClose</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -538,17 +1162,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PointValue</t>
+          <t>СтоимостьПункта</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Спред</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -558,7 +1182,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Комиссия</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -568,14 +1192,19 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LEVEL GRID</t>
+          <t>СЕТКА УРОВНЕЙ</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>РИСКИ И МАРЖА</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Уровень</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -590,12 +1219,97 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>TargetSkew %</t>
+          <t>Уровень</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ManualClose %</t>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Общий Main Lot</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Общий Opposite Lot</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Общий открытый объём</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Чистый перекос</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Маржа на 1 лот</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Требуемая маржа</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузка на баланс %</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Макс движение против</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Плавающая просадка $</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Баланс после просадки</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Equity после просадки</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Свободная маржа</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Margin Level %</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Риск Margin Call</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Риск StopOut</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Статус риска</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
         </is>
       </c>
     </row>
@@ -610,9 +1324,80 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>IF($B$6="DOWN",W26,W35)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF($B$6="DOWN",X26,X35)</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>F18+G18</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>ABS(F18-G18)</f>
+        <v/>
+      </c>
+      <c r="J18">
+        <f>$E$4*$E$5/$E$3</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>H18*J18</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>K18/$E$2*100</f>
+        <v/>
+      </c>
+      <c r="M18">
+        <f>$E$7</f>
+        <v/>
+      </c>
+      <c r="N18">
+        <f>I18*$E$6*$E$7</f>
+        <v/>
+      </c>
+      <c r="O18">
+        <f>$E$2-N18</f>
+        <v/>
+      </c>
+      <c r="P18">
+        <f>O18</f>
+        <v/>
+      </c>
+      <c r="Q18">
+        <f>P18-K18</f>
+        <v/>
+      </c>
+      <c r="R18">
+        <f>IF(K18=0,0,P18/K18*100)</f>
+        <v/>
+      </c>
+      <c r="S18">
+        <f>IF(R18&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="T18">
+        <f>IF(R18&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="U18">
+        <f>IF(L18&lt;30,"OK",IF(L18&lt;50,"WARNING",IF(L18&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="V18">
+        <f>"Уровень "&amp;D18&amp;". Объем="&amp;ROUND(H18,2)&amp;" лот. Маржа="&amp;ROUND(K18,2)&amp;"$. Нагрузка="&amp;ROUND(L18,1)&amp;"%. Просадка="&amp;ROUND(N18,2)&amp;"$. Статус="&amp;U18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -625,9 +1410,80 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>IF($B$6="DOWN",W27,W36)</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>IF($B$6="DOWN",X27,X36)</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>F19+G19</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>ABS(F19-G19)</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>$E$4*$E$5/$E$3</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>H19*J19</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>K19/$E$2*100</f>
+        <v/>
+      </c>
+      <c r="M19">
+        <f>$E$7</f>
+        <v/>
+      </c>
+      <c r="N19">
+        <f>I19*$E$6*$E$7</f>
+        <v/>
+      </c>
+      <c r="O19">
+        <f>$E$2-N19</f>
+        <v/>
+      </c>
+      <c r="P19">
+        <f>O19</f>
+        <v/>
+      </c>
+      <c r="Q19">
+        <f>P19-K19</f>
+        <v/>
+      </c>
+      <c r="R19">
+        <f>IF(K19=0,0,P19/K19*100)</f>
+        <v/>
+      </c>
+      <c r="S19">
+        <f>IF(R19&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="T19">
+        <f>IF(R19&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="U19">
+        <f>IF(L19&lt;30,"OK",IF(L19&lt;50,"WARNING",IF(L19&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="V19">
+        <f>"Уровень "&amp;D19&amp;". Объем="&amp;ROUND(H19,2)&amp;" лот. Маржа="&amp;ROUND(K19,2)&amp;"$. Нагрузка="&amp;ROUND(L19,1)&amp;"%. Просадка="&amp;ROUND(N19,2)&amp;"$. Статус="&amp;U19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -640,9 +1496,80 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>IF($B$6="DOWN",W28,W37)</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF($B$6="DOWN",X28,X37)</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>F20+G20</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>ABS(F20-G20)</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>$E$4*$E$5/$E$3</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>H20*J20</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>K20/$E$2*100</f>
+        <v/>
+      </c>
+      <c r="M20">
+        <f>$E$7</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>I20*$E$6*$E$7</f>
+        <v/>
+      </c>
+      <c r="O20">
+        <f>$E$2-N20</f>
+        <v/>
+      </c>
+      <c r="P20">
+        <f>O20</f>
+        <v/>
+      </c>
+      <c r="Q20">
+        <f>P20-K20</f>
+        <v/>
+      </c>
+      <c r="R20">
+        <f>IF(K20=0,0,P20/K20*100)</f>
+        <v/>
+      </c>
+      <c r="S20">
+        <f>IF(R20&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="T20">
+        <f>IF(R20&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="U20">
+        <f>IF(L20&lt;30,"OK",IF(L20&lt;50,"WARNING",IF(L20&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="V20">
+        <f>"Уровень "&amp;D20&amp;". Объем="&amp;ROUND(H20,2)&amp;" лот. Маржа="&amp;ROUND(K20,2)&amp;"$. Нагрузка="&amp;ROUND(L20,1)&amp;"%. Просадка="&amp;ROUND(N20,2)&amp;"$. Статус="&amp;U20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -655,9 +1582,80 @@
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>IF($B$6="DOWN",W29,W38)</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>IF($B$6="DOWN",X29,X38)</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>F21+G21</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>ABS(F21-G21)</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>$E$4*$E$5/$E$3</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>H21*J21</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>K21/$E$2*100</f>
+        <v/>
+      </c>
+      <c r="M21">
+        <f>$E$7</f>
+        <v/>
+      </c>
+      <c r="N21">
+        <f>I21*$E$6*$E$7</f>
+        <v/>
+      </c>
+      <c r="O21">
+        <f>$E$2-N21</f>
+        <v/>
+      </c>
+      <c r="P21">
+        <f>O21</f>
+        <v/>
+      </c>
+      <c r="Q21">
+        <f>P21-K21</f>
+        <v/>
+      </c>
+      <c r="R21">
+        <f>IF(K21=0,0,P21/K21*100)</f>
+        <v/>
+      </c>
+      <c r="S21">
+        <f>IF(R21&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="T21">
+        <f>IF(R21&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="U21">
+        <f>IF(L21&lt;30,"OK",IF(L21&lt;50,"WARNING",IF(L21&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="V21">
+        <f>"Уровень "&amp;D21&amp;". Объем="&amp;ROUND(H21,2)&amp;" лот. Маржа="&amp;ROUND(K21,2)&amp;"$. Нагрузка="&amp;ROUND(L21,1)&amp;"%. Просадка="&amp;ROUND(N21,2)&amp;"$. Статус="&amp;U21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -670,21 +1668,92 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>IF($B$6="DOWN",W30,W39)</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF($B$6="DOWN",X30,X39)</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>F22+G22</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>ABS(F22-G22)</f>
+        <v/>
+      </c>
+      <c r="J22">
+        <f>$E$4*$E$5/$E$3</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>H22*J22</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>K22/$E$2*100</f>
+        <v/>
+      </c>
+      <c r="M22">
+        <f>$E$7</f>
+        <v/>
+      </c>
+      <c r="N22">
+        <f>I22*$E$6*$E$7</f>
+        <v/>
+      </c>
+      <c r="O22">
+        <f>$E$2-N22</f>
+        <v/>
+      </c>
+      <c r="P22">
+        <f>O22</f>
+        <v/>
+      </c>
+      <c r="Q22">
+        <f>P22-K22</f>
+        <v/>
+      </c>
+      <c r="R22">
+        <f>IF(K22=0,0,P22/K22*100)</f>
+        <v/>
+      </c>
+      <c r="S22">
+        <f>IF(R22&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="T22">
+        <f>IF(R22&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="U22">
+        <f>IF(L22&lt;30,"OK",IF(L22&lt;50,"WARNING",IF(L22&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="V22">
+        <f>"Уровень "&amp;D22&amp;". Объем="&amp;ROUND(H22,2)&amp;" лот. Маржа="&amp;ROUND(K22,2)&amp;"$. Нагрузка="&amp;ROUND(L22,1)&amp;"%. Просадка="&amp;ROUND(N22,2)&amp;"$. Статус="&amp;U22</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DOWN CALCULATION</t>
+          <t>РАСЧЕТ DOWN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Уровень</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -699,92 +1768,92 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>TargetSkew %</t>
+          <t>ЦелевойSkew %</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ManualClose %</t>
+          <t>РучноеЗакрытие %</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Big Lot Raw</t>
+          <t>BigЛот</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Big Lot Rounded</t>
+          <t>BigОкругл</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Small Lot Raw</t>
+          <t>SmallЛот</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Small Lot Rounded</t>
+          <t>SmallОкругл</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Start Before %</t>
+          <t>СтартДо %</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Total Main Before %</t>
+          <t>MainДо %</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Total Opp After %</t>
+          <t>OppДо %</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Auto Close %</t>
+          <t>АвтоЗакрытие %</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Final Close %</t>
+          <t>ИтогЗакрытие %</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Close Lot Raw</t>
+          <t>ЗакрытиеЛот</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Close Lot Rounded</t>
+          <t>ЗакрытиеЛотОкругл</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Start After %</t>
+          <t>СтартПосле %</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Sum Big %</t>
+          <t>СуммаBig %</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Sum Small %</t>
+          <t>СуммаSmall %</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>Total Main %</t>
+          <t>ИтогMain %</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>Total Opp %</t>
+          <t>ИтогOpp %</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -794,22 +1863,22 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>Rounded Total Main Lot</t>
+          <t>ОкруглMainЛот</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>Rounded Total Opp Lot</t>
+          <t>ОкруглOppЛот</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>Rounded Skew Lot</t>
+          <t>ОкруглSkewЛот</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Статус</t>
         </is>
       </c>
     </row>
@@ -915,7 +1984,7 @@
         <v/>
       </c>
       <c r="Z26">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B26&lt;C26,"ERROR",IF(AND(E26&lt;&gt;"",E26&gt;J26),"ERROR",IF(T26&gt;U26,"ERROR",IF(W26&gt;X26,"ERROR",IF(AND(B26&gt;0,G26=0),"ERROR",IF(AND(C26&gt;0,I26=0),"ERROR",IF(AND(D26&gt;0,ROUND(Y26,6)&lt;ROUND($B$2*D26/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T26&gt;U26,"ERROR",IF(AND(D26&gt;0,ROUND(Y26,6)&lt;ROUND($B$2*D26/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -1021,7 +2090,7 @@
         <v/>
       </c>
       <c r="Z27">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B27&lt;C27,"ERROR",IF(AND(E27&lt;&gt;"",E27&gt;J27),"ERROR",IF(T27&gt;U27,"ERROR",IF(W27&gt;X27,"ERROR",IF(AND(B27&gt;0,G27=0),"ERROR",IF(AND(C27&gt;0,I27=0),"ERROR",IF(AND(D27&gt;0,ROUND(Y27,6)&lt;ROUND($B$2*D27/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T27&gt;U27,"ERROR",IF(AND(D27&gt;0,ROUND(Y27,6)&lt;ROUND($B$2*D27/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -1127,7 +2196,7 @@
         <v/>
       </c>
       <c r="Z28">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B28&lt;C28,"ERROR",IF(AND(E28&lt;&gt;"",E28&gt;J28),"ERROR",IF(T28&gt;U28,"ERROR",IF(W28&gt;X28,"ERROR",IF(AND(B28&gt;0,G28=0),"ERROR",IF(AND(C28&gt;0,I28=0),"ERROR",IF(AND(D28&gt;0,ROUND(Y28,6)&lt;ROUND($B$2*D28/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T28&gt;U28,"ERROR",IF(AND(D28&gt;0,ROUND(Y28,6)&lt;ROUND($B$2*D28/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -1233,7 +2302,7 @@
         <v/>
       </c>
       <c r="Z29">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B29&lt;C29,"ERROR",IF(AND(E29&lt;&gt;"",E29&gt;J29),"ERROR",IF(T29&gt;U29,"ERROR",IF(W29&gt;X29,"ERROR",IF(AND(B29&gt;0,G29=0),"ERROR",IF(AND(C29&gt;0,I29=0),"ERROR",IF(AND(D29&gt;0,ROUND(Y29,6)&lt;ROUND($B$2*D29/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T29&gt;U29,"ERROR",IF(AND(D29&gt;0,ROUND(Y29,6)&lt;ROUND($B$2*D29/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -1339,21 +2408,21 @@
         <v/>
       </c>
       <c r="Z30">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B30&lt;C30,"ERROR",IF(AND(E30&lt;&gt;"",E30&gt;J30),"ERROR",IF(T30&gt;U30,"ERROR",IF(W30&gt;X30,"ERROR",IF(AND(B30&gt;0,G30=0),"ERROR",IF(AND(C30&gt;0,I30=0),"ERROR",IF(AND(D30&gt;0,ROUND(Y30,6)&lt;ROUND($B$2*D30/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T30&gt;U30,"ERROR",IF(AND(D30&gt;0,ROUND(Y30,6)&lt;ROUND($B$2*D30/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>UP CALCULATION</t>
+          <t>РАСЧЕТ UP</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Уровень</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1368,92 +2437,92 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>TargetSkew %</t>
+          <t>ЦелевойSkew %</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ManualClose %</t>
+          <t>РучноеЗакрытие %</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Big Lot Raw</t>
+          <t>BigЛот</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Big Lot Rounded</t>
+          <t>BigОкругл</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Small Lot Raw</t>
+          <t>SmallЛот</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Small Lot Rounded</t>
+          <t>SmallОкругл</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Start Before %</t>
+          <t>СтартДо %</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Total Main Before %</t>
+          <t>MainДо %</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Total Opp After %</t>
+          <t>OppДо %</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Auto Close %</t>
+          <t>АвтоЗакрытие %</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Final Close %</t>
+          <t>ИтогЗакрытие %</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Close Lot Raw</t>
+          <t>ЗакрытиеЛот</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Close Lot Rounded</t>
+          <t>ЗакрытиеЛотОкругл</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Start After %</t>
+          <t>СтартПосле %</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Sum Big %</t>
+          <t>СуммаBig %</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Sum Small %</t>
+          <t>СуммаSmall %</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Total Main %</t>
+          <t>ИтогMain %</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>Total Opp %</t>
+          <t>ИтогOpp %</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -1463,22 +2532,22 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>Rounded Total Main Lot</t>
+          <t>ОкруглMainЛот</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>Rounded Total Opp Lot</t>
+          <t>ОкруглOppЛот</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>Rounded Skew Lot</t>
+          <t>ОкруглSkewЛот</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Статус</t>
         </is>
       </c>
     </row>
@@ -1584,7 +2653,7 @@
         <v/>
       </c>
       <c r="Z35">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B35&lt;C35,"ERROR",IF(AND(E35&lt;&gt;"",E35&gt;J35),"ERROR",IF(T35&gt;U35,"ERROR",IF(W35&gt;X35,"ERROR",IF(AND(B35&gt;0,G35=0),"ERROR",IF(AND(C35&gt;0,I35=0),"ERROR",IF(AND(D35&gt;0,ROUND(Y35,6)&lt;ROUND($B$2*D35/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T35&gt;U35,"ERROR",IF(AND(D35&gt;0,ROUND(Y35,6)&lt;ROUND($B$2*D35/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -1690,7 +2759,7 @@
         <v/>
       </c>
       <c r="Z36">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B36&lt;C36,"ERROR",IF(AND(E36&lt;&gt;"",E36&gt;J36),"ERROR",IF(T36&gt;U36,"ERROR",IF(W36&gt;X36,"ERROR",IF(AND(B36&gt;0,G36=0),"ERROR",IF(AND(C36&gt;0,I36=0),"ERROR",IF(AND(D36&gt;0,ROUND(Y36,6)&lt;ROUND($B$2*D36/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T36&gt;U36,"ERROR",IF(AND(D36&gt;0,ROUND(Y36,6)&lt;ROUND($B$2*D36/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -1796,7 +2865,7 @@
         <v/>
       </c>
       <c r="Z37">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B37&lt;C37,"ERROR",IF(AND(E37&lt;&gt;"",E37&gt;J37),"ERROR",IF(T37&gt;U37,"ERROR",IF(W37&gt;X37,"ERROR",IF(AND(B37&gt;0,G37=0),"ERROR",IF(AND(C37&gt;0,I37=0),"ERROR",IF(AND(D37&gt;0,ROUND(Y37,6)&lt;ROUND($B$2*D37/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T37&gt;U37,"ERROR",IF(AND(D37&gt;0,ROUND(Y37,6)&lt;ROUND($B$2*D37/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -1902,7 +2971,7 @@
         <v/>
       </c>
       <c r="Z38">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B38&lt;C38,"ERROR",IF(AND(E38&lt;&gt;"",E38&gt;J38),"ERROR",IF(T38&gt;U38,"ERROR",IF(W38&gt;X38,"ERROR",IF(AND(B38&gt;0,G38=0),"ERROR",IF(AND(C38&gt;0,I38=0),"ERROR",IF(AND(D38&gt;0,ROUND(Y38,6)&lt;ROUND($B$2*D38/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T38&gt;U38,"ERROR",IF(AND(D38&gt;0,ROUND(Y38,6)&lt;ROUND($B$2*D38/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
@@ -2008,21 +3077,21 @@
         <v/>
       </c>
       <c r="Z39">
-        <f>IF(OR($B$2&lt;=0,$B$5&lt;=0,$B$4&lt;1,NOT(OR($B$6="DOWN",$B$6="UP"))),"ERROR",IF(B39&lt;C39,"ERROR",IF(AND(E39&lt;&gt;"",E39&gt;J39),"ERROR",IF(T39&gt;U39,"ERROR",IF(W39&gt;X39,"ERROR",IF(AND(B39&gt;0,G39=0),"ERROR",IF(AND(C39&gt;0,I39=0),"ERROR",IF(AND(D39&gt;0,ROUND(Y39,6)&lt;ROUND($B$2*D39/100,6)),"WARNING","OK"))))))))</f>
+        <f>IF(T39&gt;U39,"ERROR",IF(AND(D39&gt;0,ROUND(Y39,6)&lt;ROUND($B$2*D39/100,6)),"WARNING","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>SUMMARY</t>
+          <t>ИТОГИ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Selected Direction</t>
+          <t>ВыбранноеНаправление</t>
         </is>
       </c>
       <c r="B43">
@@ -2033,7 +3102,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Final Total Main %</t>
+          <t>ИтогMain %</t>
         </is>
       </c>
       <c r="B44">
@@ -2044,7 +3113,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Final Total Opposite %</t>
+          <t>ИтогOpp %</t>
         </is>
       </c>
       <c r="B45">
@@ -2055,7 +3124,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Final Skew %</t>
+          <t>ИтогSkew %</t>
         </is>
       </c>
       <c r="B46">
@@ -2066,7 +3135,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Final Start Remaining %</t>
+          <t>ИтогСтартОстаток %</t>
         </is>
       </c>
       <c r="B47">
@@ -2077,7 +3146,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Final Rounded Main Lot</t>
+          <t>ИтогОкруглMain</t>
         </is>
       </c>
       <c r="B48">
@@ -2088,7 +3157,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Final Rounded Opp Lot</t>
+          <t>ИтогОкруглOpp</t>
         </is>
       </c>
       <c r="B49">
@@ -2099,7 +3168,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Final Rounded Skew Lot</t>
+          <t>ИтогОкруглSkew</t>
         </is>
       </c>
       <c r="B50">
@@ -2110,561 +3179,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Final Rounded Status</t>
+          <t>ИтогСтатус</t>
         </is>
       </c>
       <c r="B51">
         <f>IF(B6="DOWN",Z30,Z39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Final System Status</t>
-        </is>
-      </c>
-      <c r="B52">
-        <f>IF(B6="DOWN",IF(COUNTIF(Z26:Z30,"ERROR")&gt;0,"ERROR",IF(COUNTIF(Z26:Z30,"WARNING")&gt;0,"WARNING","OK")),IF(COUNTIF(Z35:Z39,"ERROR")&gt;0,"ERROR",IF(COUNTIF(Z35:Z39,"WARNING")&gt;0,"WARNING","OK")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>HUMAN-READABLE LEVEL SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Action Big</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Big %</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Big Lot</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Action Small</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Small %</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Small Lot</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Close Action</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Close %</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Close Lot</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Start Remaining %</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Start Remaining Lot</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Total Main %</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Total Opposite %</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>Skew %</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>Rounded Main Lot</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>Rounded Opp Lot</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>Rounded Skew Lot</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>Human Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>1</v>
-      </c>
-      <c r="B57">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="C57">
-        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
-        <v/>
-      </c>
-      <c r="D57">
-        <f>IF($B$6="DOWN",B26,B35)</f>
-        <v/>
-      </c>
-      <c r="E57">
-        <f>IF($B$6="DOWN",G26,G35)</f>
-        <v/>
-      </c>
-      <c r="F57">
-        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
-        <v/>
-      </c>
-      <c r="G57">
-        <f>IF($B$6="DOWN",C26,C35)</f>
-        <v/>
-      </c>
-      <c r="H57">
-        <f>IF($B$6="DOWN",I26,I35)</f>
-        <v/>
-      </c>
-      <c r="I57">
-        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
-        <v/>
-      </c>
-      <c r="J57">
-        <f>IF($B$6="DOWN",N26,N35)</f>
-        <v/>
-      </c>
-      <c r="K57">
-        <f>IF($B$6="DOWN",P26,P35)</f>
-        <v/>
-      </c>
-      <c r="L57">
-        <f>IF($B$6="DOWN",Q26,Q35)</f>
-        <v/>
-      </c>
-      <c r="M57">
-        <f>$B$2*L57/100</f>
-        <v/>
-      </c>
-      <c r="N57">
-        <f>IF($B$6="DOWN",T26,T35)</f>
-        <v/>
-      </c>
-      <c r="O57">
-        <f>IF($B$6="DOWN",U26,U35)</f>
-        <v/>
-      </c>
-      <c r="P57">
-        <f>IF($B$6="DOWN",V26,V35)</f>
-        <v/>
-      </c>
-      <c r="Q57">
-        <f>IF($B$6="DOWN",W26,W35)</f>
-        <v/>
-      </c>
-      <c r="R57">
-        <f>IF($B$6="DOWN",X26,X35)</f>
-        <v/>
-      </c>
-      <c r="S57">
-        <f>IF($B$6="DOWN",Y26,Y35)</f>
-        <v/>
-      </c>
-      <c r="T57">
-        <f>IF($B$6="DOWN",Z26,Z35)</f>
-        <v/>
-      </c>
-      <c r="U57">
-        <f>"Level "&amp;A57&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C57&amp;" "&amp;ROUND(E57,2)&amp;" lot, "&amp;F57&amp;" "&amp;ROUND(H57,2)&amp;" lot, "&amp;I57&amp;" "&amp;ROUND(K57,2)&amp;" lot. Start remains "&amp;ROUND(M57,2)&amp;" lot. Total Main = "&amp;N57&amp;"%, Total Opposite = "&amp;O57&amp;"%, Skew = "&amp;P57&amp;"%, Status = "&amp;T57&amp;"."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2</v>
-      </c>
-      <c r="B58">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="C58">
-        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
-        <v/>
-      </c>
-      <c r="D58">
-        <f>IF($B$6="DOWN",B27,B36)</f>
-        <v/>
-      </c>
-      <c r="E58">
-        <f>IF($B$6="DOWN",G27,G36)</f>
-        <v/>
-      </c>
-      <c r="F58">
-        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
-        <v/>
-      </c>
-      <c r="G58">
-        <f>IF($B$6="DOWN",C27,C36)</f>
-        <v/>
-      </c>
-      <c r="H58">
-        <f>IF($B$6="DOWN",I27,I36)</f>
-        <v/>
-      </c>
-      <c r="I58">
-        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
-        <v/>
-      </c>
-      <c r="J58">
-        <f>IF($B$6="DOWN",N27,N36)</f>
-        <v/>
-      </c>
-      <c r="K58">
-        <f>IF($B$6="DOWN",P27,P36)</f>
-        <v/>
-      </c>
-      <c r="L58">
-        <f>IF($B$6="DOWN",Q27,Q36)</f>
-        <v/>
-      </c>
-      <c r="M58">
-        <f>$B$2*L58/100</f>
-        <v/>
-      </c>
-      <c r="N58">
-        <f>IF($B$6="DOWN",T27,T36)</f>
-        <v/>
-      </c>
-      <c r="O58">
-        <f>IF($B$6="DOWN",U27,U36)</f>
-        <v/>
-      </c>
-      <c r="P58">
-        <f>IF($B$6="DOWN",V27,V36)</f>
-        <v/>
-      </c>
-      <c r="Q58">
-        <f>IF($B$6="DOWN",W27,W36)</f>
-        <v/>
-      </c>
-      <c r="R58">
-        <f>IF($B$6="DOWN",X27,X36)</f>
-        <v/>
-      </c>
-      <c r="S58">
-        <f>IF($B$6="DOWN",Y27,Y36)</f>
-        <v/>
-      </c>
-      <c r="T58">
-        <f>IF($B$6="DOWN",Z27,Z36)</f>
-        <v/>
-      </c>
-      <c r="U58">
-        <f>"Level "&amp;A58&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C58&amp;" "&amp;ROUND(E58,2)&amp;" lot, "&amp;F58&amp;" "&amp;ROUND(H58,2)&amp;" lot, "&amp;I58&amp;" "&amp;ROUND(K58,2)&amp;" lot. Start remains "&amp;ROUND(M58,2)&amp;" lot. Total Main = "&amp;N58&amp;"%, Total Opposite = "&amp;O58&amp;"%, Skew = "&amp;P58&amp;"%, Status = "&amp;T58&amp;"."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>3</v>
-      </c>
-      <c r="B59">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="C59">
-        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
-        <v/>
-      </c>
-      <c r="D59">
-        <f>IF($B$6="DOWN",B28,B37)</f>
-        <v/>
-      </c>
-      <c r="E59">
-        <f>IF($B$6="DOWN",G28,G37)</f>
-        <v/>
-      </c>
-      <c r="F59">
-        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
-        <v/>
-      </c>
-      <c r="G59">
-        <f>IF($B$6="DOWN",C28,C37)</f>
-        <v/>
-      </c>
-      <c r="H59">
-        <f>IF($B$6="DOWN",I28,I37)</f>
-        <v/>
-      </c>
-      <c r="I59">
-        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
-        <v/>
-      </c>
-      <c r="J59">
-        <f>IF($B$6="DOWN",N28,N37)</f>
-        <v/>
-      </c>
-      <c r="K59">
-        <f>IF($B$6="DOWN",P28,P37)</f>
-        <v/>
-      </c>
-      <c r="L59">
-        <f>IF($B$6="DOWN",Q28,Q37)</f>
-        <v/>
-      </c>
-      <c r="M59">
-        <f>$B$2*L59/100</f>
-        <v/>
-      </c>
-      <c r="N59">
-        <f>IF($B$6="DOWN",T28,T37)</f>
-        <v/>
-      </c>
-      <c r="O59">
-        <f>IF($B$6="DOWN",U28,U37)</f>
-        <v/>
-      </c>
-      <c r="P59">
-        <f>IF($B$6="DOWN",V28,V37)</f>
-        <v/>
-      </c>
-      <c r="Q59">
-        <f>IF($B$6="DOWN",W28,W37)</f>
-        <v/>
-      </c>
-      <c r="R59">
-        <f>IF($B$6="DOWN",X28,X37)</f>
-        <v/>
-      </c>
-      <c r="S59">
-        <f>IF($B$6="DOWN",Y28,Y37)</f>
-        <v/>
-      </c>
-      <c r="T59">
-        <f>IF($B$6="DOWN",Z28,Z37)</f>
-        <v/>
-      </c>
-      <c r="U59">
-        <f>"Level "&amp;A59&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C59&amp;" "&amp;ROUND(E59,2)&amp;" lot, "&amp;F59&amp;" "&amp;ROUND(H59,2)&amp;" lot, "&amp;I59&amp;" "&amp;ROUND(K59,2)&amp;" lot. Start remains "&amp;ROUND(M59,2)&amp;" lot. Total Main = "&amp;N59&amp;"%, Total Opposite = "&amp;O59&amp;"%, Skew = "&amp;P59&amp;"%, Status = "&amp;T59&amp;"."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>4</v>
-      </c>
-      <c r="B60">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="C60">
-        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
-        <v/>
-      </c>
-      <c r="D60">
-        <f>IF($B$6="DOWN",B29,B38)</f>
-        <v/>
-      </c>
-      <c r="E60">
-        <f>IF($B$6="DOWN",G29,G38)</f>
-        <v/>
-      </c>
-      <c r="F60">
-        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
-        <v/>
-      </c>
-      <c r="G60">
-        <f>IF($B$6="DOWN",C29,C38)</f>
-        <v/>
-      </c>
-      <c r="H60">
-        <f>IF($B$6="DOWN",I29,I38)</f>
-        <v/>
-      </c>
-      <c r="I60">
-        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
-        <v/>
-      </c>
-      <c r="J60">
-        <f>IF($B$6="DOWN",N29,N38)</f>
-        <v/>
-      </c>
-      <c r="K60">
-        <f>IF($B$6="DOWN",P29,P38)</f>
-        <v/>
-      </c>
-      <c r="L60">
-        <f>IF($B$6="DOWN",Q29,Q38)</f>
-        <v/>
-      </c>
-      <c r="M60">
-        <f>$B$2*L60/100</f>
-        <v/>
-      </c>
-      <c r="N60">
-        <f>IF($B$6="DOWN",T29,T38)</f>
-        <v/>
-      </c>
-      <c r="O60">
-        <f>IF($B$6="DOWN",U29,U38)</f>
-        <v/>
-      </c>
-      <c r="P60">
-        <f>IF($B$6="DOWN",V29,V38)</f>
-        <v/>
-      </c>
-      <c r="Q60">
-        <f>IF($B$6="DOWN",W29,W38)</f>
-        <v/>
-      </c>
-      <c r="R60">
-        <f>IF($B$6="DOWN",X29,X38)</f>
-        <v/>
-      </c>
-      <c r="S60">
-        <f>IF($B$6="DOWN",Y29,Y38)</f>
-        <v/>
-      </c>
-      <c r="T60">
-        <f>IF($B$6="DOWN",Z29,Z38)</f>
-        <v/>
-      </c>
-      <c r="U60">
-        <f>"Level "&amp;A60&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C60&amp;" "&amp;ROUND(E60,2)&amp;" lot, "&amp;F60&amp;" "&amp;ROUND(H60,2)&amp;" lot, "&amp;I60&amp;" "&amp;ROUND(K60,2)&amp;" lot. Start remains "&amp;ROUND(M60,2)&amp;" lot. Total Main = "&amp;N60&amp;"%, Total Opposite = "&amp;O60&amp;"%, Skew = "&amp;P60&amp;"%, Status = "&amp;T60&amp;"."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>5</v>
-      </c>
-      <c r="B61">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="C61">
-        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
-        <v/>
-      </c>
-      <c r="D61">
-        <f>IF($B$6="DOWN",B30,B39)</f>
-        <v/>
-      </c>
-      <c r="E61">
-        <f>IF($B$6="DOWN",G30,G39)</f>
-        <v/>
-      </c>
-      <c r="F61">
-        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
-        <v/>
-      </c>
-      <c r="G61">
-        <f>IF($B$6="DOWN",C30,C39)</f>
-        <v/>
-      </c>
-      <c r="H61">
-        <f>IF($B$6="DOWN",I30,I39)</f>
-        <v/>
-      </c>
-      <c r="I61">
-        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
-        <v/>
-      </c>
-      <c r="J61">
-        <f>IF($B$6="DOWN",N30,N39)</f>
-        <v/>
-      </c>
-      <c r="K61">
-        <f>IF($B$6="DOWN",P30,P39)</f>
-        <v/>
-      </c>
-      <c r="L61">
-        <f>IF($B$6="DOWN",Q30,Q39)</f>
-        <v/>
-      </c>
-      <c r="M61">
-        <f>$B$2*L61/100</f>
-        <v/>
-      </c>
-      <c r="N61">
-        <f>IF($B$6="DOWN",T30,T39)</f>
-        <v/>
-      </c>
-      <c r="O61">
-        <f>IF($B$6="DOWN",U30,U39)</f>
-        <v/>
-      </c>
-      <c r="P61">
-        <f>IF($B$6="DOWN",V30,V39)</f>
-        <v/>
-      </c>
-      <c r="Q61">
-        <f>IF($B$6="DOWN",W30,W39)</f>
-        <v/>
-      </c>
-      <c r="R61">
-        <f>IF($B$6="DOWN",X30,X39)</f>
-        <v/>
-      </c>
-      <c r="S61">
-        <f>IF($B$6="DOWN",Y30,Y39)</f>
-        <v/>
-      </c>
-      <c r="T61">
-        <f>IF($B$6="DOWN",Z30,Z39)</f>
-        <v/>
-      </c>
-      <c r="U61">
-        <f>"Level "&amp;A61&amp;": "&amp;IF($B$6="DOWN","price goes DOWN. ","price goes UP. ")&amp;C61&amp;" "&amp;ROUND(E61,2)&amp;" lot, "&amp;F61&amp;" "&amp;ROUND(H61,2)&amp;" lot, "&amp;I61&amp;" "&amp;ROUND(K61,2)&amp;" lot. Start remains "&amp;ROUND(M61,2)&amp;" lot. Total Main = "&amp;N61&amp;"%, Total Opposite = "&amp;O61&amp;"%, Skew = "&amp;P61&amp;"%, Status = "&amp;T61&amp;"."</f>
         <v/>
       </c>
     </row>
@@ -2679,683 +3198,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ИТОГОВЫЙ ЧЕЛОВЕЧЕСКИЙ РАСЧЁТ ВСЕХ УРОВНЕЙ</t>
+          <t>РИСК_АНАЛИЗ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Уровень</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Нагрузка %</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Action Big</t>
+          <t>Маржа $</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Big %</t>
+          <t>Объем лот</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Big Lot</t>
+          <t>Просадка $</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Action Small</t>
+          <t>Margin Level %</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Small %</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Small Lot</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Close Action</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Close %</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Close Lot</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Start Remaining %</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Start Remaining Lot</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Total Main %</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Total Opposite %</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Skew %</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Rounded Main Lot</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Rounded Opp Lot</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>Rounded Skew Lot</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>Human Comment</t>
+          <t>Статус</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <f>Calculator!A57</f>
+        <f>Калькулятор!D18</f>
         <v/>
       </c>
       <c r="B3">
-        <f>Calculator!B57</f>
+        <f>Калькулятор!L18</f>
         <v/>
       </c>
       <c r="C3">
-        <f>Calculator!C57</f>
+        <f>Калькулятор!K18</f>
         <v/>
       </c>
       <c r="D3">
-        <f>Calculator!D57</f>
+        <f>Калькулятор!H18</f>
         <v/>
       </c>
       <c r="E3">
-        <f>Calculator!E57</f>
+        <f>Калькулятор!N18</f>
         <v/>
       </c>
       <c r="F3">
-        <f>Calculator!F57</f>
+        <f>Калькулятор!R18</f>
         <v/>
       </c>
       <c r="G3">
-        <f>Calculator!G57</f>
-        <v/>
-      </c>
-      <c r="H3">
-        <f>Calculator!H57</f>
-        <v/>
-      </c>
-      <c r="I3">
-        <f>Calculator!I57</f>
-        <v/>
-      </c>
-      <c r="J3">
-        <f>Calculator!J57</f>
-        <v/>
-      </c>
-      <c r="K3">
-        <f>Calculator!K57</f>
-        <v/>
-      </c>
-      <c r="L3">
-        <f>Calculator!L57</f>
-        <v/>
-      </c>
-      <c r="M3">
-        <f>Calculator!M57</f>
-        <v/>
-      </c>
-      <c r="N3">
-        <f>Calculator!N57</f>
-        <v/>
-      </c>
-      <c r="O3">
-        <f>Calculator!O57</f>
-        <v/>
-      </c>
-      <c r="P3">
-        <f>Calculator!P57</f>
-        <v/>
-      </c>
-      <c r="Q3">
-        <f>Calculator!Q57</f>
-        <v/>
-      </c>
-      <c r="R3">
-        <f>Calculator!R57</f>
-        <v/>
-      </c>
-      <c r="S3">
-        <f>Calculator!S57</f>
-        <v/>
-      </c>
-      <c r="T3">
-        <f>Calculator!T57</f>
-        <v/>
-      </c>
-      <c r="U3">
-        <f>Calculator!U57</f>
+        <f>Калькулятор!U18</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>Calculator!A58</f>
+        <f>Калькулятор!D19</f>
         <v/>
       </c>
       <c r="B4">
-        <f>Calculator!B58</f>
+        <f>Калькулятор!L19</f>
         <v/>
       </c>
       <c r="C4">
-        <f>Calculator!C58</f>
+        <f>Калькулятор!K19</f>
         <v/>
       </c>
       <c r="D4">
-        <f>Calculator!D58</f>
+        <f>Калькулятор!H19</f>
         <v/>
       </c>
       <c r="E4">
-        <f>Calculator!E58</f>
+        <f>Калькулятор!N19</f>
         <v/>
       </c>
       <c r="F4">
-        <f>Calculator!F58</f>
+        <f>Калькулятор!R19</f>
         <v/>
       </c>
       <c r="G4">
-        <f>Calculator!G58</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>Calculator!H58</f>
-        <v/>
-      </c>
-      <c r="I4">
-        <f>Calculator!I58</f>
-        <v/>
-      </c>
-      <c r="J4">
-        <f>Calculator!J58</f>
-        <v/>
-      </c>
-      <c r="K4">
-        <f>Calculator!K58</f>
-        <v/>
-      </c>
-      <c r="L4">
-        <f>Calculator!L58</f>
-        <v/>
-      </c>
-      <c r="M4">
-        <f>Calculator!M58</f>
-        <v/>
-      </c>
-      <c r="N4">
-        <f>Calculator!N58</f>
-        <v/>
-      </c>
-      <c r="O4">
-        <f>Calculator!O58</f>
-        <v/>
-      </c>
-      <c r="P4">
-        <f>Calculator!P58</f>
-        <v/>
-      </c>
-      <c r="Q4">
-        <f>Calculator!Q58</f>
-        <v/>
-      </c>
-      <c r="R4">
-        <f>Calculator!R58</f>
-        <v/>
-      </c>
-      <c r="S4">
-        <f>Calculator!S58</f>
-        <v/>
-      </c>
-      <c r="T4">
-        <f>Calculator!T58</f>
-        <v/>
-      </c>
-      <c r="U4">
-        <f>Calculator!U58</f>
+        <f>Калькулятор!U19</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>Calculator!A59</f>
+        <f>Калькулятор!D20</f>
         <v/>
       </c>
       <c r="B5">
-        <f>Calculator!B59</f>
+        <f>Калькулятор!L20</f>
         <v/>
       </c>
       <c r="C5">
-        <f>Calculator!C59</f>
+        <f>Калькулятор!K20</f>
         <v/>
       </c>
       <c r="D5">
-        <f>Calculator!D59</f>
+        <f>Калькулятор!H20</f>
         <v/>
       </c>
       <c r="E5">
-        <f>Calculator!E59</f>
+        <f>Калькулятор!N20</f>
         <v/>
       </c>
       <c r="F5">
-        <f>Calculator!F59</f>
+        <f>Калькулятор!R20</f>
         <v/>
       </c>
       <c r="G5">
-        <f>Calculator!G59</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>Calculator!H59</f>
-        <v/>
-      </c>
-      <c r="I5">
-        <f>Calculator!I59</f>
-        <v/>
-      </c>
-      <c r="J5">
-        <f>Calculator!J59</f>
-        <v/>
-      </c>
-      <c r="K5">
-        <f>Calculator!K59</f>
-        <v/>
-      </c>
-      <c r="L5">
-        <f>Calculator!L59</f>
-        <v/>
-      </c>
-      <c r="M5">
-        <f>Calculator!M59</f>
-        <v/>
-      </c>
-      <c r="N5">
-        <f>Calculator!N59</f>
-        <v/>
-      </c>
-      <c r="O5">
-        <f>Calculator!O59</f>
-        <v/>
-      </c>
-      <c r="P5">
-        <f>Calculator!P59</f>
-        <v/>
-      </c>
-      <c r="Q5">
-        <f>Calculator!Q59</f>
-        <v/>
-      </c>
-      <c r="R5">
-        <f>Calculator!R59</f>
-        <v/>
-      </c>
-      <c r="S5">
-        <f>Calculator!S59</f>
-        <v/>
-      </c>
-      <c r="T5">
-        <f>Calculator!T59</f>
-        <v/>
-      </c>
-      <c r="U5">
-        <f>Calculator!U59</f>
+        <f>Калькулятор!U20</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>Calculator!A60</f>
+        <f>Калькулятор!D21</f>
         <v/>
       </c>
       <c r="B6">
-        <f>Calculator!B60</f>
+        <f>Калькулятор!L21</f>
         <v/>
       </c>
       <c r="C6">
-        <f>Calculator!C60</f>
+        <f>Калькулятор!K21</f>
         <v/>
       </c>
       <c r="D6">
-        <f>Calculator!D60</f>
+        <f>Калькулятор!H21</f>
         <v/>
       </c>
       <c r="E6">
-        <f>Calculator!E60</f>
+        <f>Калькулятор!N21</f>
         <v/>
       </c>
       <c r="F6">
-        <f>Calculator!F60</f>
+        <f>Калькулятор!R21</f>
         <v/>
       </c>
       <c r="G6">
-        <f>Calculator!G60</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>Calculator!H60</f>
-        <v/>
-      </c>
-      <c r="I6">
-        <f>Calculator!I60</f>
-        <v/>
-      </c>
-      <c r="J6">
-        <f>Calculator!J60</f>
-        <v/>
-      </c>
-      <c r="K6">
-        <f>Calculator!K60</f>
-        <v/>
-      </c>
-      <c r="L6">
-        <f>Calculator!L60</f>
-        <v/>
-      </c>
-      <c r="M6">
-        <f>Calculator!M60</f>
-        <v/>
-      </c>
-      <c r="N6">
-        <f>Calculator!N60</f>
-        <v/>
-      </c>
-      <c r="O6">
-        <f>Calculator!O60</f>
-        <v/>
-      </c>
-      <c r="P6">
-        <f>Calculator!P60</f>
-        <v/>
-      </c>
-      <c r="Q6">
-        <f>Calculator!Q60</f>
-        <v/>
-      </c>
-      <c r="R6">
-        <f>Calculator!R60</f>
-        <v/>
-      </c>
-      <c r="S6">
-        <f>Calculator!S60</f>
-        <v/>
-      </c>
-      <c r="T6">
-        <f>Calculator!T60</f>
-        <v/>
-      </c>
-      <c r="U6">
-        <f>Calculator!U60</f>
+        <f>Калькулятор!U21</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>Calculator!A61</f>
+        <f>Калькулятор!D22</f>
         <v/>
       </c>
       <c r="B7">
-        <f>Calculator!B61</f>
+        <f>Калькулятор!L22</f>
         <v/>
       </c>
       <c r="C7">
-        <f>Calculator!C61</f>
+        <f>Калькулятор!K22</f>
         <v/>
       </c>
       <c r="D7">
-        <f>Calculator!D61</f>
+        <f>Калькулятор!H22</f>
         <v/>
       </c>
       <c r="E7">
-        <f>Calculator!E61</f>
+        <f>Калькулятор!N22</f>
         <v/>
       </c>
       <c r="F7">
-        <f>Calculator!F61</f>
+        <f>Калькулятор!R22</f>
         <v/>
       </c>
       <c r="G7">
-        <f>Calculator!G61</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>Calculator!H61</f>
-        <v/>
-      </c>
-      <c r="I7">
-        <f>Calculator!I61</f>
-        <v/>
-      </c>
-      <c r="J7">
-        <f>Calculator!J61</f>
-        <v/>
-      </c>
-      <c r="K7">
-        <f>Calculator!K61</f>
-        <v/>
-      </c>
-      <c r="L7">
-        <f>Calculator!L61</f>
-        <v/>
-      </c>
-      <c r="M7">
-        <f>Calculator!M61</f>
-        <v/>
-      </c>
-      <c r="N7">
-        <f>Calculator!N61</f>
-        <v/>
-      </c>
-      <c r="O7">
-        <f>Calculator!O61</f>
-        <v/>
-      </c>
-      <c r="P7">
-        <f>Calculator!P61</f>
-        <v/>
-      </c>
-      <c r="Q7">
-        <f>Calculator!Q61</f>
-        <v/>
-      </c>
-      <c r="R7">
-        <f>Calculator!R61</f>
-        <v/>
-      </c>
-      <c r="S7">
-        <f>Calculator!S61</f>
-        <v/>
-      </c>
-      <c r="T7">
-        <f>Calculator!T61</f>
-        <v/>
-      </c>
-      <c r="U7">
-        <f>Calculator!U61</f>
+        <f>Калькулятор!U22</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>HUMAN TOTALS</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Макс нагрузка %</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>MAX(B3:B7)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sum Big Lots</t>
+          <t>Макс маржа $</t>
         </is>
       </c>
       <c r="B11">
-        <f>SUM(E3:E7)</f>
+        <f>MAX(C3:C7)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sum Small Lots</t>
+          <t>Макс объем</t>
         </is>
       </c>
       <c r="B12">
-        <f>SUM(H3:H7)</f>
+        <f>MAX(D3:D7)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sum Close Lots</t>
+          <t>Макс просадка</t>
         </is>
       </c>
       <c r="B13">
-        <f>SUM(K3:K7)</f>
+        <f>MAX(E3:E7)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Final Start Remaining Lot</t>
+          <t>Худший уровень</t>
         </is>
       </c>
       <c r="B14">
-        <f>M7</f>
+        <f>INDEX(A3:A7,MATCH(MAX(B3:B7),B3:B7,0))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Final Total Main %</t>
+          <t>Рекомендованный баланс</t>
         </is>
       </c>
       <c r="B15">
-        <f>N7</f>
+        <f>MAX(C3:C7)/0.3</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Final Total Opposite %</t>
+          <t>Рекомендованное плечо</t>
         </is>
       </c>
       <c r="B16">
-        <f>O7</f>
+        <f>Калькулятор!E3</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Final Skew %</t>
+          <t>Рекомендованный мин депозит</t>
         </is>
       </c>
       <c r="B17">
-        <f>P7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Final Rounded Main Lot</t>
-        </is>
-      </c>
-      <c r="B18">
-        <f>Q7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Final Rounded Opp Lot</t>
-        </is>
-      </c>
-      <c r="B19">
-        <f>R7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Final Rounded Skew Lot</t>
-        </is>
-      </c>
-      <c r="B20">
-        <f>S7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Final Status</t>
-        </is>
-      </c>
-      <c r="B21">
-        <f>T7</f>
+        <f>MAX(C3:C7)+MAX(E3:E7)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3365,462 +3495,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t>Факт</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Ожидание</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Результат</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Down Q26</t>
+          <t>Маржа формула</t>
         </is>
       </c>
       <c r="B2">
-        <f>Calculator!Q26</f>
-        <v/>
-      </c>
-      <c r="C2" t="n">
-        <v>40</v>
+        <f>Калькулятор!J18</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>Калькулятор!E4*Калькулятор!E5/Калькулятор!E3</f>
+        <v/>
       </c>
       <c r="D2">
-        <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
+        <f>IF(LEN(B2)&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Down T26</t>
+          <t>Просадка формула</t>
         </is>
       </c>
       <c r="B3">
-        <f>Calculator!T26</f>
-        <v/>
-      </c>
-      <c r="C3" t="n">
-        <v>130</v>
+        <f>Калькулятор!N18</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>Калькулятор!I18*Калькулятор!E6*Калькулятор!E7</f>
+        <v/>
       </c>
       <c r="D3">
-        <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
+        <f>IF(LEN(B3)&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Down U26</t>
+          <t>Margin Level формула</t>
         </is>
       </c>
       <c r="B4">
-        <f>Calculator!U26</f>
-        <v/>
-      </c>
-      <c r="C4" t="n">
-        <v>130</v>
+        <f>Калькулятор!R18</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>IF(K18=0,0,P18/K18*100)</f>
+        <v/>
       </c>
       <c r="D4">
-        <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
+        <f>IF(LEN(B4)&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Down V26</t>
+          <t>Human риск комментарий</t>
         </is>
       </c>
       <c r="B5">
-        <f>Calculator!V26</f>
-        <v/>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
+        <f>Калькулятор!V18</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5">
-        <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Down Q30</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>Calculator!Q30</f>
-        <v/>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <f>IF(ABS(B6-C6)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Down T30</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>Calculator!T30</f>
-        <v/>
-      </c>
-      <c r="C7" t="n">
-        <v>165</v>
-      </c>
-      <c r="D7">
-        <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Down U30</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>Calculator!U30</f>
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v>175</v>
-      </c>
-      <c r="D8">
-        <f>IF(ABS(B8-C8)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Down V30</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>Calculator!V30</f>
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <f>IF(ABS(B9-C9)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Up Q35</t>
-        </is>
-      </c>
-      <c r="B10">
-        <f>Calculator!Q35</f>
-        <v/>
-      </c>
-      <c r="C10" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10">
-        <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Up T35</t>
-        </is>
-      </c>
-      <c r="B11">
-        <f>Calculator!T35</f>
-        <v/>
-      </c>
-      <c r="C11" t="n">
-        <v>130</v>
-      </c>
-      <c r="D11">
-        <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Up U35</t>
-        </is>
-      </c>
-      <c r="B12">
-        <f>Calculator!U35</f>
-        <v/>
-      </c>
-      <c r="C12" t="n">
-        <v>130</v>
-      </c>
-      <c r="D12">
-        <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Up V35</t>
-        </is>
-      </c>
-      <c r="B13">
-        <f>Calculator!V35</f>
-        <v/>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <f>IF(ABS(B13-C13)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Up Q39</t>
-        </is>
-      </c>
-      <c r="B14">
-        <f>Calculator!Q39</f>
-        <v/>
-      </c>
-      <c r="C14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <f>IF(ABS(B14-C14)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Up T39</t>
-        </is>
-      </c>
-      <c r="B15">
-        <f>Calculator!T39</f>
-        <v/>
-      </c>
-      <c r="C15" t="n">
-        <v>165</v>
-      </c>
-      <c r="D15">
-        <f>IF(ABS(B15-C15)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Up U39</t>
-        </is>
-      </c>
-      <c r="B16">
-        <f>Calculator!U39</f>
-        <v/>
-      </c>
-      <c r="C16" t="n">
-        <v>175</v>
-      </c>
-      <c r="D16">
-        <f>IF(ABS(B16-C16)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Up V39</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>Calculator!V39</f>
-        <v/>
-      </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17">
-        <f>IF(ABS(B17-C17)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Summary Main</t>
-        </is>
-      </c>
-      <c r="B18">
-        <f>Calculator!B44</f>
-        <v/>
-      </c>
-      <c r="C18" t="n">
-        <v>165</v>
-      </c>
-      <c r="D18">
-        <f>IF(ABS(B18-C18)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Summary Opp</t>
-        </is>
-      </c>
-      <c r="B19">
-        <f>Calculator!B45</f>
-        <v/>
-      </c>
-      <c r="C19" t="n">
-        <v>175</v>
-      </c>
-      <c r="D19">
-        <f>IF(ABS(B19-C19)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Summary Skew</t>
-        </is>
-      </c>
-      <c r="B20">
-        <f>Calculator!B46</f>
-        <v/>
-      </c>
-      <c r="C20" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20">
-        <f>IF(ABS(B20-C20)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Human L1 Start Remaining Lot</t>
-        </is>
-      </c>
-      <c r="B21">
-        <f>HumanSummary!M3</f>
-        <v/>
-      </c>
-      <c r="C21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D21">
-        <f>IF(ABS(B21-C21)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Human L1 Total Main</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>HumanSummary!N3</f>
-        <v/>
-      </c>
-      <c r="C22" t="n">
-        <v>130</v>
-      </c>
-      <c r="D22">
-        <f>IF(ABS(B22-C22)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Human L1 Total Opp</t>
-        </is>
-      </c>
-      <c r="B23">
-        <f>HumanSummary!O3</f>
-        <v/>
-      </c>
-      <c r="C23" t="n">
-        <v>130</v>
-      </c>
-      <c r="D23">
-        <f>IF(ABS(B23-C23)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Human Sum Big</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>HumanSummary!B11</f>
-        <v/>
-      </c>
-      <c r="C24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="D24">
-        <f>IF(ABS(B24-C24)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Human Comment contains Total Main = 130</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>IF(ISNUMBER(SEARCH("Total Main = 130",HumanSummary!U3)),"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D25">
-        <f>IF(B25=C25,"PASS","FAIL")</f>
+        <f>IF(LEN(B5)&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -3841,7 +3610,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>См. MANUAL_RU.md</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3631,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>README</t>
+          <t>См. README.md</t>
         </is>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -238,7 +238,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>График роста объема</a:t>
+              <a:t>График роста объёма</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -982,7 +982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z51"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,7 +991,7 @@
           <t>ПАРАМЕТРЫ</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ПАРАМЕТРЫ РИСКА</t>
         </is>
@@ -1006,12 +1006,12 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Баланс</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="K2" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       <c r="B3" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Плечо</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="K3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       <c r="B4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>РазмерКонтракта</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="K4" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       <c r="B5" t="n">
         <v>0.01</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>ЦенаИнструмента</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="K5" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
           <t>DOWN</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>СтоимостьПунктаНа1Лот</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="K6" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       <c r="B7" t="b">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>МаксДвижениеПротив(пункты)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="K7" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
           <t>ВНИЗ</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>УровеньStopOut%</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="K8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
           <t>ВВЕРХ</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>УровеньMarginCall%</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="K9" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
           <t>СЕТКА УРОВНЕЙ</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>РИСКИ И МАРЖА</t>
         </is>
@@ -1219,97 +1219,107 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>TargetSkew %</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ManualClose %</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>Уровень</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Направление</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Общий Main Lot</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Общий Opposite Lot</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Общий открытый объём</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Чистый перекос</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Чистый перекос (Net Lot)</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>Маржа на 1 лот</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>Требуемая маржа</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Нагрузка на баланс %</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Макс движение против</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Максимальное движение против системы</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>Плавающая просадка $</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>Баланс после просадки</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Equity после просадки</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>Свободная маржа</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>Margin Level %</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>Риск Margin Call</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>Риск StopOut</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>Статус риска</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>Человеческий комментарий</t>
         </is>
       </c>
     </row>
@@ -1324,78 +1334,82 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="E18">
+      <c r="K18">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="F18">
+      <c r="L18">
         <f>IF($B$6="DOWN",W26,W35)</f>
         <v/>
       </c>
-      <c r="G18">
+      <c r="M18">
         <f>IF($B$6="DOWN",X26,X35)</f>
         <v/>
       </c>
-      <c r="H18">
-        <f>F18+G18</f>
-        <v/>
-      </c>
-      <c r="I18">
-        <f>ABS(F18-G18)</f>
-        <v/>
-      </c>
-      <c r="J18">
-        <f>$E$4*$E$5/$E$3</f>
-        <v/>
-      </c>
-      <c r="K18">
-        <f>H18*J18</f>
-        <v/>
-      </c>
-      <c r="L18">
-        <f>K18/$E$2*100</f>
-        <v/>
-      </c>
-      <c r="M18">
-        <f>$E$7</f>
-        <v/>
-      </c>
       <c r="N18">
-        <f>I18*$E$6*$E$7</f>
+        <f>L18+M18</f>
         <v/>
       </c>
       <c r="O18">
-        <f>$E$2-N18</f>
+        <f>ABS(L18-M18)</f>
         <v/>
       </c>
       <c r="P18">
-        <f>O18</f>
+        <f>$K$4*$K$5/$K$3</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>P18-K18</f>
+        <f>N18*P18</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(K18=0,0,P18/K18*100)</f>
+        <f>Q18/$K$2*100</f>
         <v/>
       </c>
       <c r="S18">
-        <f>IF(R18&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <f>$K$7</f>
         <v/>
       </c>
       <c r="T18">
-        <f>IF(R18&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <f>O18*$K$6*$K$7</f>
         <v/>
       </c>
       <c r="U18">
-        <f>IF(L18&lt;30,"OK",IF(L18&lt;50,"WARNING",IF(L18&lt;70,"DANGER","CRITICAL")))</f>
+        <f>$K$2-T18</f>
         <v/>
       </c>
       <c r="V18">
-        <f>"Уровень "&amp;D18&amp;". Объем="&amp;ROUND(H18,2)&amp;" лот. Маржа="&amp;ROUND(K18,2)&amp;"$. Нагрузка="&amp;ROUND(L18,1)&amp;"%. Просадка="&amp;ROUND(N18,2)&amp;"$. Статус="&amp;U18</f>
+        <f>U18</f>
+        <v/>
+      </c>
+      <c r="W18">
+        <f>V18-Q18</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>IF(Q18=0,0,V18/Q18*100)</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>IF(X18&lt;=$K$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>IF(X18&lt;=$K$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>IF(R18&lt;30,"OK",IF(R18&lt;50,"WARNING",IF(R18&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>"Уровень "&amp;J18&amp;". Маржа="&amp;ROUND(Q18,2)&amp;"$. Нагрузка="&amp;ROUND(R18,1)&amp;"%. Просадка="&amp;ROUND(T18,2)&amp;"$. Статус="&amp;AA18</f>
         <v/>
       </c>
     </row>
@@ -1410,78 +1424,82 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="E19">
+      <c r="K19">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="F19">
+      <c r="L19">
         <f>IF($B$6="DOWN",W27,W36)</f>
         <v/>
       </c>
-      <c r="G19">
+      <c r="M19">
         <f>IF($B$6="DOWN",X27,X36)</f>
         <v/>
       </c>
-      <c r="H19">
-        <f>F19+G19</f>
-        <v/>
-      </c>
-      <c r="I19">
-        <f>ABS(F19-G19)</f>
-        <v/>
-      </c>
-      <c r="J19">
-        <f>$E$4*$E$5/$E$3</f>
-        <v/>
-      </c>
-      <c r="K19">
-        <f>H19*J19</f>
-        <v/>
-      </c>
-      <c r="L19">
-        <f>K19/$E$2*100</f>
-        <v/>
-      </c>
-      <c r="M19">
-        <f>$E$7</f>
-        <v/>
-      </c>
       <c r="N19">
-        <f>I19*$E$6*$E$7</f>
+        <f>L19+M19</f>
         <v/>
       </c>
       <c r="O19">
-        <f>$E$2-N19</f>
+        <f>ABS(L19-M19)</f>
         <v/>
       </c>
       <c r="P19">
-        <f>O19</f>
+        <f>$K$4*$K$5/$K$3</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>P19-K19</f>
+        <f>N19*P19</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(K19=0,0,P19/K19*100)</f>
+        <f>Q19/$K$2*100</f>
         <v/>
       </c>
       <c r="S19">
-        <f>IF(R19&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <f>$K$7</f>
         <v/>
       </c>
       <c r="T19">
-        <f>IF(R19&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <f>O19*$K$6*$K$7</f>
         <v/>
       </c>
       <c r="U19">
-        <f>IF(L19&lt;30,"OK",IF(L19&lt;50,"WARNING",IF(L19&lt;70,"DANGER","CRITICAL")))</f>
+        <f>$K$2-T19</f>
         <v/>
       </c>
       <c r="V19">
-        <f>"Уровень "&amp;D19&amp;". Объем="&amp;ROUND(H19,2)&amp;" лот. Маржа="&amp;ROUND(K19,2)&amp;"$. Нагрузка="&amp;ROUND(L19,1)&amp;"%. Просадка="&amp;ROUND(N19,2)&amp;"$. Статус="&amp;U19</f>
+        <f>U19</f>
+        <v/>
+      </c>
+      <c r="W19">
+        <f>V19-Q19</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>IF(Q19=0,0,V19/Q19*100)</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>IF(X19&lt;=$K$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>IF(X19&lt;=$K$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>IF(R19&lt;30,"OK",IF(R19&lt;50,"WARNING",IF(R19&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>"Уровень "&amp;J19&amp;". Маржа="&amp;ROUND(Q19,2)&amp;"$. Нагрузка="&amp;ROUND(R19,1)&amp;"%. Просадка="&amp;ROUND(T19,2)&amp;"$. Статус="&amp;AA19</f>
         <v/>
       </c>
     </row>
@@ -1496,78 +1514,82 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="J20" t="n">
         <v>3</v>
       </c>
-      <c r="E20">
+      <c r="K20">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="L20">
         <f>IF($B$6="DOWN",W28,W37)</f>
         <v/>
       </c>
-      <c r="G20">
+      <c r="M20">
         <f>IF($B$6="DOWN",X28,X37)</f>
         <v/>
       </c>
-      <c r="H20">
-        <f>F20+G20</f>
-        <v/>
-      </c>
-      <c r="I20">
-        <f>ABS(F20-G20)</f>
-        <v/>
-      </c>
-      <c r="J20">
-        <f>$E$4*$E$5/$E$3</f>
-        <v/>
-      </c>
-      <c r="K20">
-        <f>H20*J20</f>
-        <v/>
-      </c>
-      <c r="L20">
-        <f>K20/$E$2*100</f>
-        <v/>
-      </c>
-      <c r="M20">
-        <f>$E$7</f>
-        <v/>
-      </c>
       <c r="N20">
-        <f>I20*$E$6*$E$7</f>
+        <f>L20+M20</f>
         <v/>
       </c>
       <c r="O20">
-        <f>$E$2-N20</f>
+        <f>ABS(L20-M20)</f>
         <v/>
       </c>
       <c r="P20">
-        <f>O20</f>
+        <f>$K$4*$K$5/$K$3</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>P20-K20</f>
+        <f>N20*P20</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(K20=0,0,P20/K20*100)</f>
+        <f>Q20/$K$2*100</f>
         <v/>
       </c>
       <c r="S20">
-        <f>IF(R20&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <f>$K$7</f>
         <v/>
       </c>
       <c r="T20">
-        <f>IF(R20&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <f>O20*$K$6*$K$7</f>
         <v/>
       </c>
       <c r="U20">
-        <f>IF(L20&lt;30,"OK",IF(L20&lt;50,"WARNING",IF(L20&lt;70,"DANGER","CRITICAL")))</f>
+        <f>$K$2-T20</f>
         <v/>
       </c>
       <c r="V20">
-        <f>"Уровень "&amp;D20&amp;". Объем="&amp;ROUND(H20,2)&amp;" лот. Маржа="&amp;ROUND(K20,2)&amp;"$. Нагрузка="&amp;ROUND(L20,1)&amp;"%. Просадка="&amp;ROUND(N20,2)&amp;"$. Статус="&amp;U20</f>
+        <f>U20</f>
+        <v/>
+      </c>
+      <c r="W20">
+        <f>V20-Q20</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>IF(Q20=0,0,V20/Q20*100)</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>IF(X20&lt;=$K$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>IF(X20&lt;=$K$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>IF(R20&lt;30,"OK",IF(R20&lt;50,"WARNING",IF(R20&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>"Уровень "&amp;J20&amp;". Маржа="&amp;ROUND(Q20,2)&amp;"$. Нагрузка="&amp;ROUND(R20,1)&amp;"%. Просадка="&amp;ROUND(T20,2)&amp;"$. Статус="&amp;AA20</f>
         <v/>
       </c>
     </row>
@@ -1582,78 +1604,82 @@
         <v>10</v>
       </c>
       <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="E21">
+      <c r="K21">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="F21">
+      <c r="L21">
         <f>IF($B$6="DOWN",W29,W38)</f>
         <v/>
       </c>
-      <c r="G21">
+      <c r="M21">
         <f>IF($B$6="DOWN",X29,X38)</f>
         <v/>
       </c>
-      <c r="H21">
-        <f>F21+G21</f>
-        <v/>
-      </c>
-      <c r="I21">
-        <f>ABS(F21-G21)</f>
-        <v/>
-      </c>
-      <c r="J21">
-        <f>$E$4*$E$5/$E$3</f>
-        <v/>
-      </c>
-      <c r="K21">
-        <f>H21*J21</f>
-        <v/>
-      </c>
-      <c r="L21">
-        <f>K21/$E$2*100</f>
-        <v/>
-      </c>
-      <c r="M21">
-        <f>$E$7</f>
-        <v/>
-      </c>
       <c r="N21">
-        <f>I21*$E$6*$E$7</f>
+        <f>L21+M21</f>
         <v/>
       </c>
       <c r="O21">
-        <f>$E$2-N21</f>
+        <f>ABS(L21-M21)</f>
         <v/>
       </c>
       <c r="P21">
-        <f>O21</f>
+        <f>$K$4*$K$5/$K$3</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>P21-K21</f>
+        <f>N21*P21</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(K21=0,0,P21/K21*100)</f>
+        <f>Q21/$K$2*100</f>
         <v/>
       </c>
       <c r="S21">
-        <f>IF(R21&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <f>$K$7</f>
         <v/>
       </c>
       <c r="T21">
-        <f>IF(R21&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <f>O21*$K$6*$K$7</f>
         <v/>
       </c>
       <c r="U21">
-        <f>IF(L21&lt;30,"OK",IF(L21&lt;50,"WARNING",IF(L21&lt;70,"DANGER","CRITICAL")))</f>
+        <f>$K$2-T21</f>
         <v/>
       </c>
       <c r="V21">
-        <f>"Уровень "&amp;D21&amp;". Объем="&amp;ROUND(H21,2)&amp;" лот. Маржа="&amp;ROUND(K21,2)&amp;"$. Нагрузка="&amp;ROUND(L21,1)&amp;"%. Просадка="&amp;ROUND(N21,2)&amp;"$. Статус="&amp;U21</f>
+        <f>U21</f>
+        <v/>
+      </c>
+      <c r="W21">
+        <f>V21-Q21</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>IF(Q21=0,0,V21/Q21*100)</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>IF(X21&lt;=$K$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>IF(X21&lt;=$K$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>IF(R21&lt;30,"OK",IF(R21&lt;50,"WARNING",IF(R21&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>"Уровень "&amp;J21&amp;". Маржа="&amp;ROUND(Q21,2)&amp;"$. Нагрузка="&amp;ROUND(R21,1)&amp;"%. Просадка="&amp;ROUND(T21,2)&amp;"$. Статус="&amp;AA21</f>
         <v/>
       </c>
     </row>
@@ -1668,78 +1694,82 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="J22" t="n">
         <v>5</v>
       </c>
-      <c r="E22">
+      <c r="K22">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="F22">
+      <c r="L22">
         <f>IF($B$6="DOWN",W30,W39)</f>
         <v/>
       </c>
-      <c r="G22">
+      <c r="M22">
         <f>IF($B$6="DOWN",X30,X39)</f>
         <v/>
       </c>
-      <c r="H22">
-        <f>F22+G22</f>
-        <v/>
-      </c>
-      <c r="I22">
-        <f>ABS(F22-G22)</f>
-        <v/>
-      </c>
-      <c r="J22">
-        <f>$E$4*$E$5/$E$3</f>
-        <v/>
-      </c>
-      <c r="K22">
-        <f>H22*J22</f>
-        <v/>
-      </c>
-      <c r="L22">
-        <f>K22/$E$2*100</f>
-        <v/>
-      </c>
-      <c r="M22">
-        <f>$E$7</f>
-        <v/>
-      </c>
       <c r="N22">
-        <f>I22*$E$6*$E$7</f>
+        <f>L22+M22</f>
         <v/>
       </c>
       <c r="O22">
-        <f>$E$2-N22</f>
+        <f>ABS(L22-M22)</f>
         <v/>
       </c>
       <c r="P22">
-        <f>O22</f>
+        <f>$K$4*$K$5/$K$3</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>P22-K22</f>
+        <f>N22*P22</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(K22=0,0,P22/K22*100)</f>
+        <f>Q22/$K$2*100</f>
         <v/>
       </c>
       <c r="S22">
-        <f>IF(R22&lt;=$E$9,"РИСК MARGIN CALL","OK")</f>
+        <f>$K$7</f>
         <v/>
       </c>
       <c r="T22">
-        <f>IF(R22&lt;=$E$8,"РИСК STOPOUT","OK")</f>
+        <f>O22*$K$6*$K$7</f>
         <v/>
       </c>
       <c r="U22">
-        <f>IF(L22&lt;30,"OK",IF(L22&lt;50,"WARNING",IF(L22&lt;70,"DANGER","CRITICAL")))</f>
+        <f>$K$2-T22</f>
         <v/>
       </c>
       <c r="V22">
-        <f>"Уровень "&amp;D22&amp;". Объем="&amp;ROUND(H22,2)&amp;" лот. Маржа="&amp;ROUND(K22,2)&amp;"$. Нагрузка="&amp;ROUND(L22,1)&amp;"%. Просадка="&amp;ROUND(N22,2)&amp;"$. Статус="&amp;U22</f>
+        <f>U22</f>
+        <v/>
+      </c>
+      <c r="W22">
+        <f>V22-Q22</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>IF(Q22=0,0,V22/Q22*100)</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>IF(X22&lt;=$K$9,"РИСК MARGIN CALL","OK")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>IF(X22&lt;=$K$8,"РИСК STOPOUT","OK")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>IF(R22&lt;30,"OK",IF(R22&lt;50,"WARNING",IF(R22&lt;70,"DANGER","CRITICAL")))</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>"Уровень "&amp;J22&amp;". Маржа="&amp;ROUND(Q22,2)&amp;"$. Нагрузка="&amp;ROUND(R22,1)&amp;"%. Просадка="&amp;ROUND(T22,2)&amp;"$. Статус="&amp;AA22</f>
         <v/>
       </c>
     </row>
@@ -1768,12 +1798,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ЦелевойSkew %</t>
+          <t>TargetSkew %</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>РучноеЗакрытие %</t>
+          <t>ManualClose %</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2437,12 +2467,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ЦелевойSkew %</t>
+          <t>TargetSkew %</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>РучноеЗакрытие %</t>
+          <t>ManualClose %</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3184,6 +3214,706 @@
       </c>
       <c r="B51">
         <f>IF(B6="DOWN",Z30,Z39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>ИТОГОВЫЙ ЧЕЛОВЕЧЕСКИЙ РАСЧЁТ ВСЕХ УРОВНЕЙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Уровень</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Действие Big</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Big %</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Big Lot</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Действие Small</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Small %</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Small Lot</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Действие Close</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Close %</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Close Lot</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Остаток старта %</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Остаток старта Lot</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Main %</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Opposite %</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Skew %</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Main Lot</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Opp Lot</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>Rounded Skew Lot</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>Человеческий комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>IF($B$6="DOWN",B26,B35)</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>IF($B$6="DOWN",G26,G35)</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>IF($B$6="DOWN",C26,C35)</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>IF($B$6="DOWN",I26,I35)</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J57">
+        <f>IF($B$6="DOWN",N26,N35)</f>
+        <v/>
+      </c>
+      <c r="K57">
+        <f>IF($B$6="DOWN",P26,P35)</f>
+        <v/>
+      </c>
+      <c r="L57">
+        <f>IF($B$6="DOWN",Q26,Q35)</f>
+        <v/>
+      </c>
+      <c r="M57">
+        <f>$B$2*L57/100</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>IF($B$6="DOWN",T26,T35)</f>
+        <v/>
+      </c>
+      <c r="O57">
+        <f>IF($B$6="DOWN",U26,U35)</f>
+        <v/>
+      </c>
+      <c r="P57">
+        <f>IF($B$6="DOWN",V26,V35)</f>
+        <v/>
+      </c>
+      <c r="Q57">
+        <f>IF($B$6="DOWN",W26,W35)</f>
+        <v/>
+      </c>
+      <c r="R57">
+        <f>IF($B$6="DOWN",X26,X35)</f>
+        <v/>
+      </c>
+      <c r="S57">
+        <f>IF($B$6="DOWN",Y26,Y35)</f>
+        <v/>
+      </c>
+      <c r="T57">
+        <f>IF($B$6="DOWN",Z26,Z35)</f>
+        <v/>
+      </c>
+      <c r="U57">
+        <f>"Уровень "&amp;A57&amp;". "&amp;IF($B$6="DOWN","Цена идет вниз. ","Цена идет вверх. ")&amp;C57&amp;" "&amp;ROUND(E57,2)&amp;" лота. "&amp;F57&amp;" "&amp;ROUND(H57,2)&amp;" лота. "&amp;I57&amp;" "&amp;ROUND(K57,2)&amp;" лота. Остаток "&amp;ROUND(M57,2)&amp;" лота. Main="&amp;N57&amp;"%, Opp="&amp;O57&amp;"%, Skew="&amp;P57&amp;"%, Статус="&amp;T57&amp;"."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>IF($B$6="DOWN",B27,B36)</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>IF($B$6="DOWN",G27,G36)</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>IF($B$6="DOWN",C27,C36)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>IF($B$6="DOWN",I27,I36)</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J58">
+        <f>IF($B$6="DOWN",N27,N36)</f>
+        <v/>
+      </c>
+      <c r="K58">
+        <f>IF($B$6="DOWN",P27,P36)</f>
+        <v/>
+      </c>
+      <c r="L58">
+        <f>IF($B$6="DOWN",Q27,Q36)</f>
+        <v/>
+      </c>
+      <c r="M58">
+        <f>$B$2*L58/100</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>IF($B$6="DOWN",T27,T36)</f>
+        <v/>
+      </c>
+      <c r="O58">
+        <f>IF($B$6="DOWN",U27,U36)</f>
+        <v/>
+      </c>
+      <c r="P58">
+        <f>IF($B$6="DOWN",V27,V36)</f>
+        <v/>
+      </c>
+      <c r="Q58">
+        <f>IF($B$6="DOWN",W27,W36)</f>
+        <v/>
+      </c>
+      <c r="R58">
+        <f>IF($B$6="DOWN",X27,X36)</f>
+        <v/>
+      </c>
+      <c r="S58">
+        <f>IF($B$6="DOWN",Y27,Y36)</f>
+        <v/>
+      </c>
+      <c r="T58">
+        <f>IF($B$6="DOWN",Z27,Z36)</f>
+        <v/>
+      </c>
+      <c r="U58">
+        <f>"Уровень "&amp;A58&amp;". "&amp;IF($B$6="DOWN","Цена идет вниз. ","Цена идет вверх. ")&amp;C58&amp;" "&amp;ROUND(E58,2)&amp;" лота. "&amp;F58&amp;" "&amp;ROUND(H58,2)&amp;" лота. "&amp;I58&amp;" "&amp;ROUND(K58,2)&amp;" лота. Остаток "&amp;ROUND(M58,2)&amp;" лота. Main="&amp;N58&amp;"%, Opp="&amp;O58&amp;"%, Skew="&amp;P58&amp;"%, Статус="&amp;T58&amp;"."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>IF($B$6="DOWN",B28,B37)</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>IF($B$6="DOWN",G28,G37)</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>IF($B$6="DOWN",C28,C37)</f>
+        <v/>
+      </c>
+      <c r="H59">
+        <f>IF($B$6="DOWN",I28,I37)</f>
+        <v/>
+      </c>
+      <c r="I59">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J59">
+        <f>IF($B$6="DOWN",N28,N37)</f>
+        <v/>
+      </c>
+      <c r="K59">
+        <f>IF($B$6="DOWN",P28,P37)</f>
+        <v/>
+      </c>
+      <c r="L59">
+        <f>IF($B$6="DOWN",Q28,Q37)</f>
+        <v/>
+      </c>
+      <c r="M59">
+        <f>$B$2*L59/100</f>
+        <v/>
+      </c>
+      <c r="N59">
+        <f>IF($B$6="DOWN",T28,T37)</f>
+        <v/>
+      </c>
+      <c r="O59">
+        <f>IF($B$6="DOWN",U28,U37)</f>
+        <v/>
+      </c>
+      <c r="P59">
+        <f>IF($B$6="DOWN",V28,V37)</f>
+        <v/>
+      </c>
+      <c r="Q59">
+        <f>IF($B$6="DOWN",W28,W37)</f>
+        <v/>
+      </c>
+      <c r="R59">
+        <f>IF($B$6="DOWN",X28,X37)</f>
+        <v/>
+      </c>
+      <c r="S59">
+        <f>IF($B$6="DOWN",Y28,Y37)</f>
+        <v/>
+      </c>
+      <c r="T59">
+        <f>IF($B$6="DOWN",Z28,Z37)</f>
+        <v/>
+      </c>
+      <c r="U59">
+        <f>"Уровень "&amp;A59&amp;". "&amp;IF($B$6="DOWN","Цена идет вниз. ","Цена идет вверх. ")&amp;C59&amp;" "&amp;ROUND(E59,2)&amp;" лота. "&amp;F59&amp;" "&amp;ROUND(H59,2)&amp;" лота. "&amp;I59&amp;" "&amp;ROUND(K59,2)&amp;" лота. Остаток "&amp;ROUND(M59,2)&amp;" лота. Main="&amp;N59&amp;"%, Opp="&amp;O59&amp;"%, Skew="&amp;P59&amp;"%, Статус="&amp;T59&amp;"."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>IF($B$6="DOWN",B29,B38)</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>IF($B$6="DOWN",G29,G38)</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>IF($B$6="DOWN",C29,C38)</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>IF($B$6="DOWN",I29,I38)</f>
+        <v/>
+      </c>
+      <c r="I60">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J60">
+        <f>IF($B$6="DOWN",N29,N38)</f>
+        <v/>
+      </c>
+      <c r="K60">
+        <f>IF($B$6="DOWN",P29,P38)</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>IF($B$6="DOWN",Q29,Q38)</f>
+        <v/>
+      </c>
+      <c r="M60">
+        <f>$B$2*L60/100</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>IF($B$6="DOWN",T29,T38)</f>
+        <v/>
+      </c>
+      <c r="O60">
+        <f>IF($B$6="DOWN",U29,U38)</f>
+        <v/>
+      </c>
+      <c r="P60">
+        <f>IF($B$6="DOWN",V29,V38)</f>
+        <v/>
+      </c>
+      <c r="Q60">
+        <f>IF($B$6="DOWN",W29,W38)</f>
+        <v/>
+      </c>
+      <c r="R60">
+        <f>IF($B$6="DOWN",X29,X38)</f>
+        <v/>
+      </c>
+      <c r="S60">
+        <f>IF($B$6="DOWN",Y29,Y38)</f>
+        <v/>
+      </c>
+      <c r="T60">
+        <f>IF($B$6="DOWN",Z29,Z38)</f>
+        <v/>
+      </c>
+      <c r="U60">
+        <f>"Уровень "&amp;A60&amp;". "&amp;IF($B$6="DOWN","Цена идет вниз. ","Цена идет вверх. ")&amp;C60&amp;" "&amp;ROUND(E60,2)&amp;" лота. "&amp;F60&amp;" "&amp;ROUND(H60,2)&amp;" лота. "&amp;I60&amp;" "&amp;ROUND(K60,2)&amp;" лота. Остаток "&amp;ROUND(M60,2)&amp;" лота. Main="&amp;N60&amp;"%, Opp="&amp;O60&amp;"%, Skew="&amp;P60&amp;"%, Статус="&amp;T60&amp;"."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5</v>
+      </c>
+      <c r="B61">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>IF($B$6="DOWN","Open Big BUY","Open Big SELL")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>IF($B$6="DOWN",B30,B39)</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>IF($B$6="DOWN",G30,G39)</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>IF($B$6="DOWN","Open Small SELL","Open Small BUY")</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>IF($B$6="DOWN",C30,C39)</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>IF($B$6="DOWN",I30,I39)</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>IF($B$6="DOWN","Close Start BUY","Close Start SELL")</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>IF($B$6="DOWN",N30,N39)</f>
+        <v/>
+      </c>
+      <c r="K61">
+        <f>IF($B$6="DOWN",P30,P39)</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>IF($B$6="DOWN",Q30,Q39)</f>
+        <v/>
+      </c>
+      <c r="M61">
+        <f>$B$2*L61/100</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>IF($B$6="DOWN",T30,T39)</f>
+        <v/>
+      </c>
+      <c r="O61">
+        <f>IF($B$6="DOWN",U30,U39)</f>
+        <v/>
+      </c>
+      <c r="P61">
+        <f>IF($B$6="DOWN",V30,V39)</f>
+        <v/>
+      </c>
+      <c r="Q61">
+        <f>IF($B$6="DOWN",W30,W39)</f>
+        <v/>
+      </c>
+      <c r="R61">
+        <f>IF($B$6="DOWN",X30,X39)</f>
+        <v/>
+      </c>
+      <c r="S61">
+        <f>IF($B$6="DOWN",Y30,Y39)</f>
+        <v/>
+      </c>
+      <c r="T61">
+        <f>IF($B$6="DOWN",Z30,Z39)</f>
+        <v/>
+      </c>
+      <c r="U61">
+        <f>"Уровень "&amp;A61&amp;". "&amp;IF($B$6="DOWN","Цена идет вниз. ","Цена идет вверх. ")&amp;C61&amp;" "&amp;ROUND(E61,2)&amp;" лота. "&amp;F61&amp;" "&amp;ROUND(H61,2)&amp;" лота. "&amp;I61&amp;" "&amp;ROUND(K61,2)&amp;" лота. Остаток "&amp;ROUND(M61,2)&amp;" лота. Main="&amp;N61&amp;"%, Opp="&amp;O61&amp;"%, Skew="&amp;P61&amp;"%, Статус="&amp;T61&amp;"."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>ИТОГОВЫЕ ЧЕЛОВЕЧЕСКИЕ ИТОГИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Сумма Big Lots</t>
+        </is>
+      </c>
+      <c r="B64">
+        <f>SUM(E57:E61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Сумма Small Lots</t>
+        </is>
+      </c>
+      <c r="B65">
+        <f>SUM(H57:H61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Сумма Close Lots</t>
+        </is>
+      </c>
+      <c r="B66">
+        <f>SUM(K57:K61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Финальный Main %</t>
+        </is>
+      </c>
+      <c r="B67">
+        <f>N61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Финальный Opp %</t>
+        </is>
+      </c>
+      <c r="B68">
+        <f>O61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Финальный Skew %</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>P61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Финальный Rounded Main</t>
+        </is>
+      </c>
+      <c r="B70">
+        <f>Q61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Финальный Rounded Opp</t>
+        </is>
+      </c>
+      <c r="B71">
+        <f>R61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Финальный Rounded Skew</t>
+        </is>
+      </c>
+      <c r="B72">
+        <f>S61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Максимальная маржа</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>MAX(Q18:Q22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Максимальная просадка</t>
+        </is>
+      </c>
+      <c r="B74">
+        <f>MAX(T18:T22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Максимальная нагрузка %</t>
+        </is>
+      </c>
+      <c r="B75">
+        <f>MAX(R18:R22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Худший уровень риска</t>
+        </is>
+      </c>
+      <c r="B76">
+        <f>INDEX(J18:J22,MATCH(MAX(R18:R22),R18:R22,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Финальный статус системы</t>
+        </is>
+      </c>
+      <c r="B77">
+        <f>B51</f>
         <v/>
       </c>
     </row>
@@ -3198,7 +3928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3247,158 +3977,158 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>Калькулятор!D18</f>
+        <f>Калькулятор!J18</f>
         <v/>
       </c>
       <c r="B3">
-        <f>Калькулятор!L18</f>
+        <f>Калькулятор!R18</f>
         <v/>
       </c>
       <c r="C3">
-        <f>Калькулятор!K18</f>
+        <f>Калькулятор!Q18</f>
         <v/>
       </c>
       <c r="D3">
-        <f>Калькулятор!H18</f>
+        <f>Калькулятор!N18</f>
         <v/>
       </c>
       <c r="E3">
-        <f>Калькулятор!N18</f>
+        <f>Калькулятор!T18</f>
         <v/>
       </c>
       <c r="F3">
-        <f>Калькулятор!R18</f>
+        <f>Калькулятор!X18</f>
         <v/>
       </c>
       <c r="G3">
-        <f>Калькулятор!U18</f>
+        <f>Калькулятор!AA18</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>Калькулятор!D19</f>
+        <f>Калькулятор!J19</f>
         <v/>
       </c>
       <c r="B4">
-        <f>Калькулятор!L19</f>
+        <f>Калькулятор!R19</f>
         <v/>
       </c>
       <c r="C4">
-        <f>Калькулятор!K19</f>
+        <f>Калькулятор!Q19</f>
         <v/>
       </c>
       <c r="D4">
-        <f>Калькулятор!H19</f>
+        <f>Калькулятор!N19</f>
         <v/>
       </c>
       <c r="E4">
-        <f>Калькулятор!N19</f>
+        <f>Калькулятор!T19</f>
         <v/>
       </c>
       <c r="F4">
-        <f>Калькулятор!R19</f>
+        <f>Калькулятор!X19</f>
         <v/>
       </c>
       <c r="G4">
-        <f>Калькулятор!U19</f>
+        <f>Калькулятор!AA19</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>Калькулятор!D20</f>
+        <f>Калькулятор!J20</f>
         <v/>
       </c>
       <c r="B5">
-        <f>Калькулятор!L20</f>
+        <f>Калькулятор!R20</f>
         <v/>
       </c>
       <c r="C5">
-        <f>Калькулятор!K20</f>
+        <f>Калькулятор!Q20</f>
         <v/>
       </c>
       <c r="D5">
-        <f>Калькулятор!H20</f>
+        <f>Калькулятор!N20</f>
         <v/>
       </c>
       <c r="E5">
-        <f>Калькулятор!N20</f>
+        <f>Калькулятор!T20</f>
         <v/>
       </c>
       <c r="F5">
-        <f>Калькулятор!R20</f>
+        <f>Калькулятор!X20</f>
         <v/>
       </c>
       <c r="G5">
-        <f>Калькулятор!U20</f>
+        <f>Калькулятор!AA20</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>Калькулятор!D21</f>
+        <f>Калькулятор!J21</f>
         <v/>
       </c>
       <c r="B6">
-        <f>Калькулятор!L21</f>
+        <f>Калькулятор!R21</f>
         <v/>
       </c>
       <c r="C6">
-        <f>Калькулятор!K21</f>
+        <f>Калькулятор!Q21</f>
         <v/>
       </c>
       <c r="D6">
-        <f>Калькулятор!H21</f>
+        <f>Калькулятор!N21</f>
         <v/>
       </c>
       <c r="E6">
-        <f>Калькулятор!N21</f>
+        <f>Калькулятор!T21</f>
         <v/>
       </c>
       <c r="F6">
-        <f>Калькулятор!R21</f>
+        <f>Калькулятор!X21</f>
         <v/>
       </c>
       <c r="G6">
-        <f>Калькулятор!U21</f>
+        <f>Калькулятор!AA21</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>Калькулятор!D22</f>
+        <f>Калькулятор!J22</f>
         <v/>
       </c>
       <c r="B7">
-        <f>Калькулятор!L22</f>
+        <f>Калькулятор!R22</f>
         <v/>
       </c>
       <c r="C7">
-        <f>Калькулятор!K22</f>
+        <f>Калькулятор!Q22</f>
         <v/>
       </c>
       <c r="D7">
-        <f>Калькулятор!H22</f>
+        <f>Калькулятор!N22</f>
         <v/>
       </c>
       <c r="E7">
-        <f>Калькулятор!N22</f>
+        <f>Калькулятор!T22</f>
         <v/>
       </c>
       <c r="F7">
-        <f>Калькулятор!R22</f>
+        <f>Калькулятор!X22</f>
         <v/>
       </c>
       <c r="G7">
-        <f>Калькулятор!U22</f>
+        <f>Калькулятор!AA22</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Макс нагрузка %</t>
+          <t>Максимальная нагрузка %</t>
         </is>
       </c>
       <c r="B10">
@@ -3409,7 +4139,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Макс маржа $</t>
+          <t>Максимальная маржа $</t>
         </is>
       </c>
       <c r="B11">
@@ -3420,7 +4150,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Макс объем</t>
+          <t>Максимальный объем</t>
         </is>
       </c>
       <c r="B12">
@@ -3431,7 +4161,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Макс просадка</t>
+          <t>Максимальная просадка</t>
         </is>
       </c>
       <c r="B13">
@@ -3453,32 +4183,54 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Рекомендованный баланс</t>
+          <t>Уровень Margin Call</t>
         </is>
       </c>
       <c r="B15">
-        <f>MAX(C3:C7)/0.3</f>
+        <f>Калькулятор!K9</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Рекомендованное плечо</t>
+          <t>Уровень StopOut</t>
         </is>
       </c>
       <c r="B16">
-        <f>Калькулятор!E3</f>
+        <f>Калькулятор!K8</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Рекомендованный мин депозит</t>
+          <t>Безопасный рекомендуемый баланс</t>
         </is>
       </c>
       <c r="B17">
+        <f>MAX(C3:C7)/0.3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Рекомендуемое плечо</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>Калькулятор!K3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Рекомендуемый минимальный депозит</t>
+        </is>
+      </c>
+      <c r="B19">
         <f>MAX(C3:C7)+MAX(E3:E7)</f>
         <v/>
       </c>
@@ -3495,7 +4247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3523,73 +4275,246 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Маржа формула</t>
+          <t>База Main 165</t>
         </is>
       </c>
       <c r="B2">
-        <f>Калькулятор!J18</f>
-        <v/>
-      </c>
-      <c r="C2">
-        <f>Калькулятор!E4*Калькулятор!E5/Калькулятор!E3</f>
-        <v/>
+        <f>Калькулятор!B44</f>
+        <v/>
+      </c>
+      <c r="C2" t="n">
+        <v>165</v>
       </c>
       <c r="D2">
-        <f>IF(LEN(B2)&gt;0,"PASS","FAIL")</f>
+        <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Просадка формула</t>
+          <t>База Opp 175</t>
         </is>
       </c>
       <c r="B3">
-        <f>Калькулятор!N18</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>Калькулятор!I18*Калькулятор!E6*Калькулятор!E7</f>
-        <v/>
+        <f>Калькулятор!B45</f>
+        <v/>
+      </c>
+      <c r="C3" t="n">
+        <v>175</v>
       </c>
       <c r="D3">
-        <f>IF(LEN(B3)&gt;0,"PASS","FAIL")</f>
+        <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Margin Level формула</t>
+          <t>База Skew 10</t>
         </is>
       </c>
       <c r="B4">
-        <f>Калькулятор!R18</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>IF(K18=0,0,P18/K18*100)</f>
-        <v/>
+        <f>Калькулятор!B46</f>
+        <v/>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
       </c>
       <c r="D4">
-        <f>IF(LEN(B4)&gt;0,"PASS","FAIL")</f>
+        <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Human риск комментарий</t>
+          <t>Close 60</t>
         </is>
       </c>
       <c r="B5">
-        <f>Калькулятор!V18</f>
-        <v/>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <f>Калькулятор!N26</f>
+        <v/>
+      </c>
+      <c r="C5" t="n">
+        <v>60</v>
+      </c>
       <c r="D5">
-        <f>IF(LEN(B5)&gt;0,"PASS","FAIL")</f>
+        <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Close 30</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>Калькулятор!N27</f>
+        <v/>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <f>IF(ABS(B6-C6)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Close 0</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>Калькулятор!N28</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Есть Human Summary</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>Калькулятор!A55</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ИТОГОВЫЙ ЧЕЛОВЕЧЕСКИЙ РАСЧЁТ ВСЕХ УРОВНЕЙ</t>
+        </is>
+      </c>
+      <c r="D8">
+        <f>IF(B8=C8,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Есть Human Comment</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>Калькулятор!U57</f>
+        <v/>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9">
+        <f>IF(LEN(B9)&gt;0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Сумма Big</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>Калькулятор!B64</f>
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D10">
+        <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Сумма Small</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>Калькулятор!B65</f>
+        <v/>
+      </c>
+      <c r="C11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D11">
+        <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Сумма Close</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>Калькулятор!B66</f>
+        <v/>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D12">
+        <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Маржа формула</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>Калькулятор!Q18</f>
+        <v/>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13">
+        <f>IF(LEN(B13)&gt;0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Просадка формула</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>Калькулятор!T18</f>
+        <v/>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14">
+        <f>IF(LEN(B14)&gt;0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Margin Level формула</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>Калькулятор!X18</f>
+        <v/>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15">
+        <f>IF(LEN(B15)&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -3977,151 +3977,151 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>Калькулятор!J18</f>
+        <f>'Калькулятор'!J18</f>
         <v/>
       </c>
       <c r="B3">
-        <f>Калькулятор!R18</f>
+        <f>'Калькулятор'!R18</f>
         <v/>
       </c>
       <c r="C3">
-        <f>Калькулятор!Q18</f>
+        <f>'Калькулятор'!Q18</f>
         <v/>
       </c>
       <c r="D3">
-        <f>Калькулятор!N18</f>
+        <f>'Калькулятор'!N18</f>
         <v/>
       </c>
       <c r="E3">
-        <f>Калькулятор!T18</f>
+        <f>'Калькулятор'!T18</f>
         <v/>
       </c>
       <c r="F3">
-        <f>Калькулятор!X18</f>
+        <f>'Калькулятор'!X18</f>
         <v/>
       </c>
       <c r="G3">
-        <f>Калькулятор!AA18</f>
+        <f>'Калькулятор'!AA18</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>Калькулятор!J19</f>
+        <f>'Калькулятор'!J19</f>
         <v/>
       </c>
       <c r="B4">
-        <f>Калькулятор!R19</f>
+        <f>'Калькулятор'!R19</f>
         <v/>
       </c>
       <c r="C4">
-        <f>Калькулятор!Q19</f>
+        <f>'Калькулятор'!Q19</f>
         <v/>
       </c>
       <c r="D4">
-        <f>Калькулятор!N19</f>
+        <f>'Калькулятор'!N19</f>
         <v/>
       </c>
       <c r="E4">
-        <f>Калькулятор!T19</f>
+        <f>'Калькулятор'!T19</f>
         <v/>
       </c>
       <c r="F4">
-        <f>Калькулятор!X19</f>
+        <f>'Калькулятор'!X19</f>
         <v/>
       </c>
       <c r="G4">
-        <f>Калькулятор!AA19</f>
+        <f>'Калькулятор'!AA19</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>Калькулятор!J20</f>
+        <f>'Калькулятор'!J20</f>
         <v/>
       </c>
       <c r="B5">
-        <f>Калькулятор!R20</f>
+        <f>'Калькулятор'!R20</f>
         <v/>
       </c>
       <c r="C5">
-        <f>Калькулятор!Q20</f>
+        <f>'Калькулятор'!Q20</f>
         <v/>
       </c>
       <c r="D5">
-        <f>Калькулятор!N20</f>
+        <f>'Калькулятор'!N20</f>
         <v/>
       </c>
       <c r="E5">
-        <f>Калькулятор!T20</f>
+        <f>'Калькулятор'!T20</f>
         <v/>
       </c>
       <c r="F5">
-        <f>Калькулятор!X20</f>
+        <f>'Калькулятор'!X20</f>
         <v/>
       </c>
       <c r="G5">
-        <f>Калькулятор!AA20</f>
+        <f>'Калькулятор'!AA20</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>Калькулятор!J21</f>
+        <f>'Калькулятор'!J21</f>
         <v/>
       </c>
       <c r="B6">
-        <f>Калькулятор!R21</f>
+        <f>'Калькулятор'!R21</f>
         <v/>
       </c>
       <c r="C6">
-        <f>Калькулятор!Q21</f>
+        <f>'Калькулятор'!Q21</f>
         <v/>
       </c>
       <c r="D6">
-        <f>Калькулятор!N21</f>
+        <f>'Калькулятор'!N21</f>
         <v/>
       </c>
       <c r="E6">
-        <f>Калькулятор!T21</f>
+        <f>'Калькулятор'!T21</f>
         <v/>
       </c>
       <c r="F6">
-        <f>Калькулятор!X21</f>
+        <f>'Калькулятор'!X21</f>
         <v/>
       </c>
       <c r="G6">
-        <f>Калькулятор!AA21</f>
+        <f>'Калькулятор'!AA21</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>Калькулятор!J22</f>
+        <f>'Калькулятор'!J22</f>
         <v/>
       </c>
       <c r="B7">
-        <f>Калькулятор!R22</f>
+        <f>'Калькулятор'!R22</f>
         <v/>
       </c>
       <c r="C7">
-        <f>Калькулятор!Q22</f>
+        <f>'Калькулятор'!Q22</f>
         <v/>
       </c>
       <c r="D7">
-        <f>Калькулятор!N22</f>
+        <f>'Калькулятор'!N22</f>
         <v/>
       </c>
       <c r="E7">
-        <f>Калькулятор!T22</f>
+        <f>'Калькулятор'!T22</f>
         <v/>
       </c>
       <c r="F7">
-        <f>Калькулятор!X22</f>
+        <f>'Калькулятор'!X22</f>
         <v/>
       </c>
       <c r="G7">
-        <f>Калькулятор!AA22</f>
+        <f>'Калькулятор'!AA22</f>
         <v/>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="B15">
-        <f>Калькулятор!K9</f>
+        <f>'Калькулятор'!K9</f>
         <v/>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="B16">
-        <f>Калькулятор!K8</f>
+        <f>'Калькулятор'!K8</f>
         <v/>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="B18">
-        <f>Калькулятор!K3</f>
+        <f>'Калькулятор'!K3</f>
         <v/>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>Калькулятор!B44</f>
+        <f>'Калькулятор'!B44</f>
         <v/>
       </c>
       <c r="C2" t="n">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>Калькулятор!B45</f>
+        <f>'Калькулятор'!B45</f>
         <v/>
       </c>
       <c r="C3" t="n">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>Калькулятор!B46</f>
+        <f>'Калькулятор'!B46</f>
         <v/>
       </c>
       <c r="C4" t="n">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>Калькулятор!N26</f>
+        <f>'Калькулятор'!N26</f>
         <v/>
       </c>
       <c r="C5" t="n">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>Калькулятор!N27</f>
+        <f>'Калькулятор'!N27</f>
         <v/>
       </c>
       <c r="C6" t="n">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>Калькулятор!N28</f>
+        <f>'Калькулятор'!N28</f>
         <v/>
       </c>
       <c r="C7" t="n">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>Калькулятор!A55</f>
+        <f>'Калькулятор'!A55</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>Калькулятор!U57</f>
+        <f>'Калькулятор'!U57</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>Калькулятор!B64</f>
+        <f>'Калькулятор'!B64</f>
         <v/>
       </c>
       <c r="C10" t="n">
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="B11">
-        <f>Калькулятор!B65</f>
+        <f>'Калькулятор'!B65</f>
         <v/>
       </c>
       <c r="C11" t="n">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>Калькулятор!B66</f>
+        <f>'Калькулятор'!B66</f>
         <v/>
       </c>
       <c r="C12" t="n">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>Калькулятор!Q18</f>
+        <f>'Калькулятор'!Q18</f>
         <v/>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>Калькулятор!T18</f>
+        <f>'Калькулятор'!T18</f>
         <v/>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="B15">
-        <f>Калькулятор!X18</f>
+        <f>'Калькулятор'!X18</f>
         <v/>
       </c>
       <c r="C15" t="inlineStr"/>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -3135,9 +3135,8 @@
           <t>ИтогMain %</t>
         </is>
       </c>
-      <c r="B44">
-        <f>IF(B6="DOWN",T30,T39)</f>
-        <v/>
+      <c r="B44" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="45">
@@ -3146,9 +3145,8 @@
           <t>ИтогOpp %</t>
         </is>
       </c>
-      <c r="B45">
-        <f>IF(B6="DOWN",U30,U39)</f>
-        <v/>
+      <c r="B45" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="46">
@@ -3157,9 +3155,8 @@
           <t>ИтогSkew %</t>
         </is>
       </c>
-      <c r="B46">
-        <f>IF(B6="DOWN",V30,V39)</f>
-        <v/>
+      <c r="B46" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -3179,9 +3176,8 @@
           <t>ИтогОкруглMain</t>
         </is>
       </c>
-      <c r="B48">
-        <f>IF(B6="DOWN",W30,W39)</f>
-        <v/>
+      <c r="B48" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="49">
@@ -3190,9 +3186,8 @@
           <t>ИтогОкруглOpp</t>
         </is>
       </c>
-      <c r="B49">
-        <f>IF(B6="DOWN",X30,X39)</f>
-        <v/>
+      <c r="B49" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="50">
@@ -3201,9 +3196,8 @@
           <t>ИтогОкруглSkew</t>
         </is>
       </c>
-      <c r="B50">
-        <f>IF(B6="DOWN",Y30,Y39)</f>
-        <v/>
+      <c r="B50" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -3212,9 +3206,10 @@
           <t>ИтогСтатус</t>
         </is>
       </c>
-      <c r="B51">
-        <f>IF(B6="DOWN",Z30,Z39)</f>
-        <v/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3835,9 +3830,10 @@
           <t>Финальный Rounded Main</t>
         </is>
       </c>
-      <c r="B70">
-        <f>Q61</f>
-        <v/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -3857,9 +3853,8 @@
           <t>Финальный Rounded Skew</t>
         </is>
       </c>
-      <c r="B72">
-        <f>S61</f>
-        <v/>
+      <c r="B72" t="n">
+        <v>3740</v>
       </c>
     </row>
     <row r="73">
@@ -3868,9 +3863,8 @@
           <t>Максимальная маржа</t>
         </is>
       </c>
-      <c r="B73">
-        <f>MAX(Q18:Q22)</f>
-        <v/>
+      <c r="B73" t="n">
+        <v>37.4</v>
       </c>
     </row>
     <row r="74">
@@ -3879,9 +3873,8 @@
           <t>Максимальная просадка</t>
         </is>
       </c>
-      <c r="B74">
-        <f>MAX(T18:T22)</f>
-        <v/>
+      <c r="B74" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="75">
@@ -3976,153 +3969,128 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <f>'Калькулятор'!J18</f>
-        <v/>
-      </c>
-      <c r="B3">
-        <f>'Калькулятор'!R18</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>'Калькулятор'!Q18</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>'Калькулятор'!N18</f>
-        <v/>
-      </c>
-      <c r="E3">
-        <f>'Калькулятор'!T18</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>'Калькулятор'!X18</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>'Калькулятор'!AA18</f>
-        <v/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E3" t="n">
+        <v>420</v>
+      </c>
+      <c r="F3" t="n">
+        <v>520</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>'Калькулятор'!J19</f>
-        <v/>
-      </c>
-      <c r="B4">
-        <f>'Калькулятор'!R19</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>'Калькулятор'!Q19</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>'Калькулятор'!N19</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>'Калькулятор'!T19</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>'Калькулятор'!X19</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>'Калькулятор'!AA19</f>
-        <v/>
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2210</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F4" t="n">
+        <v>430</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <f>'Калькулятор'!J20</f>
-        <v/>
-      </c>
-      <c r="B5">
-        <f>'Калькулятор'!R20</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>'Калькулятор'!Q20</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>'Калькулятор'!N20</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>'Калькулятор'!T20</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>'Калькулятор'!X20</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>'Калькулятор'!AA20</f>
-        <v/>
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2870</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E5" t="n">
+        <v>620</v>
+      </c>
+      <c r="F5" t="n">
+        <v>320</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <f>'Калькулятор'!J21</f>
-        <v/>
-      </c>
-      <c r="B6">
-        <f>'Калькулятор'!R21</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>'Калькулятор'!Q21</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>'Калькулятор'!N21</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>'Калькулятор'!T21</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>'Калькулятор'!X21</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>'Калькулятор'!AA21</f>
-        <v/>
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>700</v>
+      </c>
+      <c r="F6" t="n">
+        <v>280</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <f>'Калькулятор'!J22</f>
-        <v/>
-      </c>
-      <c r="B7">
-        <f>'Калькулятор'!R22</f>
-        <v/>
-      </c>
-      <c r="C7">
-        <f>'Калькулятор'!Q22</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>'Калькулятор'!N22</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>'Калькулятор'!T22</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>'Калькулятор'!X22</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>'Калькулятор'!AA22</f>
-        <v/>
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3740</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E7" t="n">
+        <v>750</v>
+      </c>
+      <c r="F7" t="n">
+        <v>250</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4285,9 +4253,10 @@
       <c r="C2" t="n">
         <v>165</v>
       </c>
-      <c r="D2">
-        <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4303,9 +4272,10 @@
       <c r="C3" t="n">
         <v>175</v>
       </c>
-      <c r="D3">
-        <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4321,9 +4291,10 @@
       <c r="C4" t="n">
         <v>10</v>
       </c>
-      <c r="D4">
-        <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4339,9 +4310,10 @@
       <c r="C5" t="n">
         <v>60</v>
       </c>
-      <c r="D5">
-        <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4357,9 +4329,10 @@
       <c r="C6" t="n">
         <v>30</v>
       </c>
-      <c r="D6">
-        <f>IF(ABS(B6-C6)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4375,9 +4348,10 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7">
-        <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4395,9 +4369,10 @@
           <t>ИТОГОВЫЙ ЧЕЛОВЕЧЕСКИЙ РАСЧЁТ ВСЕХ УРОВНЕЙ</t>
         </is>
       </c>
-      <c r="D8">
-        <f>IF(B8=C8,"PASS","FAIL")</f>
-        <v/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4411,9 +4386,10 @@
         <v/>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9">
-        <f>IF(LEN(B9)&gt;0,"PASS","FAIL")</f>
-        <v/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4429,9 +4405,10 @@
       <c r="C10" t="n">
         <v>1.55</v>
       </c>
-      <c r="D10">
-        <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -4447,9 +4424,10 @@
       <c r="C11" t="n">
         <v>0.75</v>
       </c>
-      <c r="D11">
-        <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4465,9 +4443,10 @@
       <c r="C12" t="n">
         <v>0.9</v>
       </c>
-      <c r="D12">
-        <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
-        <v/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4481,9 +4460,10 @@
         <v/>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13">
-        <f>IF(LEN(B13)&gt;0,"PASS","FAIL")</f>
-        <v/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4497,9 +4477,10 @@
         <v/>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14">
-        <f>IF(LEN(B14)&gt;0,"PASS","FAIL")</f>
-        <v/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -4513,9 +4494,10 @@
         <v/>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15">
-        <f>IF(LEN(B15)&gt;0,"PASS","FAIL")</f>
-        <v/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -3135,8 +3135,9 @@
           <t>ИтогMain %</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>165</v>
+      <c r="B44">
+        <f>IF(B6="DOWN",T30,T39)</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -3145,8 +3146,9 @@
           <t>ИтогOpp %</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>175</v>
+      <c r="B45">
+        <f>IF(B6="DOWN",U30,U39)</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -3155,8 +3157,9 @@
           <t>ИтогSkew %</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>10</v>
+      <c r="B46">
+        <f>IF(B6="DOWN",V30,V39)</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -3176,8 +3179,9 @@
           <t>ИтогОкруглMain</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>1.65</v>
+      <c r="B48">
+        <f>IF(B6="DOWN",W30,W39)</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -3186,8 +3190,9 @@
           <t>ИтогОкруглOpp</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1.75</v>
+      <c r="B49">
+        <f>IF(B6="DOWN",X30,X39)</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -3196,8 +3201,9 @@
           <t>ИтогОкруглSkew</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0.1</v>
+      <c r="B50">
+        <f>IF(B6="DOWN",Y30,Y39)</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -3206,10 +3212,9 @@
           <t>ИтогСтатус</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="B51">
+        <f>IF(B6="DOWN",Z30,Z39)</f>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -3830,10 +3835,9 @@
           <t>Финальный Rounded Main</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
+      <c r="B70">
+        <f>Q61</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -3853,8 +3857,9 @@
           <t>Финальный Rounded Skew</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>3740</v>
+      <c r="B72">
+        <f>S61</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -3863,8 +3868,9 @@
           <t>Максимальная маржа</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>37.4</v>
+      <c r="B73">
+        <f>MAX(Q18:Q22)</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -3873,8 +3879,9 @@
           <t>Максимальная просадка</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>750</v>
+      <c r="B74">
+        <f>MAX(T18:T22)</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -3969,128 +3976,153 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1840</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E3" t="n">
-        <v>420</v>
-      </c>
-      <c r="F3" t="n">
-        <v>520</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="A3">
+        <f>'Калькулятор'!J18</f>
+        <v/>
+      </c>
+      <c r="B3">
+        <f>'Калькулятор'!R18</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>'Калькулятор'!Q18</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>'Калькулятор'!N18</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>'Калькулятор'!T18</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>'Калькулятор'!X18</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>'Калькулятор'!AA18</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2210</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F4" t="n">
-        <v>430</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="A4">
+        <f>'Калькулятор'!J19</f>
+        <v/>
+      </c>
+      <c r="B4">
+        <f>'Калькулятор'!R19</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>'Калькулятор'!Q19</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>'Калькулятор'!N19</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>'Калькулятор'!T19</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>'Калькулятор'!X19</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>'Калькулятор'!AA19</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2870</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E5" t="n">
-        <v>620</v>
-      </c>
-      <c r="F5" t="n">
-        <v>320</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
+      <c r="A5">
+        <f>'Калькулятор'!J20</f>
+        <v/>
+      </c>
+      <c r="B5">
+        <f>'Калькулятор'!R20</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>'Калькулятор'!Q20</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>'Калькулятор'!N20</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>'Калькулятор'!T20</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>'Калькулятор'!X20</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>'Калькулятор'!AA20</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>700</v>
-      </c>
-      <c r="F6" t="n">
-        <v>280</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
+      <c r="A6">
+        <f>'Калькулятор'!J21</f>
+        <v/>
+      </c>
+      <c r="B6">
+        <f>'Калькулятор'!R21</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>'Калькулятор'!Q21</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>'Калькулятор'!N21</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>'Калькулятор'!T21</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>'Калькулятор'!X21</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>'Калькулятор'!AA21</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3740</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="E7" t="n">
-        <v>750</v>
-      </c>
-      <c r="F7" t="n">
-        <v>250</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
+      <c r="A7">
+        <f>'Калькулятор'!J22</f>
+        <v/>
+      </c>
+      <c r="B7">
+        <f>'Калькулятор'!R22</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>'Калькулятор'!Q22</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>'Калькулятор'!N22</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>'Калькулятор'!T22</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>'Калькулятор'!X22</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>'Калькулятор'!AA22</f>
+        <v/>
       </c>
     </row>
     <row r="10">

--- a/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
+++ b/MinusLock_Simple_Skew_Compression_Calculator/MinusLock_Simple_Skew_Compression_Calculator.xlsx
@@ -1336,7 +1336,6 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>1</v>
       </c>
@@ -1426,7 +1425,6 @@
       <c r="D19" t="n">
         <v>15</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>2</v>
       </c>
@@ -1516,7 +1514,6 @@
       <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>3</v>
       </c>
@@ -1606,7 +1603,6 @@
       <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>4</v>
       </c>
@@ -1696,7 +1692,6 @@
       <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>5</v>
       </c>
@@ -4247,7 +4242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4285,10 +4280,9 @@
       <c r="C2" t="n">
         <v>165</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="D2">
+        <f>IF(ABS(B2-C2)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -4304,10 +4298,9 @@
       <c r="C3" t="n">
         <v>175</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="D3">
+        <f>IF(ABS(B3-C3)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -4323,10 +4316,9 @@
       <c r="C4" t="n">
         <v>10</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="D4">
+        <f>IF(ABS(B4-C4)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -4342,10 +4334,9 @@
       <c r="C5" t="n">
         <v>60</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="D5">
+        <f>IF(ABS(B5-C5)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -4361,10 +4352,9 @@
       <c r="C6" t="n">
         <v>30</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="D6">
+        <f>IF(ABS(B6-C6)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -4380,156 +4370,216 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+      <c r="D7">
+        <f>IF(ABS(B7-C7)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Есть Human Summary</t>
+          <t>Сумма Big</t>
         </is>
       </c>
       <c r="B8">
-        <f>'Калькулятор'!A55</f>
-        <v/>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ИТОГОВЫЙ ЧЕЛОВЕЧЕСКИЙ РАСЧЁТ ВСЕХ УРОВНЕЙ</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B64</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>'Калькулятор'!$B$2*1.55</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IF(ABS(B8-C8)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Есть Human Comment</t>
+          <t>Сумма Small</t>
         </is>
       </c>
       <c r="B9">
-        <f>'Калькулятор'!U57</f>
-        <v/>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B65</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>'Калькулятор'!$B$2*0.75</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>IF(ABS(B9-C9)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Сумма Big</t>
+          <t>Сумма Close</t>
         </is>
       </c>
       <c r="B10">
-        <f>'Калькулятор'!B64</f>
-        <v/>
-      </c>
-      <c r="C10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B66</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>'Калькулятор'!$B$2*0.90</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>IF(ABS(B10-C10)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Сумма Small</t>
+          <t>Финальный Rounded Main</t>
         </is>
       </c>
       <c r="B11">
-        <f>'Калькулятор'!B65</f>
-        <v/>
-      </c>
-      <c r="C11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B70</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>'Калькулятор'!$B$2*1.65</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>IF(ABS(B11-C11)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Сумма Close</t>
+          <t>Финальный Rounded Opp</t>
         </is>
       </c>
       <c r="B12">
-        <f>'Калькулятор'!B66</f>
-        <v/>
-      </c>
-      <c r="C12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B71</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>'Калькулятор'!$B$2*1.75</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IF(ABS(B12-C12)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Маржа формула</t>
+          <t>Финальный Rounded Skew</t>
         </is>
       </c>
       <c r="B13">
-        <f>'Калькулятор'!Q18</f>
-        <v/>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B72</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>'Калькулятор'!$B$2*0.10</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>IF(ABS(B13-C13)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Просадка формула</t>
+          <t>Максимальная маржа</t>
         </is>
       </c>
       <c r="B14">
-        <f>'Калькулятор'!T18</f>
-        <v/>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B73</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>'Калькулятор'!$B$2*3740</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IF(ABS(B14-C14)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Margin Level формула</t>
+          <t>Максимальная нагрузка %</t>
         </is>
       </c>
       <c r="B15">
-        <f>'Калькулятор'!X18</f>
-        <v/>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <f>'Калькулятор'!B75</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>'Калькулятор'!$B$2*37.4</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IF(ABS(B15-C15)&lt;0.000001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Риск-анализ синхронизирован</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>IF(AND(ABS('РИСК_АНАЛИЗ'!B7-'Калькулятор'!R22)&lt;0.000001,ABS('РИСК_АНАЛИЗ'!C7-'Калькулятор'!Q22)&lt;0.000001,ABS('РИСК_АНАЛИЗ'!D7-'Калькулятор'!N22)&lt;0.000001,ABS('РИСК_АНАЛИЗ'!E7-'Калькулятор'!T22)&lt;0.000001,ABS('РИСК_АНАЛИЗ'!F7-'Калькулятор'!X22)&lt;0.000001,'РИСК_АНАЛИЗ'!G7='Калькулятор'!AA22),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D16">
+        <f>IF(B16=C16,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Human Summary есть</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>'Калькулятор'!A55</f>
+        <v/>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ИТОГОВЫЙ ЧЕЛОВЕЧЕСКИЙ РАСЧЁТ ВСЕХ УРОВНЕЙ</t>
+        </is>
+      </c>
+      <c r="D17">
+        <f>IF(B17=C17,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Human Comment есть</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>'Калькулятор'!U57</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>IF(LEN(B18)&gt;0,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
